--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5822F81B-C864-4449-85FE-7341AEEFAA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A2CB3D-EA84-4FEC-A916-2BEF577B3A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3753,29 +3753,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4131,7 +4131,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>68.599999999999994</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>103379.37679999998</v>
+        <v>104132.87079999999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4186,13 +4186,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15986601836174463</v>
+        <v>0.15689676518236584</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4299,22 +4299,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4352,13 +4352,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4387,13 +4387,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4409,13 +4409,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4479,13 +4479,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4501,7 +4501,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>347</v>
       </c>
       <c r="C50" s="344"/>
@@ -4523,22 +4523,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6967954245883027E-2</v>
+        <v>7.6411022594320921E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.7740524781341113E-2</v>
+        <v>6.7250361794500738E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4599,22 +4599,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4672,22 +4672,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4724,13 +4724,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>375</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4743,13 +4743,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4880,13 +4880,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>376</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5074,13 +5074,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5093,22 +5093,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>379</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5319,13 +5319,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>386</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5362,13 +5362,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>391</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5376,22 +5376,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>393</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5415,6 +5415,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5431,17 +5442,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13000,12 +13000,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.7740524781341113E-2</v>
+        <v>6.7250361794500738E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7740524781341113E-2</v>
+        <v>6.7250361794500738E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14199,50 +14199,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6967954245883027E-2</v>
+        <v>7.6411022594320921E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8623473442596714E-2</v>
+        <v>6.8126921536355051E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.5751854867083E-2</v>
+        <v>9.5059004976583122E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.1482875857811952E-2</v>
+        <v>9.082091582989725E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>7.467461203935534E-2</v>
+        <v>7.4134274759765209E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4627992325762452E-2</v>
+        <v>5.4232710181581822E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.7653372688444138E-2</v>
+        <v>6.716384032456249E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.5358812352277815E-2</v>
+        <v>7.4813524274475518E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.7421125864244915E-2</v>
+        <v>5.7005632912984099E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.0910442981118846E-2</v>
+        <v>5.0542060615119434E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.4279259961644502E-2</v>
+        <v>4.3958860106639838E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14256,43 +14256,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4485355071322123E-2</v>
+        <v>6.4018746134481885E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6931988431178104E-2</v>
+        <v>9.6230599224006036E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.082467375640052E-2</v>
+        <v>9.0167476406498928E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.267230302166032E-2</v>
+        <v>7.2146454229897225E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2399414135373291E-2</v>
+        <v>7.1875539937577532E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1446463923740752E-2</v>
+        <v>7.092948516886563E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8500472204432958E-2</v>
+        <v>7.7932451421477575E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4024241090221007E-2</v>
+        <v>6.3560968723432143E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.61517131722543E-2</v>
+        <v>5.5745405551615702E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1898158647054264E-2</v>
+        <v>5.1522629279130573E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-68.599999999999994</v>
+        <v>-69.099999999999994</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>68.599999999999994</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17399,7 +17399,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>68.599999999999994</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15986601836174463</v>
+        <v>0.15689676518236584</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A2CB3D-EA84-4FEC-A916-2BEF577B3A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9788E9-2284-44B2-B21E-86F02A01867E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3753,29 +3753,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4131,7 +4131,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>69.099999999999994</v>
+        <v>69.39</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>104132.87079999999</v>
+        <v>104569.89732</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4186,13 +4186,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15689676518236584</v>
+        <v>0.15518819500348435</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4299,22 +4299,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4352,13 +4352,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4387,13 +4387,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4409,13 +4409,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4479,13 +4479,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4501,7 +4501,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>347</v>
       </c>
       <c r="C50" s="344"/>
@@ -4523,22 +4523,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6411022594320921E-2</v>
+        <v>7.6091679799215661E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.7250361794500738E-2</v>
+        <v>6.6969303934284477E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4599,22 +4599,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4672,22 +4672,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4724,13 +4724,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4743,13 +4743,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4880,13 +4880,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5074,13 +5074,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5093,22 +5093,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>379</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5319,13 +5319,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5362,13 +5362,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5376,22 +5376,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>393</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5415,17 +5415,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5442,6 +5431,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13000,12 +13000,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.7250361794500738E-2</v>
+        <v>6.6969303934284477E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7250361794500738E-2</v>
+        <v>6.6969303934284477E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14199,50 +14199,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6411022594320921E-2</v>
+        <v>7.6091679799215661E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8126921536355051E-2</v>
+        <v>6.7842200290562524E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.5059004976583122E-2</v>
+        <v>9.4661727105950319E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.082091582989725E-2</v>
+        <v>9.0441350105863946E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>7.4134274759765209E-2</v>
+        <v>7.3824447123501599E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4232710181581822E-2</v>
+        <v>5.4006056687524194E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.716384032456249E-2</v>
+        <v>6.6883144061496869E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.4813524274475518E-2</v>
+        <v>7.4500857866641554E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.7005632912984099E-2</v>
+        <v>5.676739060797234E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.0542060615119434E-2</v>
+        <v>5.0330831366259585E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.3958860106639838E-2</v>
+        <v>4.3775143873307568E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14256,43 +14256,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4018746134481885E-2</v>
+        <v>6.3751194089821259E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6230599224006036E-2</v>
+        <v>9.5828424937005566E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0167476406498928E-2</v>
+        <v>8.9790641586526512E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2146454229897225E-2</v>
+        <v>7.1844934245365283E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1875539937577532E-2</v>
+        <v>7.1575152178795315E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.092948516886563E-2</v>
+        <v>7.063305123459597E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7932451421477575E-2</v>
+        <v>7.760675015454821E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3560968723432143E-2</v>
+        <v>6.3295329857171942E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5745405551615702E-2</v>
+        <v>5.5512430085266531E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1522629279130573E-2</v>
+        <v>5.130730196264479E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-69.099999999999994</v>
+        <v>-69.39</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>69.099999999999994</v>
+        <v>69.39</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17399,7 +17399,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>69.099999999999994</v>
+        <v>69.39</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15689676518236584</v>
+        <v>0.15518819500348435</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9788E9-2284-44B2-B21E-86F02A01867E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9183C35C-1DF0-47A4-9E92-C98330F0A0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3753,29 +3753,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4131,7 +4131,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>69.39</v>
+        <v>68.8</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>104569.89732</v>
+        <v>103680.77439999999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4186,13 +4186,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15518819500348435</v>
+        <v>0.15867473171661994</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4299,22 +4299,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4352,13 +4352,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4387,13 +4387,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4409,13 +4409,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4479,13 +4479,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4501,7 +4501,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>347</v>
       </c>
       <c r="C50" s="344"/>
@@ -4523,22 +4523,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6091679799215661E-2</v>
+        <v>7.6744210192842666E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.6969303934284477E-2</v>
+        <v>6.7543604651162797E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4599,22 +4599,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4672,22 +4672,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4724,13 +4724,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>375</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4743,13 +4743,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4880,13 +4880,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>376</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5074,13 +5074,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5093,22 +5093,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>379</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5319,13 +5319,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>386</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5362,13 +5362,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>391</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5376,22 +5376,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>393</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5415,6 +5415,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5431,17 +5442,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13000,12 +13000,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.6969303934284477E-2</v>
+        <v>6.7543604651162797E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.6969303934284477E-2</v>
+        <v>6.7543604651162797E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14199,50 +14199,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6091679799215661E-2</v>
+        <v>7.6744210192842666E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.7842200290562524E-2</v>
+        <v>6.8423986601193809E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.4661727105950319E-2</v>
+        <v>9.5473506451771703E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.0441350105863946E-2</v>
+        <v>9.1216937265202025E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>7.3824447123501599E-2</v>
+        <v>7.4457534678775819E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4006056687524194E-2</v>
+        <v>5.4469190022489886E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.6883144061496869E-2</v>
+        <v>6.7456705907373071E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.4500857866641554E-2</v>
+        <v>7.5139746037300253E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.676739060797234E-2</v>
+        <v>5.7254203986732574E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.0330831366259585E-2</v>
+        <v>5.0762447507336522E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.3775143873307568E-2</v>
+        <v>4.4150541182686229E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14256,43 +14256,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3751194089821259E-2</v>
+        <v>6.4297897643789209E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5828424937005566E-2</v>
+        <v>9.6650209395040931E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9790641586526512E-2</v>
+        <v>9.0560648541992375E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1844934245365283E-2</v>
+        <v>7.2461046326829898E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1575152178795315E-2</v>
+        <v>7.2188950722189046E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.063305123459597E-2</v>
+        <v>7.1238770714660088E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.760675015454821E-2</v>
+        <v>7.827227315732703E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3295329857171942E-2</v>
+        <v>6.3838124110307565E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5512430085266531E-2</v>
+        <v>5.5988481447916343E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.130730196264479E-2</v>
+        <v>5.1747291906801191E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-69.39</v>
+        <v>-68.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>69.39</v>
+        <v>68.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17399,7 +17399,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>69.39</v>
+        <v>68.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15518819500348435</v>
+        <v>0.15867473171661994</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9183C35C-1DF0-47A4-9E92-C98330F0A0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDDDC8E-D5D9-4150-AA94-462EB2164642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1578,10 +1578,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1786,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2366,19 +2358,49 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>洋河股份</t>
+  </si>
+  <si>
     <t>002304.SZ</t>
   </si>
   <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>洋河股份</t>
-  </si>
-  <si>
-    <t>N</t>
+    <t/>
   </si>
   <si>
     <t>CNS_03</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3052,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3753,6 +3775,13 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4065,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4085,10 +4113,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4106,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>002304.SZ Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>425</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4120,340 +4147,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>428</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>1506988000</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>68.8</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>1506988000</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (CNY):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>103680.77439999999</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
-        <v>369</v>
-      </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C15" s="32" t="str">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>CNY</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>430</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E19" s="339">
+      <c r="D24" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (CNY):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>49.746673136282389</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C21" s="280">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.15867473171661994</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
-        <v>364</v>
-      </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
-        <v>370</v>
-      </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
-        <v>348</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>10504024858.984821</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>697421786</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-697421786</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>123170761.45263389</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-2955080</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>120215681.45263389</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4461,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-11281261.817791469</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>123170761.45263389</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-2955080</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>120215681.45263389</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-11281261.817791469</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-2656060135.109364</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
-        <v>347</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
+        <v>346</v>
+      </c>
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
-        <v>352</v>
-      </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
-        <v>371</v>
-      </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>7094251918.3469982</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>7094251918.3469982</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>7956899143.5103006</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
-        <v>400</v>
-      </c>
-      <c r="C58" s="92">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
+        <v>398</v>
+      </c>
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>7.6744210192842666E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>6.7543604651162797E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
+        <v>363</v>
+      </c>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
+        <v>370</v>
+      </c>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C72" s="311">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
-        <v>253</v>
-      </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C67" s="311">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
-        <v>366</v>
-      </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
-        <v>373</v>
-      </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
-        <v>374</v>
-      </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>66.000020765844681</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
-        <v>367</v>
-      </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
-        <v>375</v>
-      </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
+        <v>365</v>
+      </c>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
-        <v>353</v>
-      </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>40134989.460000001</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.6632587293329478E-2</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="337">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.30279158651211824</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="337">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>7.7640983998987034E-4</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="338">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
+        <v>415</v>
+      </c>
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>3.8209153156820415E-3</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>21748297978.369999</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>17437737876.49247</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.571251978444732</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>3951628136.4709997</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4868,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.6222027889213448</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>17437737876.49247</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>11.571251978444732</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
-        <v>376</v>
-      </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>80.166842945917438</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>3951628136.4709997</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>416</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>15.284602440692964</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.6222027889213448</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
-        <v>368</v>
-      </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
-        <v>377</v>
-      </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>80.166842945917438</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>15.284602440692964</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
+        <v>366</v>
+      </c>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
+        <v>375</v>
+      </c>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>129.06 CNY</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>94.28 CNY</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>89.12 CNY</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>84.43 CNY</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>80.17 CNY</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>90.751910880412424</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
-        <v>380</v>
-      </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
-        <v>412</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
-        <v>379</v>
-      </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
+        <v>410</v>
+      </c>
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
+        <v>377</v>
+      </c>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>4.6470000000000002</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
-        <v>420</v>
-      </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>002304.SZ</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>8.4394765589440173</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>41.307196577338374</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>49.746673136282389</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
         <v>CNY</v>
       </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.45183883563801042</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
-        <v>423</v>
-      </c>
-      <c r="C136" s="337">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>9.7888194444444441</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>52.518466944683119</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>62.307286389127562</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
         <v>CNY</v>
       </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.31343278852571521</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
-        <v>410</v>
-      </c>
-      <c r="C142" s="92">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>11.9757696997409</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>72.041792791060502</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
-        <v>411</v>
-      </c>
-      <c r="C145" s="239">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>84.017562490801396</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
         <v>CNY</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>7.4206133229361537E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
+        <v>382</v>
+      </c>
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
-        <v>386</v>
-      </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
+        <v>388</v>
+      </c>
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
-        <v>390</v>
-      </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
-        <v>391</v>
-      </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
-        <v>392</v>
-      </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
-        <v>393</v>
-      </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
-        <v>398</v>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5476,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -5758,7 +5882,7 @@
         <v>159</v>
       </c>
       <c r="C11" s="181">
-        <v>8812.894363989999</v>
+        <v>8812.8943639900008</v>
       </c>
       <c r="D11" s="181">
         <v>12276.83537226</v>
@@ -6015,7 +6139,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>4628711237</v>
@@ -6051,7 +6175,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-1302245456</v>
@@ -6087,7 +6211,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-7049805121</v>
@@ -6146,7 +6270,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7204,7 +7328,7 @@
       </c>
       <c r="C57" s="188">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
-        <v>8812.894363989999</v>
+        <v>8812.8943639900008</v>
       </c>
       <c r="D57" s="188">
         <f t="shared" si="27"/>
@@ -7451,7 +7575,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8829,7 +8953,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8944,7 +9068,7 @@
       </c>
       <c r="D55" s="92">
         <f>Normalized_FCF!G11/G40</f>
-        <v>3.0012732378422154E-7</v>
+        <v>3.0012732378422159E-7</v>
       </c>
       <c r="F55" s="283"/>
     </row>
@@ -9125,12 +9249,12 @@
         <v>-2155280050.938765</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -9154,12 +9278,12 @@
         <v>4310560101.8775301</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -9167,7 +9291,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9357,7 +9481,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9851,7 +9975,7 @@
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
-        <v>8812.894363989999</v>
+        <v>8812.8943639900008</v>
       </c>
       <c r="H11" s="186">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
@@ -10184,7 +10308,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10209,7 +10333,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10537,7 +10661,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10597,7 +10721,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10721,7 +10845,7 @@
         <v>-1863726721.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10779,7 +10903,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11087,7 +11211,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11226,7 +11350,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11281,7 +11405,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11414,7 +11538,7 @@
         <v>2.8574189558100579E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11441,7 +11565,7 @@
         <v>7.3628523135533419E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11649,7 +11773,7 @@
       <c r="E60" s="302"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
-        <v>8812.894363989999</v>
+        <v>8812.8943639900008</v>
       </c>
       <c r="H60" s="191">
         <f>Data!D57</f>
@@ -11704,7 +11828,7 @@
       <c r="E61" s="302"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
-        <v>8812.894363989999</v>
+        <v>8812.8943639900008</v>
       </c>
       <c r="H61" s="184">
         <f t="shared" si="22"/>
@@ -11756,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11961,7 +12085,7 @@
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
-        <v>4.052222556797298E-7</v>
+        <v>4.0522225567972991E-7</v>
       </c>
       <c r="H69" s="176"/>
       <c r="I69" s="176"/>
@@ -11985,7 +12109,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12317,7 +12441,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>363</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12379,7 +12503,7 @@
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
-        <v>3.0519475422424031E-7</v>
+        <v>3.0519475422424036E-7</v>
       </c>
       <c r="H79" s="65">
         <f t="shared" si="30"/>
@@ -13690,7 +13814,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13742,7 +13866,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14251,7 +14375,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15052,7 +15176,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15062,7 +15186,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15080,10 +15204,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15098,8 +15222,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15114,8 +15238,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15130,8 +15254,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15157,7 +15281,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>CNY</v>
       </c>
       <c r="H11" s="121"/>
@@ -16625,11 +16749,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洋河股份(002304.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16650,8 +16774,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16672,8 +16796,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16683,8 +16807,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16697,8 +16821,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16716,8 +16840,8 @@
         <v>4.4367851108990219E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16734,8 +16858,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.0482342685147259E-2</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16752,8 +16876,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7775471405087737E-2</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16769,7 +16893,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16779,21 +16903,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
-        <v>339</v>
-      </c>
-      <c r="F18" s="351"/>
+      <c r="E18" s="353" t="s">
+        <v>338</v>
+      </c>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16807,8 +16931,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16822,8 +16946,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16843,8 +16967,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16854,8 +16978,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16869,8 +16993,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16880,8 +17004,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16901,8 +17025,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16912,8 +17036,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16927,8 +17051,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16938,8 +17062,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16959,8 +17083,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16970,8 +17094,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16985,8 +17109,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16997,8 +17121,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17060,8 +17184,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17071,8 +17195,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17086,8 +17210,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17097,8 +17221,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17118,8 +17242,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17129,8 +17253,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17144,8 +17268,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17155,8 +17279,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17174,13 +17298,13 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17205,7 +17329,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17238,7 +17362,7 @@
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
         <v>322</v>
@@ -17285,7 +17409,7 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17339,7 +17463,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17420,15 +17544,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17476,17 +17600,17 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
@@ -17518,14 +17642,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>84.017562490801396</v>
       </c>
       <c r="D99" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
@@ -17540,32 +17664,32 @@
     </row>
     <row r="101" spans="2:8" ht="14.65">
       <c r="E101" s="320" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F101" s="317"/>
     </row>
     <row r="102" spans="2:8" ht="13.9">
       <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
         <v>334</v>
-      </c>
-      <c r="F102" s="318" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="13.9">
       <c r="E103" s="314" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F103" s="318" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="13.9">
       <c r="E104" s="315" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F104" s="319" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDDDC8E-D5D9-4150-AA94-462EB2164642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F83B4CE-2D1B-44A9-A3F5-719F2FDC1721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8688,7 +8688,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>104802725.23</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F83B4CE-2D1B-44A9-A3F5-719F2FDC1721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18AFABA-A92F-4511-8862-CD75DE9047C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>68.8</v>
+        <v>69.47</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4226,8 +4226,7 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>103680.77439999999</v>
+        <v>1</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>49.746673136282389</v>
+        <v>40.456571020558471</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4349,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15867473171661994</v>
+        <v>0.15471860434131091</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6744210192842666E-2</v>
+        <v>7.6004054430222762E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4651,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.7543604651162797E-2</v>
+        <v>6.6892183676407091E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>8.4394765589440173</v>
+        <v>7.3837172011661796</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>41.307196577338374</v>
+        <v>33.072853819392293</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>49.746673136282389</v>
+        <v>40.456571020558471</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45183883563801042</v>
+        <v>0.55420695136800169</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13124,12 +13123,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.7543604651162797E-2</v>
+        <v>6.6892183676407091E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7543604651162797E-2</v>
+        <v>6.6892183676407091E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14323,50 +14322,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6744210192842666E-2</v>
+        <v>7.6004054430222762E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8423986601193809E-2</v>
+        <v>6.7764074825998763E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.5473506451771703E-2</v>
+        <v>9.4552716912075618E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.1216937265202025E-2</v>
+        <v>9.0337199997781767E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>7.4457534678775819E-2</v>
+        <v>7.3739432645743133E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4469190022489886E-2</v>
+        <v>5.3943864596909516E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.7456705907373071E-2</v>
+        <v>6.6806123023280081E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.5139746037300253E-2</v>
+        <v>7.441506445035638E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.7254203986732574E-2</v>
+        <v>5.6702018630879529E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.0762447507336522E-2</v>
+        <v>5.0272871577727835E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.4150541182686229E-2</v>
+        <v>4.3724733458598133E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14380,43 +14379,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4297897643789209E-2</v>
+        <v>6.3677779730713938E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6650209395040931E-2</v>
+        <v>9.5718071201652752E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0560648541992375E-2</v>
+        <v>8.9687240818901323E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2461046326829898E-2</v>
+        <v>7.1762199327564377E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2188950722189046E-2</v>
+        <v>7.1492727935606834E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1238770714660088E-2</v>
+        <v>7.055171189245163E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.827227315732703E-2</v>
+        <v>7.7517380066562544E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3838124110307565E-2</v>
+        <v>6.3222440460474469E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5988481447916343E-2</v>
+        <v>5.5448503290868645E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1747291906801191E-2</v>
+        <v>5.1248217693794756E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16685,7 +16684,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-68.8</v>
+        <v>-69.47</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16925,7 +16924,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>68.8</v>
+        <v>69.47</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17464,7 +17463,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17473,7 +17472,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>8.4394765589440173</v>
+        <v>7.3837172011661796</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17485,7 +17484,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>41.307196577338374</v>
+        <v>33.072853819392293</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17495,7 +17494,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>49.746673136282389</v>
+        <v>40.456571020558471</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17506,7 +17505,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.45183883563801042</v>
+        <v>0.55420695136800169</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17523,7 +17522,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>68.8</v>
+        <v>69.47</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17536,7 +17535,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15867473171661994</v>
+        <v>0.15471860434131091</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18AFABA-A92F-4511-8862-CD75DE9047C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8223ECAC-36E1-44CC-A02B-C6473E28C6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <v>1</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>104690.45636</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8223ECAC-36E1-44CC-A02B-C6473E28C6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59B4DE8-A9CF-4AC0-B082-1BE64FE9F30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>69.47</v>
+        <v>68.88</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>104690.45636</v>
+        <v>103801.33344</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>40.456571020558471</v>
+        <v>40.298277562480884</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15471860434131091</v>
+        <v>0.15653784580144725</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
-        <v>-697421786</v>
+        <v>-742549850.49555075</v>
       </c>
       <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>7094251918.3469982</v>
+        <v>6396830132.3469982</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>7956899143.5103006</v>
+        <v>7911771079.0147505</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6004054430222762E-2</v>
+        <v>7.6220322194492512E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.6892183676407091E-2</v>
+        <v>6.7465156794425094E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>66.000020765844681</v>
+        <v>65.625697409458056</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>129.06 CNY</v>
+        <v>128.41 CNY</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>94.28 CNY</v>
+        <v>93.83 CNY</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>89.12 CNY</v>
+        <v>88.69 CNY</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>84.43 CNY</v>
+        <v>84.03 CNY</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>80.17 CNY</v>
+        <v>79.79 CNY</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>90.751910880412424</v>
+        <v>90.317553631447524</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>33.072853819392293</v>
+        <v>32.914560361314706</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>40.456571020558471</v>
+        <v>40.298277562480884</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55420695136800169</v>
+        <v>0.55381566548045336</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>52.518466944683119</v>
+        <v>52.267102795976577</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>62.307286389127562</v>
+        <v>62.055922240421019</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31343278852571521</v>
+        <v>0.31291404887195851</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>72.041792791060502</v>
+        <v>71.696986002711341</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>84.017562490801396</v>
+        <v>83.672755702452235</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>7.4206133229361537E-2</v>
+        <v>7.3571500354297048E-2</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -7480,32 +7480,32 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
-        <v>0</v>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
+        <v>-697421786</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
-        <v>0</v>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
+        <v>-730011100</v>
       </c>
       <c r="E62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-752915036</v>
       </c>
       <c r="F62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-759253984</v>
       </c>
       <c r="G62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-782849742</v>
       </c>
       <c r="H62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-776102930</v>
       </c>
       <c r="I62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-757446024</v>
       </c>
       <c r="J62" s="183">
         <f t="shared" si="30"/>
@@ -9913,36 +9913,36 @@
       </c>
       <c r="C10" s="191">
         <f>-C4*C78</f>
-        <v>-697421786</v>
+        <v>-742549850.49555075</v>
       </c>
       <c r="E10" s="302"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
-        <v>0</v>
+        <v>-697421786</v>
       </c>
       <c r="H10" s="191">
         <f>Data!D62</f>
-        <v>0</v>
+        <v>-730011100</v>
       </c>
       <c r="I10" s="191">
         <f>Data!E62</f>
-        <v>0</v>
+        <v>-752915036</v>
       </c>
       <c r="J10" s="191">
         <f>Data!F62</f>
-        <v>0</v>
+        <v>-759253984</v>
       </c>
       <c r="K10" s="191">
         <f>Data!G62</f>
-        <v>0</v>
+        <v>-782849742</v>
       </c>
       <c r="L10" s="191">
         <f>Data!H62</f>
-        <v>0</v>
+        <v>-776102930</v>
       </c>
       <c r="M10" s="191">
         <f>Data!I62</f>
-        <v>0</v>
+        <v>-757446024</v>
       </c>
       <c r="N10" s="191">
         <f>Data!J62</f>
@@ -10080,36 +10080,36 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>10624240540.437456</v>
+        <v>10579112475.941906</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>9570872710.3469982</v>
+        <v>8873450924.3469982</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>13100670162.603086</v>
+        <v>12370659062.603086</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>12582894156.052364</v>
+        <v>11829979120.052364</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>10158559576.410332</v>
+        <v>9399305592.4103317</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>8044081060.4725046</v>
+        <v>7261231318.4725046</v>
       </c>
       <c r="L13" s="184">
         <f t="shared" si="7"/>
-        <v>9381945036.9494953</v>
+        <v>8605842106.9494953</v>
       </c>
       <c r="M13" s="184">
         <f t="shared" si="7"/>
-        <v>10514543051.366621</v>
+        <v>9757097027.366621</v>
       </c>
       <c r="N13" s="184">
         <f t="shared" si="7"/>
@@ -10247,38 +10247,38 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>7956899143.5103006</v>
+        <v>7911771079.0147505</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>7094251918.3469982</v>
+        <v>6396830132.3469982</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>9898767083.6030865</v>
+        <v>9168755983.6030865</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>9457442694.0523643</v>
+        <v>8704527658.0523643</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>7719814855.4103317</v>
+        <v>6960560871.4103317</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>5647407802.4725046</v>
+        <v>4864558060.4725046</v>
       </c>
       <c r="L16" s="184">
         <f t="shared" si="8"/>
-        <v>6993963506.9494953</v>
+        <v>6217860576.9494953</v>
       </c>
       <c r="M16" s="184">
         <f t="shared" si="8"/>
-        <v>7790547057.366621</v>
+        <v>7033101033.366621</v>
       </c>
       <c r="N16" s="184">
         <f t="shared" si="8"/>
@@ -10355,38 +10355,38 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>7956899143.5103006</v>
+        <v>7911771079.0147505</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>7094251918.3469982</v>
+        <v>6396830132.3469982</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>9898767083.6030865</v>
+        <v>9168755983.6030865</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>9457442694.0523643</v>
+        <v>8704527658.0523643</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>7719814855.4103317</v>
+        <v>6960560871.4103317</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>5647407802.4725046</v>
+        <v>4864558060.4725046</v>
       </c>
       <c r="L19" s="186">
         <f t="shared" si="9"/>
-        <v>6993963506.9494953</v>
+        <v>6217860576.9494953</v>
       </c>
       <c r="M19" s="186">
         <f t="shared" si="9"/>
-        <v>7790547057.366621</v>
+        <v>7033101033.366621</v>
       </c>
       <c r="N19" s="186">
         <f t="shared" si="9"/>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>2.3750578776664314E-2</v>
+        <v>2.5287407238802385E-2</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
@@ -12446,31 +12446,31 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>0</v>
+        <v>2.4152050595161571E-2</v>
       </c>
       <c r="H78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>2.2037221020504476E-2</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>2.5009720389772557E-2</v>
       </c>
       <c r="J78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>2.9950636949770928E-2</v>
       </c>
       <c r="K78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>3.7100035306430725E-2</v>
       </c>
       <c r="L78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>3.3559064524150931E-2</v>
       </c>
       <c r="M78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>3.135149965867922E-2</v>
       </c>
       <c r="N78" s="6">
         <f t="shared" si="29"/>
@@ -12610,38 +12610,38 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.36180668135579358</v>
+        <v>0.36026985289365554</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.33144390751818564</v>
+        <v>0.30729185692302408</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.39547667684780757</v>
+        <v>0.37343945582730309</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.41796836228539969</v>
+        <v>0.39295864189562718</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.40072931616738749</v>
+        <v>0.37077867921761659</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.38121707824656936</v>
+        <v>0.34411704294013862</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.4056798224650765</v>
+        <v>0.37212075794092558</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.43520816327644829</v>
+        <v>0.40385666361776906</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
@@ -12782,38 +12782,38 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>0.27097082958907481</v>
+        <v>0.26943400112693677</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.24567734290241794</v>
+        <v>0.22152529230725637</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.29881917966981014</v>
+        <v>0.27678195864930566</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.31414965310979248</v>
+        <v>0.28913993272001992</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.30452704487072296</v>
+        <v>0.27457640792095206</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>0.26763632613107802</v>
+        <v>0.23053629082464727</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.30242235087203578</v>
+        <v>0.26886328634788487</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.3224590606735484</v>
+        <v>0.29110756101486918</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
@@ -12889,38 +12889,38 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>0.27097082958907481</v>
+        <v>0.26943400112693677</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.24567734290241794</v>
+        <v>0.22152529230725637</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.29881917966981014</v>
+        <v>0.27678195864930566</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.31414965310979248</v>
+        <v>0.28913993272001992</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.30452704487072296</v>
+        <v>0.27457640792095206</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>0.26763632613107802</v>
+        <v>0.23053629082464727</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.30242235087203578</v>
+        <v>0.26886328634788487</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.3224590606735484</v>
+        <v>0.29110756101486918</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
@@ -13069,12 +13069,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.88011335945004043</v>
+        <v>0.88513345065995985</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.98713343092441719</v>
+        <v>1.0947567922099266</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13124,12 +13124,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.6892183676407091E-2</v>
+        <v>6.7465156794425094E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.6892183676407091E-2</v>
+        <v>6.7465156794425094E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13261,38 +13261,38 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>0.11005974710662181</v>
+        <v>0.19222076801201537</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.26943640351561393</v>
+        <v>-0.2827018447891968</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>4.1149198278972454E-2</v>
+        <v>4.5704217823533178E-2</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.23864944251266618</v>
+        <v>0.25860139387368486</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.26286141326050028</v>
+        <v>0.29445064895516904</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.14259985229160888</v>
+        <v>-0.15624395285978743</v>
       </c>
       <c r="L97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.10771728346957665</v>
+        <v>-0.11799154166327297</v>
       </c>
       <c r="M97" s="6">
         <f t="shared" si="41"/>
-        <v>0.28770604669207467</v>
+        <v>0.19494235545197869</v>
       </c>
       <c r="N97" s="6">
         <f t="shared" si="41"/>
@@ -13872,31 +13872,31 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>0.65245938405842752</v>
+        <v>0.72359452122917711</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.61929135378429767</v>
+        <v>0.66859897667283974</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>0.38568818971474528</v>
+        <v>0.41904903922335918</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.9842659141319254</v>
+        <v>2.2007085009366882</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>0.70453400483280781</v>
+        <v>0.81791414277282404</v>
       </c>
       <c r="L114" s="334">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>0.97196559064761057</v>
+        <v>1.0932847057074204</v>
       </c>
       <c r="M114" s="334">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.162530532106353</v>
+        <v>1.2877319368842757</v>
       </c>
       <c r="N114" s="334">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -13980,36 +13980,36 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.36180668135579358</v>
+        <v>0.36026985289365554</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.33144390751818564</v>
+        <v>0.30729185692302408</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.39547667684780757</v>
+        <v>0.37343945582730309</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.41796836228539969</v>
+        <v>0.39295864189562718</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.40072931616738749</v>
+        <v>0.37077867921761659</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>0.38121707824656936</v>
+        <v>0.34411704294013862</v>
       </c>
       <c r="L117" s="23">
         <f t="shared" si="45"/>
-        <v>0.4056798224650765</v>
+        <v>0.37212075794092558</v>
       </c>
       <c r="M117" s="23">
         <f t="shared" si="45"/>
-        <v>0.43520816327644829</v>
+        <v>0.40385666361776906</v>
       </c>
       <c r="N117" s="23">
         <f t="shared" si="45"/>
@@ -14266,38 +14266,38 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2800016612675753</v>
+        <v>5.2500557927566449</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>4.7075702781621338</v>
+        <v>4.2447784138606268</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>6.5685772438818928</v>
+        <v>6.0841599160730455</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2757252838458992</v>
+        <v>5.776109470050435</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>5.1226783858997758</v>
+        <v>4.6188562028432418</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>3.7474802735473038</v>
+        <v>3.2280005285194737</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>4.6410213664272675</v>
+        <v>4.1260186391328233</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>5.1696145273662575</v>
+        <v>4.6669920618920795</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
@@ -14323,50 +14323,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6004054430222762E-2</v>
+        <v>7.6220322194492512E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.7764074825998763E-2</v>
+        <v>6.1625702872541044E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.4552716912075618E-2</v>
+        <v>8.8329847794324123E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.0337199997781767E-2</v>
+        <v>8.3857570703403536E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>7.3739432645743133E-2</v>
+        <v>6.7056565081928601E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.3943864596909516E-2</v>
+        <v>4.6864119171304792E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.6806123023280081E-2</v>
+        <v>5.9901548187178043E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.441506445035638E-2</v>
+        <v>6.7755401595413475E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.6702018630879529E-2</v>
+        <v>5.7187706653414647E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.0272871577727835E-2</v>
+        <v>5.0703489960870395E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.3724733458598133E-2</v>
+        <v>4.4099262969930497E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14380,43 +14380,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3677779730713938E-2</v>
+        <v>6.4223219481601299E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5718071201652752E-2</v>
+        <v>9.6537955957880617E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9687240818901323E-2</v>
+        <v>9.0455467765520839E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1762199327564377E-2</v>
+        <v>7.2376887155718606E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1492727935606834E-2</v>
+        <v>7.2105107573847374E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.055171189245163E-2</v>
+        <v>7.1156031143562934E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7517380066562544E-2</v>
+        <v>7.8181364593845823E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3222440460474469E-2</v>
+        <v>6.3763979947577834E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5448503290868645E-2</v>
+        <v>5.5923454175619114E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1248217693794756E-2</v>
+        <v>5.1687190522472733E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>7956899143.5103006</v>
+        <v>7911771079.0147505</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>99461239293.878754</v>
+        <v>98897138487.684372</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>120810470317.38222</v>
+        <v>120246369511.18782</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>90.758798783650263</v>
+        <v>90.324402469499802</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>8327490693.804677</v>
+        <v>8280260795.5317278</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>7710639531.3006258</v>
+        <v>7666908144.0108585</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>8715342497.7069683</v>
+        <v>8665912873.0198059</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>7472001455.5100889</v>
+        <v>7429623519.3928375</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>9121258449.3004951</v>
+        <v>9069526646.2253819</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>7240749035.7323685</v>
+        <v>7199682662.565238</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>9546079883.9317112</v>
+        <v>9491938678.8074646</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>7016653691.8695097</v>
+        <v>6976858289.836812</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>9990687322.032217</v>
+        <v>9934024497.269474</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>6799493918.1932707</v>
+        <v>6760930151.7632799</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>10456002294.159021</v>
+        <v>10396700405.648687</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>6589055064.3990755</v>
+        <v>6551684815.4430552</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>10942989251.035856</v>
+        <v>10880925384.724613</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>6385129123.4361944</v>
+        <v>6348915453.5507507</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>11452657562.554379</v>
+        <v>11387703079.682753</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>6187514525.9043703</v>
+        <v>6152421639.8999147</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>11986063609.878641</v>
+        <v>11918083880.353537</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>5996015940.8137579</v>
+        <v>5962009151.3329487</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>12544312974.989019</v>
+        <v>12473167098.33814</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>5810444082.5111265</v>
+        <v>5777489775.742363</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>104093633672.55846</v>
+        <v>103503259944.14659</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>48215493268.201691</v>
+        <v>47942036001.665039</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>115423189637.87209</v>
+        <v>114768559605.20309</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16084,7 +16084,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>115423189637.87209</v>
+        <v>114768559605.20309</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16114,19 +16114,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>99461239293.878738</v>
+        <v>98897138487.684357</v>
       </c>
       <c r="C56" s="124">
-        <v>102670379526.41306</v>
+        <v>102088077875.29443</v>
       </c>
       <c r="D56" s="124">
-        <v>105975632108.49921</v>
+        <v>105374584505.09332</v>
       </c>
       <c r="E56" s="124">
-        <v>109381214760.52371</v>
+        <v>108760852176.39565</v>
       </c>
       <c r="F56" s="124">
-        <v>116510896194.4758</v>
+        <v>115850097164.217</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16135,19 +16135,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>99461239293.878723</v>
+        <v>98897138487.684326</v>
       </c>
       <c r="C57" s="124">
-        <v>105882474869.97748</v>
+        <v>105281955613.83261</v>
       </c>
       <c r="D57" s="124">
-        <v>112947292112.40126</v>
+        <v>112306704291.55356</v>
       </c>
       <c r="E57" s="124">
-        <v>120732713643.93181</v>
+        <v>120047970304.87741</v>
       </c>
       <c r="F57" s="124">
-        <v>138817370667.01062</v>
+        <v>138030059034.22797</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16156,19 +16156,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>99461239293.878708</v>
+        <v>98897138487.684326</v>
       </c>
       <c r="C58" s="124">
-        <v>109858333488.21954</v>
+        <v>109235264894.58612</v>
       </c>
       <c r="D58" s="124">
-        <v>122035735039.5298</v>
+        <v>121343601530.94844</v>
       </c>
       <c r="E58" s="124">
-        <v>136347138311.85847</v>
+        <v>135573836760.51987</v>
       </c>
       <c r="F58" s="124">
-        <v>173149520249.06439</v>
+        <v>172167491625.06873</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16177,19 +16177,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>99461239293.878693</v>
+        <v>98897138487.684326</v>
       </c>
       <c r="C59" s="124">
-        <v>113909095821.52815</v>
+        <v>113263053069.17578</v>
       </c>
       <c r="D59" s="124">
-        <v>131817862960.77042</v>
+        <v>131070249485.46187</v>
       </c>
       <c r="E59" s="124">
-        <v>154158952637.9407</v>
+        <v>153284630237.75223</v>
       </c>
       <c r="F59" s="124">
-        <v>217506260897.88818</v>
+        <v>216272660170.65109</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16198,19 +16198,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>99461239293.878693</v>
+        <v>98897138487.684357</v>
       </c>
       <c r="C60" s="124">
-        <v>117676529568.34595</v>
+        <v>117009119573.54868</v>
       </c>
       <c r="D60" s="124">
-        <v>141453591744.15585</v>
+        <v>140651328614.23242</v>
       </c>
       <c r="E60" s="124">
-        <v>172825192485.27939</v>
+        <v>171845003307.02484</v>
       </c>
       <c r="F60" s="124">
-        <v>270702498161.31653</v>
+        <v>269167191558.10355</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16219,19 +16219,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>99461239293.878693</v>
+        <v>98897138487.684341</v>
       </c>
       <c r="C61" s="124">
-        <v>120999930213.88893</v>
+        <v>120313671338.89705</v>
       </c>
       <c r="D61" s="124">
-        <v>150477537143.78979</v>
+        <v>149624094128.00204</v>
       </c>
       <c r="E61" s="124">
-        <v>191489060218.90814</v>
+        <v>190403017716.18277</v>
       </c>
       <c r="F61" s="124">
-        <v>332125475338.44678</v>
+        <v>330241804375.50458</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16281,23 +16281,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16308,23 +16308,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>80.166842945917409</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>82.296349108232135</v>
+        <v>81.909948120886099</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>84.489633050828985</v>
+        <v>84.090792712746747</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>86.749493548739053</v>
+        <v>86.337836266711548</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>91.48057397801395</v>
+        <v>91.042084069495203</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16335,23 +16335,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>80.166842945917409</v>
+        <v>79.79251958953077</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>84.427816209207336</v>
+        <v>84.029326469312352</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>89.115854363740596</v>
+        <v>88.69077611437983</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>94.282067718810808</v>
+        <v>93.827688958625345</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>106.28259925793311</v>
+        <v>105.76015871243264</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16362,23 +16362,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>80.166842945917395</v>
+        <v>79.79251958953077</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>87.066097747110803</v>
+        <v>86.65264482403947</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>95.146720520026207</v>
+        <v>94.687437825949445</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>104.64341410506384</v>
+        <v>104.13027030342866</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>129.0645653930674</v>
+        <v>128.41291546354199</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16389,23 +16389,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>80.166842945917395</v>
+        <v>79.79251958953077</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>89.754083539505032</v>
+        <v>89.325385532385951</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>101.63789889785048</v>
+        <v>101.14180106873135</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>116.46289397224409</v>
+        <v>115.88271523147876</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>158.49860245827549</v>
+        <v>157.68001549723991</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16416,23 +16416,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>80.166842945917395</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>92.254059482789131</v>
+        <v>91.811182701555794</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>108.03193042523188</v>
+        <v>107.49956843567162</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>128.84934950297074</v>
+        <v>128.19892018418747</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>193.79831105809734</v>
+        <v>192.77951953274152</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16442,23 +16442,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>80.166842945917395</v>
+        <v>79.79251958953077</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>94.459386031867808</v>
+        <v>94.004001599482223</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>114.01999761596859</v>
+        <v>113.45367391877409</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>141.23423095765304</v>
+        <v>140.51355998832523</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>234.55708098667691</v>
+        <v>233.30712348008615</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>129.0645653930674</v>
+        <v>128.41291546354199</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>94.282067718810808</v>
+        <v>93.827688958625345</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16538,7 +16538,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>89.115854363740596</v>
+        <v>88.69077611437983</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>84.427816209207336</v>
+        <v>84.029326469312352</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>80.166842945917395</v>
+        <v>79.79251958953077</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-69.47</v>
+        <v>-68.88</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>95.39891088041243</v>
+        <v>94.964553631447529</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>7094251918.3469982</v>
+        <v>6396830132.3469982</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>7956899143.5103006</v>
+        <v>7911771079.0147505</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-2.7775471405087737E-2</v>
+        <v>-2.7759904709511951E-2</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>69.47</v>
+        <v>68.88</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>80.166842945917438</v>
+        <v>79.792519589530784</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>89.115854363740596</v>
+        <v>88.69077611437983</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>84.427816209207336</v>
+        <v>84.029326469312352</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>94.282067718810808</v>
+        <v>93.827688958625345</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>89.211489403847992</v>
+        <v>88.785868754215429</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>80.166842945917395</v>
+        <v>79.79251958953077</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>129.0645653930674</v>
+        <v>128.41291546354199</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>90.751910880412424</v>
+        <v>90.317553631447524</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>90.758798783650263</v>
+        <v>90.324402469499802</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.15610494636020344</v>
+        <v>0.15685568984609902</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>33.072853819392293</v>
+        <v>32.914560361314706</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>40.456571020558471</v>
+        <v>40.298277562480884</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17506,7 +17506,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.55420695136800169</v>
+        <v>0.55381566548045336</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>69.47</v>
+        <v>68.88</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15471860434131091</v>
+        <v>0.15653784580144725</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>52.518466944683119</v>
+        <v>52.267102795976577</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>62.307286389127562</v>
+        <v>62.055922240421019</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.31343278852571521</v>
+        <v>0.31291404887195851</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>72.041792791060502</v>
+        <v>71.696986002711341</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>84.017562490801396</v>
+        <v>83.672755702452235</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>7.4206133229361537E-2</v>
+        <v>7.3571500354297048E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59B4DE8-A9CF-4AC0-B082-1BE64FE9F30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F07C38-63A1-4725-969F-DFD04D600CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F07C38-63A1-4725-969F-DFD04D600CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC67BAC1-E0A8-41E9-9AA9-F4C54809EC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2377,6 +2377,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>N</t>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4194,10 +4206,10 @@
         <v>427</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4206,7 +4218,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>68.88</v>
+        <v>68.31</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4239,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>103801.33344</v>
+        <v>102942.35028</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4310,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4350,10 +4362,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15653784580144725</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.15993573478625023</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4643,7 +4659,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6220322194492512E-2</v>
+        <v>7.6856328396378931E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4668,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.7465156794425094E-2</v>
+        <v>6.8028107158541948E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4709,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4721,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5308,7 +5324,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5318,7 +5334,7 @@
         <v>9.7888194444444441</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5328,7 +5344,7 @@
         <v>52.267102795976577</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
@@ -5341,7 +5357,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>426</v>
       </c>
@@ -5354,7 +5370,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
@@ -5363,12 +5379,12 @@
         <v>0.31291404887195851</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5377,7 +5393,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5387,7 +5403,7 @@
         <v>11.9757696997409</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5397,7 +5413,7 @@
         <v>71.696986002711341</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
@@ -5410,7 +5426,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>426</v>
       </c>
@@ -5423,7 +5439,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
@@ -5432,118 +5448,187 @@
         <v>7.3571500354297048E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>11.211366726236903</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>64.736045237011837</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>75.94741196324874</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.15917061295928081</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6270,7 +6355,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12109,7 +12194,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12441,7 +12526,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13124,12 +13209,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.7465156794425094E-2</v>
+        <v>6.8028107158541948E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.7465156794425094E-2</v>
+        <v>6.8028107158541948E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14323,50 +14408,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6220322194492512E-2</v>
+        <v>7.6856328396378931E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.1625702872541044E-2</v>
+        <v>6.2139927007182356E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>8.8329847794324123E-2</v>
+        <v>8.9066899664368981E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.3857570703403536E-2</v>
+        <v>8.4557304494955854E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.7056565081928601E-2</v>
+        <v>6.7616106029032966E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.6864119171304792E-2</v>
+        <v>4.7255168035711809E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9901548187178043E-2</v>
+        <v>6.0401385435995068E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.7755401595413475E-2</v>
+        <v>6.8320773852907038E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.7187706653414647E-2</v>
+        <v>5.7664898759877042E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.0703489960870395E-2</v>
+        <v>5.1126575735686609E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.4099262969930497E-2</v>
+        <v>4.446724100964445E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14380,43 +14465,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4223219481601299E-2</v>
+        <v>6.4759118107051636E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6537955957880617E-2</v>
+        <v>9.7343498849053092E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0455467765520839E-2</v>
+        <v>9.1210256473270024E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2376887155718606E-2</v>
+        <v>7.2980822533829565E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2105107573847374E-2</v>
+        <v>7.2706775138143859E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1156031143562934E-2</v>
+        <v>7.1749779317356377E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8181364593845823E-2</v>
+        <v>7.8833734346714979E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3763979947577834E-2</v>
+        <v>6.429604653475568E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5923454175619114E-2</v>
+        <v>5.6390096964084972E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1687190522472733E-2</v>
+        <v>5.2118484602370396E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16652,7 +16737,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16685,7 +16770,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-68.88</v>
+        <v>-68.31</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16925,7 +17010,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>68.88</v>
+        <v>68.31</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17523,7 +17608,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>68.88</v>
+        <v>68.31</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17536,7 +17621,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15653784580144725</v>
+        <v>0.15993573478625023</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17662,33 +17747,89 @@
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>431</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>11.211366726236903</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>64.736045237011837</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>75.94741196324874</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.15917061295928081</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC67BAC1-E0A8-41E9-9AA9-F4C54809EC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC73C40-83F7-4021-9EDA-2D6D0B7F24C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2382,13 +2359,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>N</t>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,6 +3803,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45780</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>435</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>436</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>CNY</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4271,29 +4307,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (CNY):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>40.298277562480884</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (CNY) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>90.317553631447524</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.15993573478625023</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>002304.SZ (CNY)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>433</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>40.298277562480884</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>62.055922240421019</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>83.672755702452235</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>75.94741196324874</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>442</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>10504024858.984821</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>697421786</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-742549850.49555075</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>123170761.45263389</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>123170761.45263389</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-2955080</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>120215681.45263389</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-11281261.817791469</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-2656060135.109364</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,1080 +4676,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-11281261.817791469</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>6396830132.3469982</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-2656060135.109364</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>7911771079.0147505</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>6396830132.3469982</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>7911771079.0147505</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>7.6856328396378931E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>6.8028107158541948E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>65.625697409458056</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>40134989.460000001</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.6632587293329478E-2</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>0.30279158651211824</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>7.7640983998987034E-4</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>3.8209153156820415E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>21748297978.369999</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>17437737876.49247</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>11.571251978444732</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>3951628136.4709997</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.6222027889213448</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>17437737876.49247</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>11.571251978444732</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>79.792519589530784</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>3951628136.4709997</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>15.284602440692964</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.6222027889213448</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>79.792519589530784</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>15.284602440692964</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>128.41 CNY</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>93.83 CNY</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>88.69 CNY</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>84.03 CNY</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>79.79 CNY</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>90.317553631447524</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>4.6470000000000002</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>002304.SZ</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>7.3837172011661796</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>32.914560361314706</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>40.298277562480884</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C140" s="340" t="str">
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.55381566548045336</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>9.7888194444444441</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>52.267102795976577</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>62.055922240421019</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C148" s="340" t="str">
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.31291404887195851</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>11.9757696997409</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>71.696986002711341</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>83.672755702452235</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C156" s="340" t="str">
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>7.3571500354297048E-2</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>11.211366726236903</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>64.736045237011837</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>75.94741196324874</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C164" s="340" t="str">
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>0.15917061295928081</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5675,17 +5792,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6224,7 +6341,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>4628711237</v>
@@ -6260,7 +6377,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-1302245456</v>
@@ -6296,7 +6413,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-7049805121</v>
@@ -6355,7 +6472,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7660,7 +7777,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8108,11 +8225,11 @@
         <f t="shared" si="40"/>
         <v>675347400</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8142,11 +8259,11 @@
         <f t="shared" si="40"/>
         <v>14433244696</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8278,15 +8395,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8344,7 +8461,7 @@
         <f>413398699+8994904.73+1090851688.67+17051847.78</f>
         <v>1530297140.1800001</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8354,7 +8471,7 @@
       <c r="G4" s="19">
         <v>21748297978.369999</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8365,7 +8482,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8375,7 +8492,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8386,7 +8503,7 @@
       <c r="C6" s="19">
         <v>19732881051.73</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8396,7 +8513,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8407,7 +8524,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8417,7 +8534,7 @@
       <c r="G7" s="19">
         <v>6380145437.1400003</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8428,7 +8545,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8438,7 +8555,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8449,7 +8566,7 @@
       <c r="C9" s="19">
         <v>23310180.68</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8459,7 +8576,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8470,10 +8587,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8482,10 +8599,10 @@
       <c r="C11" s="19">
         <v>909932715.44000006</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8543,7 +8660,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8552,7 +8669,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8563,7 +8680,7 @@
       <c r="C16" s="19">
         <v>4614148799.21</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8572,7 +8689,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8583,7 +8700,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8592,7 +8709,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8603,7 +8720,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8612,7 +8729,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8624,7 +8741,7 @@
         <f>5571618070.98+1912601220.28+66814914.62</f>
         <v>7551034205.8799992</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8633,7 +8750,7 @@
       <c r="G19" s="19">
         <v>1235408741.8699999</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8644,7 +8761,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8653,7 +8770,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8664,7 +8781,7 @@
       <c r="C21" s="19">
         <v>1804220059.96</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8673,7 +8790,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8685,10 +8802,10 @@
         <f>1242507668.92+180606719.81</f>
         <v>1423114388.73</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8698,10 +8815,10 @@
         <f>276001989.95+116472530.48</f>
         <v>392474520.43000001</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9034,13 +9151,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9056,7 +9173,7 @@
         <f>H29</f>
         <v>23033712462.895008</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9071,23 +9188,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>15.284602440692964</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9101,7 +9218,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>4.5851652280403769E-3</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9112,22 +9229,22 @@
         <f>G29/G32</f>
         <v>0.76602628203208212</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9141,7 +9258,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.23046078921961435</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9155,22 +9272,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>3.0012732378422159E-7</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9192,22 +9309,22 @@
         <f>G39/G32</f>
         <v>0.1121242032569815</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9221,7 +9338,7 @@
         <f>G28/G29</f>
         <v>2.0315234416617856E-3</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9240,13 +9357,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9274,7 +9391,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9284,7 +9401,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9294,7 +9411,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9304,26 +9421,26 @@
         <f>SUM(C66:C69)</f>
         <v>21748297978.369999</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9334,65 +9451,65 @@
         <v>-2155280050.938765</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>9.6209966209831155</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>10.090706295405646</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>4310560101.8775301</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9406,7 +9523,7 @@
         <f>G7*H7+G17*H17</f>
         <v>3828087262.2839999</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9420,7 +9537,7 @@
         <f>G19*H19</f>
         <v>123540874.18699999</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9434,7 +9551,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9448,11 +9565,11 @@
         <f>SUM(D79:D81)</f>
         <v>3951628136.4709997</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9463,15 +9580,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9481,14 +9598,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-2.6632587293329478E-2</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9498,13 +9615,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>11.571251978444732</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9515,24 +9632,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>2.6222027889213448</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>21349231023.503471</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>14.166822180072746</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
@@ -9551,22 +9668,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9653,7 +9770,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9667,7 +9784,7 @@
         <v>29364412234.25</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9723,7 +9840,7 @@
         <f>C25</f>
         <v>-16771264812.015179</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-18093543855</v>
@@ -9778,7 +9895,7 @@
         <f>C4+C5</f>
         <v>12593147422.234821</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>10782753139</v>
@@ -9833,7 +9950,7 @@
         <f>C35</f>
         <v>-2089122563.25</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-2029526709</v>
@@ -9889,7 +10006,7 @@
         <v>10504024858.984821</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9945,7 +10062,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>697421786</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>697421786</v>
@@ -10000,7 +10117,7 @@
         <f>-C4*C78</f>
         <v>-742549850.49555075</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-697421786</v>
@@ -10056,7 +10173,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10112,7 +10229,7 @@
         <f>C50</f>
         <v>120215681.45263389</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>120215681.45263389</v>
@@ -10167,7 +10284,7 @@
         <f>SUM(C8:C12)</f>
         <v>10579112475.941906</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>8873450924.3469982</v>
@@ -10222,7 +10339,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-2656060135.109364</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-2476620792</v>
@@ -10278,7 +10395,7 @@
         <v>-11281261.817791469</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10335,7 +10452,7 @@
         <v>7911771079.0147505</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10392,8 +10509,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10417,8 +10534,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10443,7 +10560,7 @@
         <v>7911771079.0147505</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10539,7 +10656,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10563,7 +10680,7 @@
         <v>-12129601276.881763</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10620,7 +10737,7 @@
         <v>-4641663535.1334143</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10677,7 +10794,7 @@
         <v>-16771264812.015179</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10726,14 +10843,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10745,8 +10862,8 @@
         <v>0.41307148190536791</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10805,8 +10922,8 @@
         <v>0.15807105206483515</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10863,7 +10980,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.57114253397020309</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.62658809260617898</v>
@@ -10911,14 +11028,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10929,8 +11046,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-1863726721.5</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10987,8 +11104,8 @@
         <v>-225395841.75</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11046,7 +11163,7 @@
         <v>-2089122563.25</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11095,14 +11212,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11115,7 +11232,7 @@
         <v>6.3468892434570531E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11173,7 +11290,7 @@
         <v>7.6758165616236402E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11229,7 +11346,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>7.114470899619417E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>7.0283482311520096E-2</v>
@@ -11277,26 +11394,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11375,7 +11492,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11386,7 +11503,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-2955080</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-2955080</v>
@@ -11435,111 +11552,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>123170761.45263389</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>123170761.45263389</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>151697919.76771277</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>128000242.61810873</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>86004563.664204091</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>20711167.472504321</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>15378408.949495818</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>13702426.366621511</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328">
+      <c r="P48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>621439989</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>621439989</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>765369577</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>645806427</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>433923396</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>104495154</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>77589504</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>69133580</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324">
+      <c r="P49" s="320">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11553,7 +11670,7 @@
         <f>C47+C48</f>
         <v>120215681.45263389</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>120215681.45263389</v>
@@ -11601,14 +11718,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11622,8 +11739,8 @@
         <f>G53</f>
         <v>2.8574189558100579E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11649,8 +11766,8 @@
         <f>G54</f>
         <v>7.3628523135533419E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11676,7 +11793,7 @@
         <f>-C8/C47</f>
         <v>3554.5653109170721</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>2962.0945727357634</v>
@@ -11724,14 +11841,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11745,7 +11862,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11800,7 +11917,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11855,7 +11972,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>8812.8943639900008</v>
@@ -11910,7 +12027,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>8812.8943639900008</v>
@@ -11961,11 +12078,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12021,7 +12138,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-228634727</v>
@@ -12069,14 +12186,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12090,7 +12207,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12115,7 +12232,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12140,7 +12257,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12166,7 +12283,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12194,7 +12311,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12216,7 +12333,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12240,7 +12357,7 @@
         <v>0.57114253397020309</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12297,7 +12414,7 @@
         <v>0.42885746602979691</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12354,7 +12471,7 @@
         <v>7.114470899619417E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12411,7 +12528,7 @@
         <v>0.35771275703360272</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12468,7 +12585,7 @@
         <v>2.3750578776664314E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12525,8 +12642,8 @@
         <v>2.5287407238802385E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>442</v>
+      <c r="E78" s="296" t="s">
+        <v>452</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12584,7 +12701,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12641,7 +12758,7 @@
         <v>4.0939243221908249E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12698,7 +12815,7 @@
         <v>0.36026985289365554</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12755,7 +12872,7 @@
         <v>9.0451670338948395E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12808,12 +12925,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>3.841814277703558E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12870,7 +12987,7 @@
         <v>0.26943400112693677</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12922,26 +13039,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12951,7 +13068,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12977,7 +13094,7 @@
         <v>0.26943400112693677</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13026,14 +13143,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13045,7 +13162,7 @@
         <f>G90</f>
         <v>4.6470000000000002</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>4.6470000000000002</v>
@@ -13101,7 +13218,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>7002973236</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>7002973236</v>
@@ -13156,7 +13273,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.88513345065995985</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>1.0947567922099266</v>
@@ -13205,13 +13322,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>6.8028107158541948E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>6.8028107158541948E-2</v>
@@ -13259,7 +13376,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13268,7 +13385,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13292,7 +13409,7 @@
         <v>1.6903664633710624E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13349,7 +13466,7 @@
         <v>0.19222076801201537</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13427,7 +13544,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13442,7 +13559,7 @@
         <v>67345265219.619995</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13499,7 +13616,7 @@
         <v>1530297140.1800001</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13556,7 +13673,7 @@
         <v>19732881051.73</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13613,7 +13730,7 @@
         <v>15652219365.74</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13670,7 +13787,7 @@
         <v>51693045853.879997</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13719,7 +13836,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13728,7 +13845,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13754,7 +13871,7 @@
         <v>5.2114005482973548E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13811,7 +13928,7 @@
         <v>0.67199986481302709</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13868,7 +13985,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13887,63 +14004,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>0.69432864508205805</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.61175156713199319</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.38848325372610293</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.0389375478654403</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>0.53159654216650631</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>0.92036395831447737</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.1160050094303653</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>1.0399444322943818</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.2756477220610554</v>
       </c>
-      <c r="P113" s="334">
+      <c r="P113" s="329">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>1.0878170604353194</v>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13951,58 +14068,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>0.72359452122917711</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>0.66859897667283974</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.41904903922335918</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>2.2007085009366882</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.81791414277282404</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.0932847057074204</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.2877319368842757</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.1595323507076634</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.4069766594758819</v>
       </c>
-      <c r="P114" s="334">
+      <c r="P114" s="329">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>1.2749920037134175</v>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14011,7 +14128,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14067,7 +14184,7 @@
         <f>C81</f>
         <v>0.36026985289365554</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.30729185692302408</v>
@@ -14121,7 +14238,7 @@
         <f>C4/C101</f>
         <v>0.43602786533677701</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.42877991347767891</v>
@@ -14176,7 +14293,7 @@
         <v>1.3027915865121182</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14233,7 +14350,7 @@
         <v>0.20319996017793959</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14329,7 +14446,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14354,7 +14471,7 @@
         <v>5.2500557927566449</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14411,7 +14528,7 @@
         <v>7.6856328396378931E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14460,7 +14577,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15211,13 +15328,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15261,7 +15378,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15271,7 +15388,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15289,10 +15406,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15307,8 +15424,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15323,8 +15440,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15339,8 +15456,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15404,7 +15521,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15414,7 +15531,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15424,7 +15541,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16685,7 +16802,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16738,12 +16855,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16756,19 +16873,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-68.31</v>
       </c>
@@ -16785,19 +16902,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>4.6470000000000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>4.6470000000000002</v>
       </c>
@@ -16811,13 +16928,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>94.964553631447529</v>
       </c>
@@ -16834,15 +16951,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洋河股份(002304.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16859,12 +16976,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16881,37 +16998,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16925,12 +17042,12 @@
         <v>4.4367851108990219E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16943,12 +17060,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.0482342685147259E-2</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16961,8 +17078,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7759904709511951E-2</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16978,7 +17095,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16988,25 +17105,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17016,12 +17133,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -17031,8 +17148,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17052,8 +17169,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17063,8 +17180,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17078,8 +17195,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17089,8 +17206,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17110,8 +17227,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17121,8 +17238,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17136,8 +17253,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17147,8 +17264,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17168,8 +17285,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17179,8 +17296,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17194,8 +17311,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17206,8 +17323,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17269,8 +17386,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17280,8 +17397,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17295,8 +17412,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17306,12 +17423,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17327,8 +17444,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17338,8 +17455,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17353,8 +17470,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17364,8 +17481,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17380,16 +17497,16 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17398,10 +17515,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17413,8 +17530,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17425,8 +17542,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17441,23 +17558,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17465,38 +17582,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>0.15685568984609902</v>
       </c>
@@ -17516,10 +17633,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17540,15 +17657,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17589,7 +17706,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.55381566548045336</v>
       </c>
@@ -17599,14 +17716,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>68.31</v>
       </c>
@@ -17617,9 +17734,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.15993573478625023</v>
       </c>
@@ -17629,15 +17746,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17678,28 +17795,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.31291404887195851</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17711,7 +17828,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17723,23 +17840,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>83.672755702452235</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>7.3571500354297048E-2</v>
       </c>
@@ -17749,15 +17866,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17783,19 +17900,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>75.94741196324874</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>0.15917061295928081</v>
       </c>
@@ -17804,33 +17921,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC73C40-83F7-4021-9EDA-2D6D0B7F24C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A799C35A-BF08-4F12-B68C-00334171A60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,29 +3830,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4312,13 +4312,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>62.055922240421019</v>
+        <v>59.586071941939053</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4458,7 +4458,7 @@
         <v>441</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4514,22 +4514,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4541,13 +4541,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4567,13 +4567,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4602,13 +4602,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4738,22 +4738,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4814,22 +4814,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4873,22 +4873,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4944,13 +4944,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5081,13 +5081,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5126,13 +5126,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5275,13 +5275,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,22 +5294,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>9.7888194444444441</v>
+        <v>9.528212628500361</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>52.267102795976577</v>
+        <v>50.057859313438691</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>62.055922240421019</v>
+        <v>59.586071941939053</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31291404887195851</v>
+        <v>0.34026034202512023</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5642,13 +5642,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5685,13 +5685,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5699,22 +5699,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,17 +5738,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5765,6 +5754,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>9.7888194444444441</v>
+        <v>9.528212628500361</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>52.267102795976577</v>
+        <v>50.057859313438691</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>62.055922240421019</v>
+        <v>59.586071941939053</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17797,7 +17797,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.31291404887195851</v>
+        <v>0.34026034202512023</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A799C35A-BF08-4F12-B68C-00334171A60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCD2CE9-985D-448D-A93D-033CB8A7B960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3111,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3745,7 +3745,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3809,9 +3808,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3830,29 +3826,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4160,7 +4166,7 @@
         <v>45780</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4194,7 +4200,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>446</v>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       <c r="D22" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>443</v>
       </c>
     </row>
@@ -4378,7 +4384,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4388,14 +4394,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>90.317553631447524</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.15993573478625023</v>
       </c>
@@ -4408,18 +4414,18 @@
       <c r="B28" s="45" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>002304.SZ (CNY)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>433</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4427,18 +4433,18 @@
       <c r="B29" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>40.298277562480884</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>428</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4446,18 +4452,18 @@
       <c r="B30" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>59.586071941939053</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4465,18 +4471,18 @@
       <c r="B31" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>83.672755702452235</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4484,18 +4490,18 @@
       <c r="B32" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>75.94741196324874</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>442</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4523,13 +4529,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4636,7 +4642,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>123170761.45263389</v>
       </c>
@@ -4644,14 +4650,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-2955080</v>
       </c>
@@ -4659,8 +4665,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4719,10 +4725,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4823,13 +4829,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4867,7 +4873,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4979,28 +4985,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>0.30279158651211824</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>7.7640983998987034E-4</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>3.8209153156820415E-3</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5275,13 +5281,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,13 +5300,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5364,7 +5370,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5397,7 +5403,7 @@
         <f>Scenarios!C83</f>
         <v>40.298277562480884</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5406,11 +5412,11 @@
       <c r="B145" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5433,7 +5439,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5466,7 +5472,7 @@
         <f>Scenarios!C93</f>
         <v>59.586071941939053</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5475,11 +5481,11 @@
       <c r="B153" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5535,7 +5541,7 @@
         <f>Scenarios!C99</f>
         <v>83.672755702452235</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5544,11 +5550,11 @@
       <c r="B161" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5604,7 +5610,7 @@
         <f>Scenarios!C105</f>
         <v>75.94741196324874</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5613,11 +5619,11 @@
       <c r="B169" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5656,13 +5662,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5699,22 +5705,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,6 +5744,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5754,17 +5771,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8225,11 +8231,11 @@
         <f t="shared" si="40"/>
         <v>675347400</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8259,11 +8265,11 @@
         <f t="shared" si="40"/>
         <v>14433244696</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9488,7 +9494,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
@@ -11559,104 +11565,104 @@
         <v>123170761.45263389</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>123170761.45263389</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>151697919.76771277</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>128000242.61810873</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>86004563.664204091</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>20711167.472504321</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>15378408.949495818</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>13702426.366621511</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324">
+      <c r="P48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>621439989</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>621439989</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>765369577</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>645806427</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>433923396</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>104495154</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>77589504</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>69133580</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320">
+      <c r="P49" s="319">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -14020,47 +14026,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>0.69432864508205805</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.61175156713199319</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.38848325372610293</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.0389375478654403</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>0.53159654216650631</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>0.92036395831447737</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.1160050094303653</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>1.0399444322943818</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.2756477220610554</v>
       </c>
-      <c r="P113" s="329">
+      <c r="P113" s="328">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>1.0878170604353194</v>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14072,47 +14078,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>0.72359452122917711</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>0.66859897667283974</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.41904903922335918</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>2.2007085009366882</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.81791414277282404</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.0932847057074204</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.2877319368842757</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.1595323507076634</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.4069766594758819</v>
       </c>
-      <c r="P114" s="329">
+      <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>1.2749920037134175</v>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15406,10 +15412,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15424,8 +15430,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15440,8 +15446,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15456,8 +15462,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16951,11 +16957,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洋河股份(002304.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16976,8 +16982,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16998,8 +17004,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -17009,8 +17015,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -17023,8 +17029,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -17042,8 +17048,8 @@
         <v>4.4367851108990219E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -17060,8 +17066,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.0482342685147259E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -17078,8 +17084,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7759904709511951E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17105,21 +17111,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17133,8 +17139,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17148,8 +17154,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17169,8 +17175,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17180,8 +17186,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17195,8 +17201,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17206,8 +17212,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17227,8 +17233,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17238,8 +17244,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17253,8 +17259,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17264,8 +17270,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17285,8 +17291,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17296,8 +17302,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17311,8 +17317,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17323,8 +17329,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17386,8 +17392,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17397,8 +17403,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17412,8 +17418,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17423,8 +17429,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17444,8 +17450,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17455,8 +17461,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17470,8 +17476,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17481,8 +17487,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17499,7 +17505,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17613,7 +17619,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>0.15685568984609902</v>
       </c>
@@ -17706,7 +17712,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.55381566548045336</v>
       </c>
@@ -17795,7 +17801,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.34026034202512023</v>
       </c>
@@ -17805,7 +17811,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17816,7 +17822,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17828,7 +17834,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17840,7 +17846,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17856,7 +17862,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>7.3571500354297048E-2</v>
       </c>
@@ -17912,7 +17918,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.15917061295928081</v>
       </c>
@@ -17921,32 +17927,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCD2CE9-985D-448D-A93D-033CB8A7B960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A0E447-D49A-414E-9C84-EB5158100B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4909,7 +4909,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>65.625697409458056</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4963,7 +4963,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>40134989.460000001</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5034,7 +5034,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>17437737876.49247</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5065,7 +5065,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>3951628136.4709997</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5100,7 +5100,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>79.792519589530784</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5159,111 +5159,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.1</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>128.41 CNY</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.06</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>93.83 CNY</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.04</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>88.69 CNY</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.02</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>84.03 CNY</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>79.79 CNY</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-40134989.460000001</v>
       </c>
       <c r="D86" s="248">
@@ -9614,7 +9614,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>17437737876.49247</v>
       </c>
       <c r="D87" s="248">
@@ -9631,7 +9631,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>3951628136.4709997</v>
       </c>
       <c r="D88" s="248">
@@ -15591,7 +15591,7 @@
         <v>8280260795.5317278</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15613,7 +15613,7 @@
         <v>8665912873.0198059</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15635,7 +15635,7 @@
         <v>9069526646.2253819</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15657,7 +15657,7 @@
         <v>9491938678.8074646</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15679,7 +15679,7 @@
         <v>9934024497.269474</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15701,7 +15701,7 @@
         <v>10396700405.648687</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15723,7 +15723,7 @@
         <v>10880925384.724613</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15745,7 +15745,7 @@
         <v>11387703079.682753</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15767,7 +15767,7 @@
         <v>11918083880.353537</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15789,7 +15789,7 @@
         <v>12473167098.33814</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15811,7 +15811,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15833,7 +15833,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15855,7 +15855,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15877,7 +15877,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15899,7 +15899,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15921,7 +15921,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15943,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15965,7 +15965,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15987,7 +15987,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -16009,7 +16009,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -16031,7 +16031,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -16053,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -16075,7 +16075,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -16097,7 +16097,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16119,7 +16119,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16141,7 +16141,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16163,7 +16163,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16185,7 +16185,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16207,7 +16207,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16229,7 +16229,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16930,7 +16930,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17147,7 +17147,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>79.792519589530784</v>
       </c>
       <c r="D22" t="str">
@@ -17194,7 +17194,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>88.69077611437983</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17252,7 +17252,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>84.029326469312352</v>
       </c>
       <c r="D33" t="str">
@@ -17310,7 +17310,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>93.827688958625345</v>
       </c>
       <c r="D39" t="str">
@@ -17411,7 +17411,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>79.79251958953077</v>
       </c>
       <c r="D51" t="str">
@@ -17469,7 +17469,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>128.41291546354199</v>
       </c>
       <c r="D57" t="str">
@@ -17557,7 +17557,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>90.324402469499802</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A0E447-D49A-414E-9C84-EB5158100B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB9FD4F-75DD-46E2-A565-F0D76D488FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB9FD4F-75DD-46E2-A565-F0D76D488FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7976D7D1-22C0-4306-9038-3659638D9ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2410,25 +2405,55 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>洋河股份</t>
+  </si>
+  <si>
+    <t>002304.SZ</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_03</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>洋河股份</t>
-  </si>
-  <si>
-    <t>002304.SZ</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CNS_03</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2444,7 +2469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2463,6 +2488,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3111,7 +3137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3617,9 +3643,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3836,29 +3859,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3877,7 +3907,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3924,8 +3968,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4166,15 +4210,15 @@
         <v>45780</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>445</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4189,7 +4233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4198,10 +4242,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>446</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,9 +4259,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4238,20 +4282,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4267,17 +4311,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4291,7 +4335,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4318,73 +4362,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>449</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>443</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>445</v>
+        <v>436</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>445</v>
+        <v>437</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4394,14 +4442,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>90.317553631447524</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.15993573478625023</v>
       </c>
@@ -4412,96 +4460,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>437</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>435</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>002304.SZ (CNY)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>433</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>431</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C29" s="345">
+        <v>427</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>40.298277562480884</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>428</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C30" s="346">
+        <v>428</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>59.586071941939053</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C31" s="346">
+        <v>429</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>83.672755702452235</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C32" s="346">
+        <v>430</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>75.94741196324874</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>442</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4510,8 +4558,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4520,22 +4568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4547,13 +4595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4573,13 +4621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4608,13 +4656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4630,19 +4678,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>123170761.45263389</v>
       </c>
@@ -4650,14 +4698,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-2955080</v>
       </c>
@@ -4665,8 +4713,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4700,13 +4748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4722,13 +4770,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4744,22 +4792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4788,26 +4836,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>7.6856328396378931E-2</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>6.8028107158541948E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.88513345065995985</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4820,22 +4876,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4844,7 +4900,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4853,7 +4909,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4864,7 +4920,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4873,42 +4929,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>65.625697409458056</v>
       </c>
@@ -4918,8 +4974,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4931,13 +4987,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4950,13 +5006,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4973,9 +5029,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.6632587293329478E-2</v>
       </c>
@@ -4985,28 +5041,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>0.30279158651211824</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>7.7640983998987034E-4</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>3.8209153156820415E-3</v>
       </c>
@@ -5044,9 +5100,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>11.571251978444732</v>
       </c>
@@ -5075,9 +5131,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>2.6222027889213448</v>
       </c>
@@ -5087,20 +5143,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>451</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>79.792519589530784</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5109,10 +5165,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>15.284602440692964</v>
       </c>
@@ -5122,8 +5178,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5132,49 +5188,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>128.41 CNY</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5192,11 +5248,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>93.83 CNY</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5214,11 +5270,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>88.69 CNY</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5236,11 +5292,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>84.03 CNY</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5258,11 +5314,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>79.79 CNY</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5300,22 +5356,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5326,7 +5382,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5335,7 +5391,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5355,22 +5411,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>002304.SZ</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5403,20 +5459,20 @@
         <f>Scenarios!C83</f>
         <v>40.298277562480884</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5432,14 +5488,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5472,20 +5528,20 @@
         <f>Scenarios!C93</f>
         <v>59.586071941939053</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5501,12 +5557,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5535,26 +5591,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>83.672755702452235</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5570,12 +5626,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5604,26 +5660,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>75.94741196324874</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5638,8 +5694,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5648,113 +5704,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5771,6 +5816,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5783,7 +5839,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6347,7 +6403,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>4628711237</v>
@@ -6383,7 +6439,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-1302245456</v>
@@ -6419,7 +6475,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-7049805121</v>
@@ -6478,7 +6534,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7783,7 +7839,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8231,11 +8287,11 @@
         <f t="shared" si="40"/>
         <v>675347400</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8265,11 +8321,11 @@
         <f t="shared" si="40"/>
         <v>14433244696</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8372,17 +8428,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8467,7 +8523,7 @@
         <f>413398699+8994904.73+1090851688.67+17051847.78</f>
         <v>1530297140.1800001</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8477,7 +8533,7 @@
       <c r="G4" s="19">
         <v>21748297978.369999</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8488,7 +8544,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8498,7 +8554,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8509,7 +8565,7 @@
       <c r="C6" s="19">
         <v>19732881051.73</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8519,7 +8575,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8530,7 +8586,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8540,7 +8596,7 @@
       <c r="G7" s="19">
         <v>6380145437.1400003</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8551,7 +8607,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8561,7 +8617,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8572,7 +8628,7 @@
       <c r="C9" s="19">
         <v>23310180.68</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8582,7 +8638,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8593,10 +8649,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8605,10 +8661,10 @@
       <c r="C11" s="19">
         <v>909932715.44000006</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8666,7 +8722,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8675,7 +8731,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8686,7 +8742,7 @@
       <c r="C16" s="19">
         <v>4614148799.21</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8695,7 +8751,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8706,7 +8762,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8715,7 +8771,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8726,7 +8782,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8735,7 +8791,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8747,7 +8803,7 @@
         <f>5571618070.98+1912601220.28+66814914.62</f>
         <v>7551034205.8799992</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8756,7 +8812,7 @@
       <c r="G19" s="19">
         <v>1235408741.8699999</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8767,7 +8823,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8776,7 +8832,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8787,7 +8843,7 @@
       <c r="C21" s="19">
         <v>1804220059.96</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8796,7 +8852,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8808,10 +8864,10 @@
         <f>1242507668.92+180606719.81</f>
         <v>1423114388.73</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8821,10 +8877,10 @@
         <f>276001989.95+116472530.48</f>
         <v>392474520.43000001</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9157,13 +9213,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9179,7 +9235,7 @@
         <f>H29</f>
         <v>23033712462.895008</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9194,23 +9250,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>15.284602440692964</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9224,7 +9280,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>4.5851652280403769E-3</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9235,22 +9291,22 @@
         <f>G29/G32</f>
         <v>0.76602628203208212</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9264,7 +9320,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.23046078921961435</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9278,22 +9334,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>3.0012732378422159E-7</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9315,22 +9371,22 @@
         <f>G39/G32</f>
         <v>0.1121242032569815</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9344,7 +9400,7 @@
         <f>G28/G29</f>
         <v>2.0315234416617856E-3</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9363,13 +9419,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9397,7 +9453,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9407,7 +9463,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9417,7 +9473,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9427,26 +9483,26 @@
         <f>SUM(C66:C69)</f>
         <v>21748297978.369999</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9457,65 +9513,65 @@
         <v>-2155280050.938765</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>9.6209966209831155</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>10.090706295405646</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>4310560101.8775301</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9529,7 +9585,7 @@
         <f>G7*H7+G17*H17</f>
         <v>3828087262.2839999</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9543,7 +9599,7 @@
         <f>G19*H19</f>
         <v>123540874.18699999</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9557,7 +9613,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9571,11 +9627,11 @@
         <f>SUM(D79:D81)</f>
         <v>3951628136.4709997</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9586,76 +9642,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-40134989.460000001</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-2.6632587293329478E-2</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>17437737876.49247</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>11.571251978444732</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>3951628136.4709997</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>2.6222027889213448</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>21349231023.503471</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>14.166822180072746</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
@@ -9776,7 +9832,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9790,7 +9846,7 @@
         <v>29364412234.25</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9846,7 +9902,7 @@
         <f>C25</f>
         <v>-16771264812.015179</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-18093543855</v>
@@ -9901,7 +9957,7 @@
         <f>C4+C5</f>
         <v>12593147422.234821</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>10782753139</v>
@@ -9956,7 +10012,7 @@
         <f>C35</f>
         <v>-2089122563.25</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-2029526709</v>
@@ -10012,7 +10068,7 @@
         <v>10504024858.984821</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -10068,7 +10124,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>697421786</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>697421786</v>
@@ -10123,7 +10179,7 @@
         <f>-C4*C78</f>
         <v>-742549850.49555075</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-697421786</v>
@@ -10179,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10235,7 +10291,7 @@
         <f>C50</f>
         <v>120215681.45263389</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>120215681.45263389</v>
@@ -10290,7 +10346,7 @@
         <f>SUM(C8:C12)</f>
         <v>10579112475.941906</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>8873450924.3469982</v>
@@ -10345,7 +10401,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-2656060135.109364</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-2476620792</v>
@@ -10401,7 +10457,7 @@
         <v>-11281261.817791469</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10458,7 +10514,7 @@
         <v>7911771079.0147505</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10515,8 +10571,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10540,8 +10596,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10566,7 +10622,7 @@
         <v>7911771079.0147505</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10662,7 +10718,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10686,7 +10742,7 @@
         <v>-12129601276.881763</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10743,7 +10799,7 @@
         <v>-4641663535.1334143</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10800,7 +10856,7 @@
         <v>-16771264812.015179</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10849,14 +10905,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10868,8 +10924,8 @@
         <v>0.41307148190536791</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10928,8 +10984,8 @@
         <v>0.15807105206483515</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10986,7 +11042,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.57114253397020309</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.62658809260617898</v>
@@ -11034,14 +11090,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -11052,8 +11108,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-1863726721.5</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11110,8 +11166,8 @@
         <v>-225395841.75</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11169,7 +11225,7 @@
         <v>-2089122563.25</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11218,14 +11274,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11238,7 +11294,7 @@
         <v>6.3468892434570531E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11296,7 +11352,7 @@
         <v>7.6758165616236402E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11352,7 +11408,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>7.114470899619417E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>7.0283482311520096E-2</v>
@@ -11400,26 +11456,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11498,7 +11554,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11509,7 +11565,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-2955080</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-2955080</v>
@@ -11558,111 +11614,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>123170761.45263389</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>123170761.45263389</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>151697919.76771277</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>128000242.61810873</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>86004563.664204091</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>20711167.472504321</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>15378408.949495818</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>13702426.366621511</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323">
+      <c r="P48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>621439989</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>621439989</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>765369577</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>645806427</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>433923396</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>104495154</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>77589504</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>69133580</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319">
+      <c r="P49" s="318">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11676,7 +11732,7 @@
         <f>C47+C48</f>
         <v>120215681.45263389</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>120215681.45263389</v>
@@ -11724,14 +11780,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11745,8 +11801,8 @@
         <f>G53</f>
         <v>2.8574189558100579E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11772,8 +11828,8 @@
         <f>G54</f>
         <v>7.3628523135533419E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11799,7 +11855,7 @@
         <f>-C8/C47</f>
         <v>3554.5653109170721</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>2962.0945727357634</v>
@@ -11847,14 +11903,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11868,7 +11924,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11923,7 +11979,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11978,7 +12034,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>8812.8943639900008</v>
@@ -12033,7 +12089,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>8812.8943639900008</v>
@@ -12084,11 +12140,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12144,7 +12200,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-228634727</v>
@@ -12192,14 +12248,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12213,7 +12269,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12238,7 +12294,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12263,7 +12319,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12289,7 +12345,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12317,7 +12373,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12339,7 +12395,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12363,7 +12419,7 @@
         <v>0.57114253397020309</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12420,7 +12476,7 @@
         <v>0.42885746602979691</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12477,7 +12533,7 @@
         <v>7.114470899619417E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12534,7 +12590,7 @@
         <v>0.35771275703360272</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12591,7 +12647,7 @@
         <v>2.3750578776664314E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12648,8 +12704,8 @@
         <v>2.5287407238802385E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>452</v>
+      <c r="E78" s="295" t="s">
+        <v>460</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12707,7 +12763,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12764,7 +12820,7 @@
         <v>4.0939243221908249E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12821,7 +12877,7 @@
         <v>0.36026985289365554</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12878,7 +12934,7 @@
         <v>9.0451670338948395E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12931,12 +12987,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>3.841814277703558E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12993,7 +13049,7 @@
         <v>0.26943400112693677</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -13045,26 +13101,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -13074,7 +13130,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13100,7 +13156,7 @@
         <v>0.26943400112693677</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13149,14 +13205,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13168,7 +13224,7 @@
         <f>G90</f>
         <v>4.6470000000000002</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>4.6470000000000002</v>
@@ -13224,7 +13280,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>7002973236</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>7002973236</v>
@@ -13279,7 +13335,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.88513345065995985</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>1.0947567922099266</v>
@@ -13328,13 +13384,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>6.8028107158541948E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>6.8028107158541948E-2</v>
@@ -13382,7 +13438,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13391,7 +13447,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13415,7 +13471,7 @@
         <v>1.6903664633710624E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13472,7 +13528,7 @@
         <v>0.19222076801201537</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13550,7 +13606,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13565,7 +13621,7 @@
         <v>67345265219.619995</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13622,7 +13678,7 @@
         <v>1530297140.1800001</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13679,7 +13735,7 @@
         <v>19732881051.73</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13736,7 +13792,7 @@
         <v>15652219365.74</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13793,7 +13849,7 @@
         <v>51693045853.879997</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13842,7 +13898,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13851,7 +13907,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13877,7 +13933,7 @@
         <v>5.2114005482973548E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13934,7 +13990,7 @@
         <v>0.67199986481302709</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13991,7 +14047,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -14010,63 +14066,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>0.69432864508205805</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>0.61175156713199319</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.38848325372610293</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.0389375478654403</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>0.53159654216650631</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>0.92036395831447737</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.1160050094303653</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>1.0399444322943818</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.2756477220610554</v>
       </c>
-      <c r="P113" s="328">
+      <c r="P113" s="327">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>1.0878170604353194</v>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14074,58 +14130,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>0.72359452122917711</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>0.66859897667283974</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.41904903922335918</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>2.2007085009366882</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.81791414277282404</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.0932847057074204</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.2877319368842757</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.1595323507076634</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.4069766594758819</v>
       </c>
-      <c r="P114" s="328">
+      <c r="P114" s="327">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>1.2749920037134175</v>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14134,7 +14190,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14190,7 +14246,7 @@
         <f>C81</f>
         <v>0.36026985289365554</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.30729185692302408</v>
@@ -14244,7 +14300,7 @@
         <f>C4/C101</f>
         <v>0.43602786533677701</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.42877991347767891</v>
@@ -14299,7 +14355,7 @@
         <v>1.3027915865121182</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14356,7 +14412,7 @@
         <v>0.20319996017793959</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14452,7 +14508,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14477,7 +14533,7 @@
         <v>5.2500557927566449</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14534,7 +14590,7 @@
         <v>7.6856328396378931E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14583,7 +14639,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15316,7 +15372,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15384,7 +15440,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15394,7 +15450,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15412,10 +15468,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15430,8 +15486,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15446,8 +15502,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15462,8 +15518,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16808,7 +16864,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16839,12 +16895,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16859,6 +16915,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>442</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>7002973236</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>87537165450</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>58.087499999999999</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>67.40962183549351</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>447</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>7329135810.3133821</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>6786236861.4012794</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>7670489364.4145861</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>6576208302.8245764</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>8027741416.2259245</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>6372679958.773056</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>8401632436.2255907</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>6175450652.8488035</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>8792937382.2087021</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>5984325434.9011974</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>9202467305.5296268</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>5799115388.3295727</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>9631071032.1548481</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>5619637443.34972</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>10079636922.010645</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>5445714196.0396194</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>10549094710.272169</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>5277173732.9855909</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>11040417434.410316</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>5113849461.3554754</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>91614197628.917282</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>42435099757.817802</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>101585491190.62669</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>101585491190.62669</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.02</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.04</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>87537165449.999985</v>
+      </c>
+      <c r="C51" s="124">
+        <v>90361572641.00206</v>
+      </c>
+      <c r="D51" s="124">
+        <v>93270569594.852798</v>
+      </c>
+      <c r="E51" s="124">
+        <v>96267868383.610886</v>
+      </c>
+      <c r="F51" s="124">
+        <v>102542796262.25502</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>87537165449.999969</v>
+      </c>
+      <c r="C52" s="124">
+        <v>93188580664.700378</v>
+      </c>
+      <c r="D52" s="124">
+        <v>99406420701.830536</v>
+      </c>
+      <c r="E52" s="124">
+        <v>106258474200.68056</v>
+      </c>
+      <c r="F52" s="124">
+        <v>122175022447.76418</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>87537165449.999969</v>
+      </c>
+      <c r="C53" s="124">
+        <v>96687786949.899811</v>
+      </c>
+      <c r="D53" s="124">
+        <v>107405280738.59561</v>
+      </c>
+      <c r="E53" s="124">
+        <v>120000937951.04907</v>
+      </c>
+      <c r="F53" s="124">
+        <v>152391205953.56683</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>87537165449.999969</v>
+      </c>
+      <c r="C54" s="124">
+        <v>100252916995.4017</v>
+      </c>
+      <c r="D54" s="124">
+        <v>116014662205.92873</v>
+      </c>
+      <c r="E54" s="124">
+        <v>135677353695.47769</v>
+      </c>
+      <c r="F54" s="124">
+        <v>191430165980.25726</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>87537165449.999969</v>
+      </c>
+      <c r="C55" s="124">
+        <v>103568685766.819</v>
+      </c>
+      <c r="D55" s="124">
+        <v>124495195836.22354</v>
+      </c>
+      <c r="E55" s="124">
+        <v>152105760755.81912</v>
+      </c>
+      <c r="F55" s="124">
+        <v>238248885068.27466</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>87537165449.999969</v>
+      </c>
+      <c r="C56" s="124">
+        <v>106493655073.76625</v>
+      </c>
+      <c r="D56" s="124">
+        <v>132437290737.38911</v>
+      </c>
+      <c r="E56" s="124">
+        <v>168532080087.19437</v>
+      </c>
+      <c r="F56" s="124">
+        <v>292308067859.06183</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0.02</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.04</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.06</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.1</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>58.087499999999999</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>58.087499999999999</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>58.087499999999999</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>58.087499999999999</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>58.087499999999999</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>58.087499999999991</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>59.961706822484359</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>61.892045321431091</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>63.880978736135184</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>68.044865826572618</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>58.087499999999977</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>61.837639493280889</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>65.963644502697122</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>70.510497894263622</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>81.072326022346672</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>58.087499999999977</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>64.159626320780134</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>71.271490375899219</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>79.62965727069431</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>101.12303877241679</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>58.087499999999977</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>66.52535852667819</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>76.984463184795587</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>90.03213940355046</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>127.02832801605405</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>58.087499999999977</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>68.725620752666245</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>82.611935752788696</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>100.9336243923768</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>158.09607313945079</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>58.087499999999977</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>70.66655811046023</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>87.882113684640558</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>111.83372401584775</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>193.96841106834415</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.1</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>101.12303877241679</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.06</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>70.510497894263622</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.04</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>65.963644502697122</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0.02</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>61.837639493280889</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>58.087499999999977</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16879,19 +18386,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-68.31</v>
       </c>
@@ -16908,19 +18415,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>4.6470000000000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>4.6470000000000002</v>
       </c>
@@ -16934,13 +18441,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>94.964553631447529</v>
       </c>
@@ -16957,15 +18464,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洋河股份(002304.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16982,12 +18489,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17004,37 +18511,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>449</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17048,12 +18555,12 @@
         <v>4.4367851108990219E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17066,12 +18573,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.0482342685147259E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17084,8 +18591,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7759904709511951E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17101,7 +18608,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17111,25 +18618,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17139,23 +18646,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>79.792519589530784</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17175,8 +18682,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17186,23 +18693,23 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>88.69077611437983</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17212,8 +18719,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17233,8 +18740,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17244,23 +18751,23 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>84.029326469312352</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17270,8 +18777,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17291,8 +18798,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17302,23 +18809,23 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>93.827688958625345</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17329,8 +18836,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17392,8 +18899,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17403,23 +18910,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>79.79251958953077</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17429,12 +18936,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17450,8 +18957,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17461,23 +18968,23 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>128.41291546354199</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17487,8 +18994,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17503,16 +19010,16 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17521,10 +19028,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17536,8 +19043,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17548,8 +19055,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17557,30 +19064,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>90.324402469499802</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17588,38 +19095,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>0.15685568984609902</v>
       </c>
@@ -17639,10 +19146,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17663,12 +19170,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17712,7 +19219,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.55381566548045336</v>
       </c>
@@ -17722,14 +19229,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>68.31</v>
       </c>
@@ -17740,9 +19247,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.15993573478625023</v>
       </c>
@@ -17752,12 +19259,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17801,28 +19308,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.34026034202512023</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17834,7 +19341,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17846,23 +19353,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>83.672755702452235</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>7.3571500354297048E-2</v>
       </c>
@@ -17872,12 +19379,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17906,19 +19413,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>75.94741196324874</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.15917061295928081</v>
       </c>
@@ -17927,33 +19434,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF69A8E7-3755-6640-A554-5CC2E56D38D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67ED7278-71B0-C840-834F-D17DB0E8F973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2600" yWindow="5220" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3874,6 +3874,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3909,9 +3912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4220,7 +4220,7 @@
       <c r="C1" s="44">
         <v>45780</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>461</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4375,13 +4375,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>40.298277562480884</v>
+        <v>49.548968425784025</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,7 +4506,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>59.586071941939053</v>
+        <v>67.080596886647925</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4525,7 +4525,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="342">
-        <v>0.21740000000000001</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.15">
@@ -4581,22 +4581,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4608,13 +4608,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4634,13 +4634,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4669,13 +4669,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4691,13 +4691,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4783,13 +4783,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4805,22 +4805,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4889,22 +4889,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4948,22 +4948,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -5000,13 +5000,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5019,13 +5019,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5156,13 +5156,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5201,13 +5201,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5350,13 +5350,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5369,22 +5369,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>7.3837172011661796</v>
+        <v>8.4394765589440173</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>32.914560361314706</v>
+        <v>41.10949186684001</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>40.298277562480884</v>
+        <v>49.548968425784025</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55381566548045336</v>
+        <v>0.45139160181447113</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.15">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.21740000000000001</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.15">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>9.528212628500361</v>
+        <v>10.311354456764589</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.15">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>50.057859313438691</v>
+        <v>56.769242429883334</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.15">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>59.586071941939053</v>
+        <v>67.080596886647925</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34026034202512023</v>
+        <v>0.25728062608538993</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.15">
@@ -5717,13 +5717,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5731,13 +5731,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5760,13 +5760,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15481,10 +15481,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15499,8 +15499,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15515,8 +15515,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15531,8 +15531,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -17011,8 +17011,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18477,11 +18477,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洋河股份(002304.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18502,8 +18502,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18524,8 +18524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18535,8 +18535,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18549,8 +18549,8 @@
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18568,8 +18568,8 @@
         <v>4.4367851108990219E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18586,8 +18586,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.0482342685147259E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18604,8 +18604,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7759904709511951E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18631,21 +18631,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18659,8 +18659,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18674,8 +18674,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18695,8 +18695,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18706,8 +18706,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18721,8 +18721,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18732,8 +18732,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18753,8 +18753,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18764,8 +18764,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18779,8 +18779,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18790,8 +18790,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18811,8 +18811,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18822,8 +18822,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18837,8 +18837,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18849,8 +18849,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18912,8 +18912,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18923,8 +18923,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18938,8 +18938,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18949,8 +18949,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18970,8 +18970,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18981,8 +18981,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18996,8 +18996,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -19007,8 +19007,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.15">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>7.3837172011661796</v>
+        <v>8.4394765589440173</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>32.914560361314706</v>
+        <v>41.10949186684001</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>40.298277562480884</v>
+        <v>49.548968425784025</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.55381566548045336</v>
+        <v>0.45139160181447113</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.15">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.21740000000000001</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.15">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>9.528212628500361</v>
+        <v>10.311354456764589</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>50.057859313438691</v>
+        <v>56.769242429883334</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>59.586071941939053</v>
+        <v>67.080596886647925</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.34026034202512023</v>
+        <v>0.25728062608538993</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.15">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67ED7278-71B0-C840-834F-D17DB0E8F973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600AE558-FF75-4A8F-9EFC-91191836EADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="5220" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2491,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3915,7 +3904,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4204,7 +4193,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4213,7 +4202,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4230,7 +4219,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4244,7 +4233,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>417</v>
       </c>
@@ -4253,7 +4242,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4261,7 +4250,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4270,7 +4259,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4280,7 +4269,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4290,17 +4279,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>419</v>
       </c>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4322,7 +4311,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>418</v>
       </c>
@@ -4332,7 +4321,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>422</v>
       </c>
@@ -4346,7 +4335,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>421</v>
       </c>
@@ -4360,7 +4349,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4370,11 +4359,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4383,14 +4372,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4405,7 +4394,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4418,7 +4407,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>436</v>
       </c>
@@ -4426,7 +4415,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>437</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4450,28 +4439,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>90.317553631447524</v>
+        <v>114.36041665330859</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15993573478625023</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.24557216589977915</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>435</v>
       </c>
@@ -4490,13 +4479,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>49.548968425784025</v>
+        <v>69.666696764969942</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,16 +4495,16 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>67.080596886647925</v>
+        <v>88.645807274031327</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4525,16 +4514,16 @@
         <v>439</v>
       </c>
       <c r="F30" s="342">
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>83.672755702452235</v>
+        <v>108.44069756687449</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4544,16 +4533,16 @@
         <v>438</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>75.94741196324874</v>
+        <v>100.86650294928437</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4563,14 +4552,14 @@
         <v>440</v>
       </c>
       <c r="F32" s="342">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4580,7 +4569,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4589,7 +4578,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4598,7 +4587,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4607,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4616,7 +4605,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4629,11 +4618,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4642,7 +4631,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4655,7 +4644,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4668,7 +4657,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4677,7 +4666,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4690,7 +4679,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4699,7 +4688,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4714,7 +4703,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4729,7 +4718,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4742,12 +4731,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4760,7 +4749,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4769,7 +4758,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4782,7 +4771,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4791,7 +4780,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4804,7 +4793,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4813,7 +4802,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4822,7 +4811,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4835,7 +4824,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4848,7 +4837,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4858,7 +4847,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4874,7 +4863,7 @@
         <v>0.88513345065995985</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4884,10 +4873,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4897,7 +4886,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4906,21 +4895,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>432</v>
       </c>
@@ -4929,25 +4918,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4956,7 +4945,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4965,7 +4954,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4973,20 +4962,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>65.625697409458056</v>
+        <v>87.500929879277408</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4996,10 +4985,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5008,17 +4997,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5027,7 +5016,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5040,7 +5029,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5053,7 +5042,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5062,7 +5051,7 @@
         <v>0.30279158651211824</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5071,7 +5060,7 @@
         <v>7.7640983998987034E-4</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5080,12 +5069,12 @@
         <v>3.8209153156820415E-3</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5098,7 +5087,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5111,7 +5100,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5124,12 +5113,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5142,7 +5131,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5155,7 +5144,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5164,20 +5153,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>451</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5190,7 +5179,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5200,7 +5189,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5209,7 +5198,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5226,7 +5215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5241,14 +5230,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>128.41 CNY</v>
+        <v>161.6 CNY</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5263,14 +5252,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>93.83 CNY</v>
+        <v>118.46 CNY</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5285,14 +5274,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>88.69 CNY</v>
+        <v>112.33 CNY</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5307,14 +5296,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>84.03 CNY</v>
+        <v>106.75 CNY</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5329,27 +5318,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>79.79 CNY</v>
+        <v>101.67 CNY</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>90.317553631447524</v>
+        <v>114.36041665330859</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5358,7 +5347,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5368,7 +5357,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5377,7 +5366,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5386,12 +5375,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5400,16 +5389,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5422,7 +5411,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5435,49 +5424,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>8.4394765589440173</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>9.248657083863371</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>41.10949186684001</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>60.418039681106563</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>49.548968425784025</v>
+        <v>69.666696764969942</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>418</v>
       </c>
@@ -5490,63 +5479,63 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.45139160181447113</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.39081459473718705</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>10.311354456764589</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+        <v>10.843167062410641</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>56.769242429883334</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>77.802640211620684</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>67.080596886647925</v>
+        <v>88.645807274031327</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>418</v>
       </c>
@@ -5559,63 +5548,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.25728062608538993</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.22485585600158187</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>11.9757696997409</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>12.421486529148241</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>71.696986002711341</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>96.019211037726251</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>83.672755702452235</v>
+        <v>108.44069756687449</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>418</v>
       </c>
@@ -5628,63 +5617,63 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>7.3571500354297048E-2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>5.1763706881028049E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>11.211366726236903</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+        <v>11.826104101614131</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>64.736045237011837</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>89.040398847670232</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>75.94741196324874</v>
+        <v>100.86650294928437</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>418</v>
       </c>
@@ -5697,16 +5686,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15917061295928081</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.11738532019602332</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5716,7 +5705,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5725,12 +5714,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5739,27 +5728,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5768,12 +5757,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5782,7 +5771,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5791,22 +5780,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5867,15 +5856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5924,7 +5913,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5940,7 +5929,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5948,7 +5937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5984,7 +5973,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6020,7 +6009,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6056,7 +6045,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6092,7 +6081,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6122,7 +6111,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6138,7 +6127,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6154,7 +6143,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6178,7 +6167,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6208,7 +6197,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6238,7 +6227,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6274,7 +6263,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6310,7 +6299,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6346,13 +6335,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6382,7 +6371,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6398,7 +6387,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6414,7 +6403,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6450,7 +6439,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6486,7 +6475,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6522,7 +6511,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6542,7 +6531,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6550,7 +6539,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6587,7 +6576,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6624,7 +6613,7 @@
       </c>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6661,7 +6650,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6698,7 +6687,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6735,7 +6724,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6751,12 +6740,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6805,7 +6794,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6854,7 +6843,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6903,7 +6892,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6952,7 +6941,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7001,7 +6990,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7050,7 +7039,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7099,7 +7088,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7148,7 +7137,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7197,7 +7186,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7246,7 +7235,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7295,7 +7284,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7344,7 +7333,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7393,12 +7382,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7447,7 +7436,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7496,12 +7485,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7550,7 +7539,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7599,7 +7588,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7648,7 +7637,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7697,13 +7686,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7752,7 +7741,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7801,7 +7790,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7850,7 +7839,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7899,7 +7888,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7948,12 +7937,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8003,7 +7992,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8052,7 +8041,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8102,7 +8091,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8151,7 +8140,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8201,7 +8190,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8217,13 +8206,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8272,7 +8261,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8306,7 +8295,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8340,7 +8329,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8389,7 +8378,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8470,7 +8459,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8481,7 +8470,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8497,7 +8486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8508,7 +8497,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8528,7 +8517,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8550,7 +8539,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8571,7 +8560,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8592,7 +8581,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8613,7 +8602,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8634,7 +8623,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8655,7 +8644,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8667,7 +8656,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8679,7 +8668,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8703,12 +8692,12 @@
         <v>23401555442.817001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8728,7 +8717,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8748,7 +8737,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8768,7 +8757,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8788,7 +8777,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8808,7 +8797,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8829,7 +8818,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8849,7 +8838,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8869,7 +8858,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8882,7 +8871,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8895,7 +8884,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8919,7 +8908,7 @@
         <v>123540874.18699999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8936,7 +8925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8955,7 +8944,7 @@
         <v>23138515188.125008</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8970,7 +8959,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8989,7 +8978,7 @@
         <v>23033712462.895008</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9005,7 +8994,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -9022,7 +9011,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9042,7 +9031,7 @@
         <v>38790734553.865005</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9053,7 +9042,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9066,7 +9055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9085,7 +9074,7 @@
         <v>15265638236.861</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9101,7 +9090,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9117,7 +9106,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9133,7 +9122,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9152,7 +9141,7 @@
         <v>755103420.58799994</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9172,7 +9161,7 @@
         <v>23525096317.004002</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9192,7 +9181,7 @@
         <v>19573468180.533001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9211,7 +9200,7 @@
         <v>3951628136.4709997</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9222,7 +9211,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9236,7 +9225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9250,7 +9239,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9265,10 +9254,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9281,7 +9270,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9295,7 +9284,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9306,10 +9295,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9321,7 +9310,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9335,7 +9324,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9349,10 +9338,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9364,7 +9353,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9375,7 +9364,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9386,10 +9375,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9401,7 +9390,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9417,7 +9406,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9428,7 +9417,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9442,7 +9431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9458,7 +9447,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9468,7 +9457,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9478,7 +9467,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9488,7 +9477,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9498,10 +9487,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9513,7 +9502,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9529,7 +9518,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9545,7 +9534,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9558,7 +9547,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9571,10 +9560,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9586,7 +9575,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9600,7 +9589,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9614,7 +9603,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9628,7 +9617,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9642,7 +9631,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9653,7 +9642,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9661,7 +9650,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9678,7 +9667,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9695,7 +9684,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9712,7 +9701,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9743,19 +9732,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9812,7 +9801,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9835,7 +9824,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9849,7 +9838,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9906,7 +9895,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9961,7 +9950,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10016,7 +10005,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10071,7 +10060,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10128,7 +10117,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10183,7 +10172,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10238,7 +10227,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10295,7 +10284,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10350,7 +10339,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10405,7 +10394,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10460,7 +10449,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10517,7 +10506,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10574,7 +10563,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10600,7 +10589,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10625,7 +10614,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10682,7 +10671,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10701,7 +10690,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10724,7 +10713,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10745,7 +10734,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10802,7 +10791,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10859,7 +10848,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10916,18 +10905,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10986,7 +10975,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11046,7 +11035,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11101,18 +11090,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11169,7 +11158,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11228,7 +11217,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11285,18 +11274,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11354,7 +11343,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11412,7 +11401,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11467,18 +11456,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11536,10 +11525,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11562,14 +11551,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11624,7 +11613,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11679,7 +11668,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11736,7 +11725,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11791,11 +11780,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11805,7 +11794,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11832,7 +11821,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11859,7 +11848,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11914,11 +11903,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11928,7 +11917,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11983,7 +11972,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -12038,7 +12027,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12093,7 +12082,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12148,7 +12137,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12204,7 +12193,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12259,11 +12248,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12273,7 +12262,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12298,7 +12287,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12323,7 +12312,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12348,7 +12337,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12375,10 +12364,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12401,7 +12390,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12422,7 +12411,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12479,7 +12468,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12536,7 +12525,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12593,7 +12582,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12650,7 +12639,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12707,7 +12696,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12766,7 +12755,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12823,7 +12812,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12880,7 +12869,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12937,7 +12926,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12994,7 +12983,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13052,7 +13041,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13109,7 +13098,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13135,7 +13124,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13159,7 +13148,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13216,18 +13205,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13283,7 +13272,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13339,7 +13328,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13394,7 +13383,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13449,11 +13438,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13474,7 +13463,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13531,7 +13520,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13588,10 +13577,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13614,7 +13603,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13624,7 +13613,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13681,7 +13670,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13738,7 +13727,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13795,7 +13784,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13852,7 +13841,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13909,11 +13898,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13936,7 +13925,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13993,7 +13982,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14050,7 +14039,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14077,18 +14066,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14140,7 +14129,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14192,11 +14181,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14250,7 +14239,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14305,7 +14294,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14359,7 +14348,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14415,7 +14404,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14472,7 +14461,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14491,7 +14480,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14514,7 +14503,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14535,7 +14524,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14593,7 +14582,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14650,7 +14639,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14700,688 +14689,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15403,16 +15392,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15424,7 +15413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15437,7 +15426,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15458,24 +15447,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>98897138487.684372</v>
+        <v>131862851316.91251</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15487,7 +15476,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15503,7 +15492,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15519,7 +15508,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15535,13 +15524,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>120246369511.18782</v>
+        <v>153212082340.41599</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15549,7 +15538,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15563,13 +15552,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15577,10 +15566,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15590,13 +15579,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15606,7 +15595,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15616,13 +15605,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>90.324402469499802</v>
+        <v>114.28146988410187</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15630,10 +15619,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15651,7 +15640,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15665,15 +15654,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>7666908144.0108585</v>
+        <v>7811566788.2374783</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15687,15 +15676,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>7429623519.3928375</v>
+        <v>7712631606.4612007</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15709,15 +15698,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>7199682662.565238</v>
+        <v>7614949460.1461096</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15731,15 +15720,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>6976858289.836812</v>
+        <v>7518504479.327261</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15753,15 +15742,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>6760930151.7632799</v>
+        <v>7423280995.0362368</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15775,15 +15764,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>6551684815.4430552</v>
+        <v>7329263536.7554998</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15797,15 +15786,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>6348915453.5507507</v>
+        <v>7236436829.9049568</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15819,15 +15808,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>6152421639.8999147</v>
+        <v>7144785793.3603764</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15841,15 +15830,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>5962009151.3329487</v>
+        <v>7054295537.0032158</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15863,15 +15852,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>5777489775.742363</v>
+        <v>6964951359.3015137</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15893,7 +15882,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15915,7 +15904,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15937,7 +15926,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15959,7 +15948,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15981,7 +15970,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -16003,7 +15992,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -16025,7 +16014,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -16047,7 +16036,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16069,7 +16058,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16091,7 +16080,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16113,7 +16102,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16135,7 +16124,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16157,7 +16146,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16179,7 +16168,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16201,7 +16190,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16223,7 +16212,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16245,7 +16234,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16267,7 +16256,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16289,7 +16278,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16311,13 +16300,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>103503259944.14659</v>
+        <v>138004346592.19547</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16325,30 +16314,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>47942036001.665039</v>
+        <v>77060906328.665588</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>114768559605.20309</v>
+        <v>150871572714.19943</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16358,10 +16347,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>114768559605.20309</v>
+        <v>150871572714.19943</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16385,141 +16374,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>98897138487.684357</v>
+        <v>131862851316.91246</v>
       </c>
       <c r="C56" s="124">
-        <v>102088077875.29443</v>
+        <v>135805844449.92731</v>
       </c>
       <c r="D56" s="124">
-        <v>105374584505.09332</v>
+        <v>139852232415.71622</v>
       </c>
       <c r="E56" s="124">
-        <v>108760852176.39565</v>
+        <v>144006584339.69742</v>
       </c>
       <c r="F56" s="124">
-        <v>115850097164.217</v>
+        <v>152658169425.57144</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>98897138487.684326</v>
+        <v>131862851316.91245</v>
       </c>
       <c r="C57" s="124">
-        <v>105281955613.83261</v>
+        <v>139526996239.74658</v>
       </c>
       <c r="D57" s="124">
-        <v>112306704291.55356</v>
+        <v>147931823859.71997</v>
       </c>
       <c r="E57" s="124">
-        <v>120047970304.87741</v>
+        <v>157167129881.31616</v>
       </c>
       <c r="F57" s="124">
-        <v>138030059034.22797</v>
+        <v>178539987088.48749</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>98897138487.684326</v>
+        <v>131862851316.91238</v>
       </c>
       <c r="C58" s="124">
-        <v>109235264894.58612</v>
+        <v>144572728629.97778</v>
       </c>
       <c r="D58" s="124">
-        <v>121343601530.94844</v>
+        <v>159470549709.87009</v>
       </c>
       <c r="E58" s="124">
-        <v>135573836760.51987</v>
+        <v>176999632488.5451</v>
       </c>
       <c r="F58" s="124">
-        <v>172167491625.06873</v>
+        <v>222185487922.9408</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>98897138487.684326</v>
+        <v>131862851316.91241</v>
       </c>
       <c r="C59" s="124">
-        <v>113263053069.17578</v>
+        <v>150211952883.24698</v>
       </c>
       <c r="D59" s="124">
-        <v>131070249485.46187</v>
+        <v>173094380390.05438</v>
       </c>
       <c r="E59" s="124">
-        <v>153284630237.75223</v>
+        <v>201817809542.06268</v>
       </c>
       <c r="F59" s="124">
-        <v>216272660170.65109</v>
+        <v>284050326350.68671</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>98897138487.684357</v>
+        <v>131862851316.91241</v>
       </c>
       <c r="C60" s="124">
-        <v>117009119573.54868</v>
+        <v>155967698295.02356</v>
       </c>
       <c r="D60" s="124">
-        <v>140651328614.23242</v>
+        <v>187821962501.96741</v>
       </c>
       <c r="E60" s="124">
-        <v>171845003307.02484</v>
+        <v>230361572572.81885</v>
       </c>
       <c r="F60" s="124">
-        <v>269167191558.10355</v>
+        <v>365481193994.38806</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>98897138487.684341</v>
+        <v>131862851316.91241</v>
       </c>
       <c r="C61" s="124">
-        <v>120313671338.89705</v>
+        <v>161540753521.27527</v>
       </c>
       <c r="D61" s="124">
-        <v>149624094128.00204</v>
+        <v>202961248583.99805</v>
       </c>
       <c r="E61" s="124">
-        <v>190403017716.18277</v>
+        <v>261689310173.7818</v>
       </c>
       <c r="F61" s="124">
-        <v>330241804375.50458</v>
+        <v>468695345588.16614</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16529,7 +16518,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16552,193 +16541,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935012</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>81.909948120886099</v>
+        <v>104.2842248733439</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>84.090792712746747</v>
+        <v>106.96930794354016</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>86.337836266711548</v>
+        <v>109.72603322866598</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>91.042084069495203</v>
+        <v>115.46701131599914</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>79.79251958953077</v>
+        <v>101.66775205935012</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>84.029326469312352</v>
+        <v>106.7534892535641</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>88.69077611437983</v>
+        <v>112.33072518375955</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>93.827688958625345</v>
+        <v>118.45904606063196</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>105.76015871243264</v>
+        <v>132.6415459923974</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>79.79251958953077</v>
+        <v>101.66775205935008</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>86.65264482403947</v>
+        <v>110.10171259059877</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>94.687437825949445</v>
+        <v>119.9875385426915</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>104.13027030342866</v>
+        <v>131.61940474114496</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>128.41291546354199</v>
+        <v>161.60362189111279</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>79.79251958953077</v>
+        <v>101.66775205935011</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>89.325385532385951</v>
+        <v>113.84376246310552</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>101.14180106873135</v>
+        <v>129.02797594510233</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>115.88271523147876</v>
+        <v>148.08813379108935</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>157.68001549723991</v>
+        <v>202.65560002746551</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>79.792519589530784</v>
+        <v>101.66775205935011</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>91.811182701555794</v>
+        <v>117.66313289722747</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>107.49956843567162</v>
+        <v>138.80083552455022</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>128.19892018418747</v>
+        <v>167.02906963845919</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>192.77951953274152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>256.69111168628518</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>79.79251958953077</v>
+        <v>101.66775205935011</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>94.004001599482223</v>
+        <v>121.36127463840373</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>113.45367391877409</v>
+        <v>148.84689168560169</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>140.51355998832523</v>
+        <v>187.81738222022025</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>233.30712348008615</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>325.18147232205541</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16755,7 +16744,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16770,14 +16759,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>128.41291546354199</v>
+        <v>161.60362189111279</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16792,7 +16781,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>93.827688958625345</v>
+        <v>118.45904606063196</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16800,7 +16789,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16815,7 +16804,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>88.69077611437983</v>
+        <v>112.33072518375955</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16823,7 +16812,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16838,7 +16827,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>84.029326469312352</v>
+        <v>106.7534892535641</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16846,7 +16835,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16861,21 +16850,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>79.79251958953077</v>
+        <v>101.66775205935008</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16883,23 +16872,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16933,16 +16922,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>445</v>
       </c>
@@ -16954,7 +16943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>444</v>
       </c>
@@ -16967,7 +16956,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>442</v>
       </c>
@@ -16988,24 +16977,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>443</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>87537165450</v>
+        <v>116716220600</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17015,13 +17004,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>446</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>58.087499999999999</v>
+        <v>77.45</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17029,10 +17018,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17042,13 +17031,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17058,7 +17047,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17068,13 +17057,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>67.40962183549351</v>
+        <v>88.61482358387353</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17082,10 +17071,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17103,7 +17092,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17117,15 +17106,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>6786236861.4012794</v>
+        <v>6914279066.3333788</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17139,15 +17128,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>6576208302.8245764</v>
+        <v>6826708227.4960709</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17161,15 +17150,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>6372679958.773056</v>
+        <v>6740246492.2603245</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17183,15 +17172,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>6175450652.8488035</v>
+        <v>6654879813.5893021</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17205,15 +17194,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>5984325434.9011974</v>
+        <v>6570594322.3549242</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17227,15 +17216,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>5799115388.3295727</v>
+        <v>6487376325.0846176</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17249,15 +17238,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>5619637443.34972</v>
+        <v>6405212301.7365952</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17271,15 +17260,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>5445714196.0396194</v>
+        <v>6324088903.5033274</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17293,15 +17282,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>5277173732.9855909</v>
+        <v>6243992950.6428108</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17315,15 +17304,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>5113849461.3554754</v>
+        <v>6164911430.337326</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17345,7 +17334,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17367,7 +17356,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17389,7 +17378,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17411,7 +17400,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17433,7 +17422,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17455,7 +17444,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17477,7 +17466,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17499,7 +17488,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17521,7 +17510,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17543,7 +17532,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17565,7 +17554,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17587,7 +17576,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17609,7 +17598,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17631,7 +17620,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17653,7 +17642,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17675,7 +17664,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17697,7 +17686,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17719,7 +17708,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17741,7 +17730,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17763,13 +17752,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>91614197628.917282</v>
+        <v>122152263505.22304</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17777,30 +17766,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>42435099757.817802</v>
+        <v>68209185929.675713</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>101585491190.62669</v>
+        <v>133541475763.0144</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17810,10 +17799,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>101585491190.62669</v>
+        <v>133541475763.0144</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17837,141 +17826,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>87537165449.999985</v>
+        <v>116716220599.99997</v>
       </c>
       <c r="C51" s="124">
-        <v>90361572641.00206</v>
+        <v>120206295717.75392</v>
       </c>
       <c r="D51" s="124">
-        <v>93270569594.852798</v>
+        <v>123787889060.6216</v>
       </c>
       <c r="E51" s="124">
-        <v>96267868383.610886</v>
+        <v>127465044914.35091</v>
       </c>
       <c r="F51" s="124">
-        <v>102542796262.25502</v>
+        <v>135122852275.08884</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>87537165449.999969</v>
+        <v>116716220599.99995</v>
       </c>
       <c r="C52" s="124">
-        <v>93188580664.700378</v>
+        <v>123500011641.90613</v>
       </c>
       <c r="D52" s="124">
-        <v>99406420701.830536</v>
+        <v>130939405715.37531</v>
       </c>
       <c r="E52" s="124">
-        <v>106258474200.68056</v>
+        <v>139113884002.17145</v>
       </c>
       <c r="F52" s="124">
-        <v>122175022447.76418</v>
+        <v>158031714852.4176</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>87537165449.999969</v>
+        <v>116716220599.99992</v>
       </c>
       <c r="C53" s="124">
-        <v>96687786949.899811</v>
+        <v>127966158163.57823</v>
       </c>
       <c r="D53" s="124">
-        <v>107405280738.59561</v>
+        <v>141152717943.33795</v>
       </c>
       <c r="E53" s="124">
-        <v>120000937951.04907</v>
+        <v>156668295470.13065</v>
       </c>
       <c r="F53" s="124">
-        <v>152391205953.56683</v>
+        <v>196663807611.79938</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>87537165449.999969</v>
+        <v>116716220599.99991</v>
       </c>
       <c r="C54" s="124">
-        <v>100252916995.4017</v>
+        <v>132957624185.91971</v>
       </c>
       <c r="D54" s="124">
-        <v>116014662205.92873</v>
+        <v>153211626204.49652</v>
       </c>
       <c r="E54" s="124">
-        <v>135677353695.47769</v>
+        <v>178635694164.60052</v>
       </c>
       <c r="F54" s="124">
-        <v>191430165980.25726</v>
+        <v>251422445523.87103</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>87537165449.999969</v>
+        <v>116716220599.99991</v>
       </c>
       <c r="C55" s="124">
-        <v>103568685766.819</v>
+        <v>138052226983.36572</v>
       </c>
       <c r="D55" s="124">
-        <v>124495195836.22354</v>
+        <v>166247501779.09198</v>
       </c>
       <c r="E55" s="124">
-        <v>152105760755.81912</v>
+        <v>203900733630.83395</v>
       </c>
       <c r="F55" s="124">
-        <v>238248885068.27466</v>
+        <v>323499630391.57477</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>87537165449.999969</v>
+        <v>116716220599.99991</v>
       </c>
       <c r="C56" s="124">
-        <v>106493655073.76625</v>
+        <v>142985124586.49646</v>
       </c>
       <c r="D56" s="124">
-        <v>132437290737.38911</v>
+        <v>179647790309.40805</v>
       </c>
       <c r="E56" s="124">
-        <v>168532080087.19437</v>
+        <v>231629962114.94409</v>
       </c>
       <c r="F56" s="124">
-        <v>292308067859.06183</v>
+        <v>414857928548.71576</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17981,7 +17970,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -18004,193 +17993,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>58.087499999999999</v>
+        <v>77.45</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>58.087499999999999</v>
+        <v>77.45</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>58.087499999999999</v>
+        <v>77.45</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>58.087499999999999</v>
+        <v>77.45</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>58.087499999999999</v>
+        <v>77.45</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>58.087499999999991</v>
+        <v>77.449999999999974</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>59.961706822484359</v>
+        <v>79.765927610408255</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>61.892045321431091</v>
+        <v>82.142584453639714</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>63.880978736135184</v>
+        <v>84.582654217784679</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>68.044865826572618</v>
+        <v>89.664185962389112</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>58.087499999999977</v>
+        <v>77.449999999999974</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>61.837639493280889</v>
+        <v>81.951556111864278</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>65.963644502697122</v>
+        <v>86.888154195902885</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>70.510497894263622</v>
+        <v>92.312536000400428</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>81.072326022346672</v>
+        <v>104.86594110398862</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>58.087499999999977</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>64.159626320780134</v>
+        <v>84.915180587754008</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>71.271490375899219</v>
+        <v>93.66545582535359</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>79.62965727069431</v>
+        <v>103.96120969120567</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>101.12303877241679</v>
+        <v>130.50124328249422</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>58.087499999999977</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>66.52535852667819</v>
+        <v>88.227394103947546</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>76.984463184795587</v>
+        <v>101.66744937882486</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>90.03213940355046</v>
+        <v>118.53823266316688</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>127.02832801605405</v>
+        <v>166.83772234674134</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>58.087499999999977</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>68.725620752666245</v>
+        <v>91.608046635650524</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>82.611935752788696</v>
+        <v>110.31773430119681</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>100.9336243923768</v>
+        <v>135.30348856847829</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>158.09607313945079</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>214.66636123948882</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>58.087499999999977</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>70.66655811046023</v>
+        <v>94.881395596047525</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>87.882113684640558</v>
+        <v>119.20983465655205</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>111.83372401584775</v>
+        <v>153.70391941737034</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>193.96841106834415</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>275.2894704859732</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18207,7 +18196,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18222,14 +18211,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>101.12303877241679</v>
+        <v>130.50124328249422</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18244,7 +18233,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>70.510497894263622</v>
+        <v>92.312536000400428</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18252,7 +18241,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18267,7 +18256,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>65.963644502697122</v>
+        <v>86.888154195902885</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18275,7 +18264,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18290,7 +18279,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>61.837639493280889</v>
+        <v>81.951556111864278</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18298,7 +18287,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18313,21 +18302,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>58.087499999999977</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18335,23 +18324,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18381,7 +18370,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18391,7 +18380,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18404,7 +18393,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18416,7 +18405,7 @@
         <v>-68.31</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18436,7 +18425,7 @@
         <v>4.6470000000000002</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18445,7 +18434,7 @@
         <v>4.6470000000000002</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18462,10 +18451,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>94.964553631447529</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>119.0074166533086</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18490,7 +18479,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18512,7 +18501,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18534,7 +18523,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18545,7 +18534,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
@@ -18559,7 +18548,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18578,7 +18567,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18596,7 +18585,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18607,7 +18596,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18616,7 +18605,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18624,7 +18613,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18636,18 +18625,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18662,13 +18651,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>79.792519589530784</v>
+        <v>101.66775205935016</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18677,7 +18666,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18686,7 +18675,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18698,7 +18687,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18709,13 +18698,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>88.69077611437983</v>
+        <v>112.33072518375955</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18724,7 +18713,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18735,7 +18724,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18744,7 +18733,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18756,7 +18745,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18767,13 +18756,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>84.029326469312352</v>
+        <v>106.7534892535641</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18782,7 +18771,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18793,7 +18782,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18802,7 +18791,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18814,7 +18803,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18825,13 +18814,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>93.827688958625345</v>
+        <v>118.45904606063196</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18840,7 +18829,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18852,20 +18841,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>88.785868754215429</v>
+        <v>112.44094217309495</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18874,12 +18863,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18889,12 +18878,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18903,7 +18892,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18915,7 +18904,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18926,13 +18915,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>79.79251958953077</v>
+        <v>101.66775205935008</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18941,7 +18930,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18952,7 +18941,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18961,7 +18950,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18973,7 +18962,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18984,13 +18973,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>128.41291546354199</v>
+        <v>161.60362189111279</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18999,7 +18988,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -19010,13 +18999,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>90.317553631447524</v>
+        <v>114.36041665330859</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19030,7 +19019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -19039,7 +19028,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -19047,7 +19036,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19060,7 +19049,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19072,13 +19061,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>90.324402469499802</v>
+        <v>114.28146988410187</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19088,7 +19077,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -19096,7 +19085,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19106,7 +19095,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19118,7 +19107,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19128,7 +19117,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19141,10 +19130,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.15685568984609902</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.12387872128011246</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19153,12 +19142,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19168,7 +19157,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19181,49 +19170,49 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>8.4394765589440173</v>
+        <v>9.248657083863371</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>41.10949186684001</v>
+        <v>60.418039681106563</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>49.548968425784025</v>
+        <v>69.666696764969942</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19234,18 +19223,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.45139160181447113</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.39081459473718705</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19258,61 +19247,61 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15993573478625023</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.24557216589977915</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.311354456764589</v>
+        <v>10.843167062410641</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>56.769242429883334</v>
+        <v>77.802640211620684</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>67.080596886647925</v>
+        <v>88.645807274031327</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19323,58 +19312,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.25728062608538993</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.22485585600158187</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>11.9757696997409</v>
+        <v>12.421486529148241</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>71.696986002711341</v>
+        <v>96.019211037726251</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>83.672755702452235</v>
+        <v>108.44069756687449</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19384,53 +19373,53 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>7.3571500354297048E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>5.1763706881028049E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>423</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>11.211366726236903</v>
+        <v>11.826104101614131</v>
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>64.736045237011837</v>
+        <v>89.040398847670232</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>75.94741196324874</v>
+        <v>100.86650294928437</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19440,19 +19429,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.15917061295928081</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.11738532019602332</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19460,7 +19449,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19468,7 +19457,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600AE558-FF75-4A8F-9EFC-91191836EADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9A2747-C0FE-47A5-9FCB-F7D5024ECEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3866,29 +3866,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4364,13 +4364,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4446,14 +4446,14 @@
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>114.36041665330859</v>
+        <v>106.27676864573534</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.24557216589977915</v>
+        <v>0.21816040050529906</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>69.666696764969942</v>
+        <v>46.114318019582861</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4495,7 +4495,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.23700000000000002</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>88.645807274031327</v>
+        <v>68.017644343433673</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4514,7 +4514,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="342">
-        <v>0.13700000000000001</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>108.44069756687449</v>
+        <v>101.65351082247034</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>100.86650294928437</v>
+        <v>94.572618545902628</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4570,22 +4570,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4597,13 +4597,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4623,13 +4623,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4658,13 +4658,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4680,13 +4680,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4750,13 +4750,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4772,7 +4772,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4794,22 +4794,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4878,22 +4878,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4937,22 +4937,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4989,13 +4989,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5008,13 +5008,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5190,13 +5190,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="C121" s="251">
         <f>DCF!C74</f>
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D121" s="252">
         <f>DCF!D74</f>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>161.6 CNY</v>
+        <v>138.2 CNY</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="C122" s="241">
         <f>DCF!C75</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D122" s="242">
         <f>DCF!D75</f>
@@ -5252,11 +5252,11 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>118.46 CNY</v>
+        <v>112.33 CNY</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="C123" s="241">
         <f>DCF!C76</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D123" s="242">
         <f>DCF!D76</f>
@@ -5274,11 +5274,11 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>112.33 CNY</v>
+        <v>106.75 CNY</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
-        <v>0.53999999999999992</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C124" s="241">
         <f>DCF!C77</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D124" s="242">
         <f>DCF!D77</f>
@@ -5296,11 +5296,11 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>106.75 CNY</v>
+        <v>101.67 CNY</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C125" s="241">
         <f>DCF!C78</f>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D125" s="242">
         <f>DCF!D78</f>
@@ -5318,11 +5318,11 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>101.67 CNY</v>
+        <v>85.43 CNY</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>114.36041665330859</v>
+        <v>106.27676864573534</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
@@ -5339,13 +5339,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5358,22 +5358,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>9.248657083863371</v>
+        <v>7.3837172011661796</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>60.418039681106563</v>
+        <v>38.730600818416683</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>69.666696764969942</v>
+        <v>46.114318019582861</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39081459473718705</v>
+        <v>0.56609220804124138</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.13700000000000001</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>10.843167062410641</v>
+        <v>9.4902958837964402</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>77.802640211620684</v>
+        <v>58.527348459637231</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>88.645807274031327</v>
+        <v>68.017644343433673</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.22485585600158187</v>
+        <v>0.35999517853083429</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>96.019211037726251</v>
+        <v>89.232024293322098</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>108.44069756687449</v>
+        <v>101.65351082247034</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>5.1763706881028049E-2</v>
+        <v>4.3502054891001118E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>89.040398847670232</v>
+        <v>82.746514444288493</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>100.86650294928437</v>
+        <v>94.572618545902628</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.11738532019602332</v>
+        <v>0.11015610386064956</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5706,13 +5706,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5749,13 +5749,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5763,22 +5763,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5802,17 +5802,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5829,6 +5818,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>114.28146988410187</v>
+        <v>106.28001041105357</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15646,11 +15646,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>8280260795.5317278</v>
+        <v>8055871047.3986158</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>7811566788.2374783</v>
+        <v>7599878346.6024666</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15668,11 +15668,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>8665912873.0198059</v>
+        <v>8202595560.9925051</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>7712631606.4612007</v>
+        <v>7300280848.159936</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15690,11 +15690,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>9069526646.2253819</v>
+        <v>8351992421.5942717</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>7614949460.1461096</v>
+        <v>7012493888.9101992</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15712,11 +15712,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>9491938678.8074646</v>
+        <v>8504110301.6333265</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>7518504479.327261</v>
+        <v>6736051881.4009285</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15734,11 +15734,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>9934024497.269474</v>
+        <v>8658998760.0277615</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>7423280995.0362368</v>
+        <v>6470507592.2677975</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15756,11 +15756,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>10396700405.648687</v>
+        <v>8816708258.3302975</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>7329263536.7554998</v>
+        <v>6215431418.6914835</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15778,11 +15778,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>10880925384.724613</v>
+        <v>8977290177.1682949</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>7236436829.9049568</v>
+        <v>5970410693.3776951</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15800,11 +15800,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>11387703079.682753</v>
+        <v>9140796832.9831963</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>7144785793.3603764</v>
+        <v>5735049016.9358444</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15822,11 +15822,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>11918083880.353537</v>
+        <v>9307281495.0748405</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>7054295537.0032158</v>
+        <v>5508965616.576232</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15844,11 +15844,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>12473167098.33814</v>
+        <v>9476798402.9562359</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>6964951359.3015137</v>
+        <v>5291794730.0882921</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>138004346592.19547</v>
+        <v>134264517456.6436</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>77060906328.665588</v>
+        <v>74972605272.818451</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>150871572714.19943</v>
+        <v>138813469305.82932</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16350,27 +16350,27 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>150871572714.19943</v>
+        <v>138813469305.82932</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C55" s="132">
         <f>C77</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D55" s="132">
         <f>C76</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -16380,19 +16380,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
+        <v>122428991756.41138</v>
+      </c>
+      <c r="C56" s="124">
         <v>131862851316.91246</v>
       </c>
-      <c r="C56" s="124">
+      <c r="D56" s="124">
         <v>135805844449.92731</v>
       </c>
-      <c r="D56" s="124">
+      <c r="E56" s="124">
         <v>139852232415.71622</v>
       </c>
-      <c r="E56" s="124">
-        <v>144006584339.69742</v>
-      </c>
       <c r="F56" s="124">
-        <v>152658169425.57144</v>
+        <v>146125713436.09314</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16401,19 +16401,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
+        <v>115434363333.8261</v>
+      </c>
+      <c r="C57" s="124">
         <v>131862851316.91245</v>
       </c>
-      <c r="C57" s="124">
+      <c r="D57" s="124">
         <v>139526996239.74658</v>
       </c>
-      <c r="D57" s="124">
+      <c r="E57" s="124">
         <v>147931823859.71997</v>
       </c>
-      <c r="E57" s="124">
-        <v>157167129881.31616</v>
-      </c>
       <c r="F57" s="124">
-        <v>178539987088.48749</v>
+        <v>162127014665.26779</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16422,19 +16422,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
+        <v>107390580554.09012</v>
+      </c>
+      <c r="C58" s="124">
         <v>131862851316.91238</v>
       </c>
-      <c r="C58" s="124">
+      <c r="D58" s="124">
         <v>144572728629.97778</v>
       </c>
-      <c r="D58" s="124">
+      <c r="E58" s="124">
         <v>159470549709.87009</v>
       </c>
-      <c r="E58" s="124">
-        <v>176999632488.5451</v>
-      </c>
       <c r="F58" s="124">
-        <v>222185487922.9408</v>
+        <v>186913261733.77335</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16443,19 +16443,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
+        <v>99750974985.127075</v>
+      </c>
+      <c r="C59" s="124">
         <v>131862851316.91241</v>
       </c>
-      <c r="C59" s="124">
+      <c r="D59" s="124">
         <v>150211952883.24698</v>
       </c>
-      <c r="D59" s="124">
+      <c r="E59" s="124">
         <v>173094380390.05438</v>
       </c>
-      <c r="E59" s="124">
-        <v>201817809542.06268</v>
-      </c>
       <c r="F59" s="124">
-        <v>284050326350.68671</v>
+        <v>218880805795.82471</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16464,19 +16464,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
+        <v>93100408728.65657</v>
+      </c>
+      <c r="C60" s="124">
         <v>131862851316.91241</v>
       </c>
-      <c r="C60" s="124">
+      <c r="D60" s="124">
         <v>155967698295.02356</v>
       </c>
-      <c r="D60" s="124">
+      <c r="E60" s="124">
         <v>187821962501.96741</v>
       </c>
-      <c r="E60" s="124">
-        <v>230361572572.81885</v>
-      </c>
       <c r="F60" s="124">
-        <v>365481193994.38806</v>
+        <v>256860949601.11633</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16485,19 +16485,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
+        <v>87586151723.987686</v>
+      </c>
+      <c r="C61" s="124">
         <v>131862851316.91241</v>
       </c>
-      <c r="C61" s="124">
+      <c r="D61" s="124">
         <v>161540753521.27527</v>
       </c>
-      <c r="D61" s="124">
+      <c r="E61" s="124">
         <v>202961248583.99805</v>
       </c>
-      <c r="E61" s="124">
-        <v>261689310173.7818</v>
-      </c>
       <c r="F61" s="124">
-        <v>468695345588.16614</v>
+        <v>300011441894.66858</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16521,23 +16521,23 @@
     <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C64" s="133">
         <f>C55</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D64" s="133">
         <f>D55</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -16574,23 +16574,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>101.66775205935012</v>
+        <v>95.407675960203306</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>104.2842248733439</v>
+        <v>101.66775205935012</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>106.96930794354016</v>
+        <v>104.2842248733439</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>109.72603322866598</v>
+        <v>106.96930794354016</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>115.46701131599914</v>
+        <v>111.1322349345825</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16601,23 +16601,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>101.66775205935012</v>
+        <v>90.766213372189782</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>106.7534892535641</v>
+        <v>101.66775205935012</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>112.33072518375955</v>
+        <v>106.7534892535641</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>118.45904606063196</v>
+        <v>112.33072518375955</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>132.6415459923974</v>
+        <v>121.75030304738409</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16628,23 +16628,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>101.66775205935008</v>
+        <v>85.428557876767158</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>110.10171259059877</v>
+        <v>101.66775205935008</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>119.9875385426915</v>
+        <v>110.10171259059877</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>131.61940474114496</v>
+        <v>119.9875385426915</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>161.60362189111279</v>
+        <v>138.19784414824593</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16655,23 +16655,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>101.66775205935011</v>
+        <v>80.359104391428829</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>113.84376246310552</v>
+        <v>101.66775205935011</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>129.02797594510233</v>
+        <v>113.84376246310552</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>148.08813379108935</v>
+        <v>129.02797594510233</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>202.65560002746551</v>
+        <v>159.41071648833844</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16682,23 +16682,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>101.66775205935011</v>
+        <v>75.945952955272389</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>117.66313289722747</v>
+        <v>101.66775205935011</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>138.80083552455022</v>
+        <v>117.66313289722747</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>167.02906963845919</v>
+        <v>138.80083552455022</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>256.69111168628518</v>
+        <v>184.61340145019059</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16708,23 +16708,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>101.66775205935011</v>
+        <v>72.286828261068521</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>121.36127463840373</v>
+        <v>101.66775205935011</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>148.84689168560169</v>
+        <v>121.36127463840373</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>187.81738222022025</v>
+        <v>148.84689168560169</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>325.18147232205541</v>
+        <v>213.24700191253817</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>161.60362189111279</v>
+        <v>138.19784414824593</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16773,7 +16773,7 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
@@ -16781,11 +16781,11 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>118.45904606063196</v>
+        <v>112.33072518375955</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H75" s="121"/>
     </row>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="C76" s="143">
         <f>Scenarios!C26</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="146">
         <f>Scenarios!C25</f>
@@ -16804,11 +16804,11 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>112.33072518375955</v>
+        <v>106.7534892535641</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.53999999999999992</v>
+        <v>0.51</v>
       </c>
       <c r="H76" s="121"/>
     </row>
@@ -16819,7 +16819,7 @@
       </c>
       <c r="C77" s="143">
         <f>Scenarios!C32</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D77" s="146">
         <f>Scenarios!C31</f>
@@ -16827,11 +16827,11 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>106.7534892535641</v>
+        <v>101.66775205935012</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H77" s="121"/>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="C78" s="143">
         <f>Scenarios!C50</f>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
@@ -16850,11 +16850,11 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>101.66775205935008</v>
+        <v>85.428557876767158</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="C11" s="162">
         <f>Scenarios!C65</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="H11" s="121"/>
     </row>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>88.61482358387353</v>
+        <v>81.532464150178455</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17098,11 +17098,11 @@
       </c>
       <c r="C16" s="124">
         <f>C4*(1+D16)</f>
-        <v>7329135810.3133821</v>
+        <v>7130520938.2556019</v>
       </c>
       <c r="D16" s="139">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>6914279066.3333788</v>
+        <v>6726906545.5241518</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -17120,11 +17120,11 @@
       </c>
       <c r="C17" s="124">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>7670489364.4145861</v>
+        <v>7260391713.2693653</v>
       </c>
       <c r="D17" s="139">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
@@ -17132,7 +17132,7 @@
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>6826708227.4960709</v>
+        <v>6461722777.918623</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -17142,11 +17142,11 @@
       </c>
       <c r="C18" s="124">
         <f t="shared" si="2"/>
-        <v>8027741416.2259245</v>
+        <v>7392627872.0115719</v>
       </c>
       <c r="D18" s="139">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>6740246492.2603245</v>
+        <v>6206992913.6229658</v>
       </c>
       <c r="H18" s="121"/>
     </row>
@@ -17164,11 +17164,11 @@
       </c>
       <c r="C19" s="124">
         <f t="shared" si="2"/>
-        <v>8401632436.2255907</v>
+        <v>7527272496.0776186</v>
       </c>
       <c r="D19" s="139">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>6654879813.5893021</v>
+        <v>5962304845.6089191</v>
       </c>
       <c r="H19" s="121"/>
     </row>
@@ -17186,11 +17186,11 @@
       </c>
       <c r="C20" s="124">
         <f t="shared" si="2"/>
-        <v>8792937382.2087021</v>
+        <v>7664369451.7236862</v>
       </c>
       <c r="D20" s="139">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>6570594322.3549242</v>
+        <v>5727262712.6654644</v>
       </c>
       <c r="H20" s="121"/>
     </row>
@@ -17208,11 +17208,11 @@
       </c>
       <c r="C21" s="124">
         <f t="shared" si="2"/>
-        <v>9202467305.5296268</v>
+        <v>7803963404.158061</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>6487376325.0846176</v>
+        <v>5501486258.9667225</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -17230,11 +17230,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" si="2"/>
-        <v>9631071032.1548481</v>
+        <v>7946099832.0927353</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>6405212301.7365952</v>
+        <v>5284610218.8865232</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -17252,11 +17252,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>10079636922.010645</v>
+        <v>8090825042.5600481</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>6324088903.5033274</v>
+        <v>5076283726.0644341</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -17274,11 +17274,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>10549094710.272169</v>
+        <v>8238186185.9991837</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -17286,7 +17286,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>6243992950.6428108</v>
+        <v>4876169745.7671928</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -17296,11 +17296,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>11040417434.410316</v>
+        <v>8388231271.6174488</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>6164911430.337326</v>
+        <v>4683944529.6272411</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -17758,7 +17758,7 @@
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>122152263505.22304</v>
+        <v>118842015637.59337</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>68209185929.675713</v>
+        <v>66360760810.096893</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>133541475763.0144</v>
+        <v>122868445084.74913</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -17802,27 +17802,27 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>133541475763.0144</v>
+        <v>122868445084.74913</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C50" s="132">
         <f>C72</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D50" s="132">
         <f>C71</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E50" s="132">
         <f>C70</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F50" s="132">
         <f>C69</f>
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -17832,19 +17832,19 @@
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>108365995934.17218</v>
+      </c>
+      <c r="C51" s="124">
         <v>116716220599.99997</v>
       </c>
-      <c r="C51" s="124">
+      <c r="D51" s="124">
         <v>120206295717.75392</v>
       </c>
-      <c r="D51" s="124">
+      <c r="E51" s="124">
         <v>123787889060.6216</v>
       </c>
-      <c r="E51" s="124">
-        <v>127465044914.35091</v>
-      </c>
       <c r="F51" s="124">
-        <v>135122852275.08884</v>
+        <v>129340756963.83759</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -17853,19 +17853,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="124">
+        <v>102174816342.40504</v>
+      </c>
+      <c r="C52" s="124">
         <v>116716220599.99995</v>
       </c>
-      <c r="C52" s="124">
+      <c r="D52" s="124">
         <v>123500011641.90613</v>
       </c>
-      <c r="D52" s="124">
+      <c r="E52" s="124">
         <v>130939405715.37531</v>
       </c>
-      <c r="E52" s="124">
-        <v>139113884002.17145</v>
-      </c>
       <c r="F52" s="124">
-        <v>158031714852.4176</v>
+        <v>143504043935.86639</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -17874,19 +17874,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="124">
+        <v>95054995134.218185</v>
+      </c>
+      <c r="C53" s="124">
         <v>116716220599.99992</v>
       </c>
-      <c r="C53" s="124">
+      <c r="D53" s="124">
         <v>127966158163.57823</v>
       </c>
-      <c r="D53" s="124">
+      <c r="E53" s="124">
         <v>141152717943.33795</v>
       </c>
-      <c r="E53" s="124">
-        <v>156668295470.13065</v>
-      </c>
       <c r="F53" s="124">
-        <v>196663807611.79938</v>
+        <v>165443180332.52301</v>
       </c>
       <c r="H53" s="121"/>
     </row>
@@ -17895,19 +17895,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="124">
+        <v>88292924695.280884</v>
+      </c>
+      <c r="C54" s="124">
         <v>116716220599.99991</v>
       </c>
-      <c r="C54" s="124">
+      <c r="D54" s="124">
         <v>132957624185.91971</v>
       </c>
-      <c r="D54" s="124">
+      <c r="E54" s="124">
         <v>153211626204.49652</v>
       </c>
-      <c r="E54" s="124">
-        <v>178635694164.60052</v>
-      </c>
       <c r="F54" s="124">
-        <v>251422445523.87103</v>
+        <v>193738722917.29083</v>
       </c>
       <c r="H54" s="121"/>
     </row>
@@ -17916,19 +17916,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="124">
+        <v>82406286035.848465</v>
+      </c>
+      <c r="C55" s="124">
         <v>116716220599.99991</v>
       </c>
-      <c r="C55" s="124">
+      <c r="D55" s="124">
         <v>138052226983.36572</v>
       </c>
-      <c r="D55" s="124">
+      <c r="E55" s="124">
         <v>166247501779.09198</v>
       </c>
-      <c r="E55" s="124">
-        <v>203900733630.83395</v>
-      </c>
       <c r="F55" s="124">
-        <v>323499630391.57477</v>
+        <v>227356218660.23007</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -17937,19 +17937,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="124">
+        <v>77525432705.480026</v>
+      </c>
+      <c r="C56" s="124">
         <v>116716220599.99991</v>
       </c>
-      <c r="C56" s="124">
+      <c r="D56" s="124">
         <v>142985124586.49646</v>
       </c>
-      <c r="D56" s="124">
+      <c r="E56" s="124">
         <v>179647790309.40805</v>
       </c>
-      <c r="E56" s="124">
-        <v>231629962114.94409</v>
-      </c>
       <c r="F56" s="124">
-        <v>414857928548.71576</v>
+        <v>265550162801.69803</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -17973,23 +17973,23 @@
     <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="C59" s="133">
         <f>C50</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D59" s="133">
         <f>D50</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E59" s="133">
         <f>E50</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F59" s="133">
         <f>F50</f>
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -18026,23 +18026,23 @@
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>77.449999999999974</v>
+        <v>71.908997240968191</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>79.765927610408255</v>
+        <v>77.449999999999974</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>82.142584453639714</v>
+        <v>79.765927610408255</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>84.582654217784679</v>
+        <v>82.142584453639714</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>89.664185962389112</v>
+        <v>85.827330386066507</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -18053,23 +18053,23 @@
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>77.449999999999974</v>
+        <v>67.800683444330701</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>81.951556111864278</v>
+        <v>77.449999999999974</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>86.888154195902885</v>
+        <v>81.951556111864278</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>92.312536000400428</v>
+        <v>86.888154195902885</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>104.86594110398862</v>
+        <v>95.225737654093066</v>
       </c>
       <c r="H62" s="121"/>
     </row>
@@ -18080,23 +18080,23 @@
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>77.449999999999946</v>
+        <v>63.076146017233171</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>84.915180587754008</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>93.66545582535359</v>
+        <v>84.915180587754008</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>103.96120969120567</v>
+        <v>93.66545582535359</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>130.50124328249422</v>
+        <v>109.78400646357039</v>
       </c>
       <c r="H63" s="121"/>
     </row>
@@ -18107,23 +18107,23 @@
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>77.449999999999946</v>
+        <v>58.5890031607955</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>88.227394103947546</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>101.66744937882486</v>
+        <v>88.227394103947546</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>118.53823266316688</v>
+        <v>101.66744937882486</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>166.83772234674134</v>
+        <v>128.56022935636571</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -18134,23 +18134,23 @@
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>77.449999999999946</v>
+        <v>54.682775201825407</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>91.608046635650524</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>110.31773430119681</v>
+        <v>91.608046635650524</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>135.30348856847829</v>
+        <v>110.31773430119681</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>214.66636123948882</v>
+        <v>150.86796886254572</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18160,23 +18160,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>77.449999999999946</v>
+        <v>51.443961534849663</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>94.881395596047525</v>
+        <v>77.449999999999946</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>119.20983465655205</v>
+        <v>94.881395596047525</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>153.70391941737034</v>
+        <v>119.20983465655205</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>275.2894704859732</v>
+        <v>176.2125264446021</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="C69" s="143">
         <f>Scenarios!C56</f>
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D69" s="146">
         <f>Scenarios!C55</f>
@@ -18211,7 +18211,7 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>130.50124328249422</v>
+        <v>109.78400646357039</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="C70" s="143">
         <f>Scenarios!C38</f>
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D70" s="146">
         <f>Scenarios!C37</f>
@@ -18233,11 +18233,11 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>92.312536000400428</v>
+        <v>86.888154195902885</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H70" s="121"/>
     </row>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="C71" s="143">
         <f>Scenarios!C26</f>
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D71" s="146">
         <f>Scenarios!C25</f>
@@ -18256,11 +18256,11 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>86.888154195902885</v>
+        <v>81.951556111864278</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
-        <v>0.53999999999999992</v>
+        <v>0.51</v>
       </c>
       <c r="H71" s="121"/>
     </row>
@@ -18271,7 +18271,7 @@
       </c>
       <c r="C72" s="143">
         <f>Scenarios!C32</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D72" s="146">
         <f>Scenarios!C31</f>
@@ -18279,11 +18279,11 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>81.951556111864278</v>
+        <v>77.449999999999974</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H72" s="121"/>
     </row>
@@ -18294,7 +18294,7 @@
       </c>
       <c r="C73" s="143">
         <f>Scenarios!C50</f>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D73" s="146">
         <f>Scenarios!C49</f>
@@ -18302,11 +18302,11 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>77.449999999999946</v>
+        <v>63.076146017233171</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>119.0074166533086</v>
+        <v>110.92376864573535</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18692,7 +18692,7 @@
         <v>135</v>
       </c>
       <c r="C26" s="165">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
       <c r="E26" s="356"/>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>112.33072518375955</v>
+        <v>106.7534892535641</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18750,7 +18750,7 @@
         <v>135</v>
       </c>
       <c r="C32" s="165">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D32" s="165"/>
       <c r="E32" s="356"/>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>106.7534892535641</v>
+        <v>101.66775205935012</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18808,7 +18808,7 @@
         <v>135</v>
       </c>
       <c r="C38" s="165">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="356"/>
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>118.45904606063196</v>
+        <v>112.33072518375955</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>112.44094217309495</v>
+        <v>106.85178900076039</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18909,7 +18909,7 @@
         <v>135</v>
       </c>
       <c r="C50" s="165">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D50" s="165"/>
       <c r="E50" s="356"/>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>101.66775205935008</v>
+        <v>85.428557876767158</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18935,7 +18935,7 @@
         <v>148</v>
       </c>
       <c r="C52" s="166">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D52" s="166"/>
       <c r="E52" s="356"/>
@@ -18967,7 +18967,7 @@
         <v>135</v>
       </c>
       <c r="C56" s="165">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D56" s="165"/>
       <c r="E56" s="356"/>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>161.60362189111279</v>
+        <v>138.19784414824593</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>114.36041665330859</v>
+        <v>106.27676864573534</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19054,7 +19054,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>4.6574870890079501E-2</v>
+        <v>1.821336423219809E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="273" t="s">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>114.28146988410187</v>
+        <v>106.28001041105357</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.12387872128011246</v>
+        <v>0.13330121305528825</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19190,7 +19190,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>9.248657083863371</v>
+        <v>7.3837172011661796</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>60.418039681106563</v>
+        <v>38.730600818416683</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>69.666696764969942</v>
+        <v>46.114318019582861</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.39081459473718705</v>
+        <v>0.56609220804124138</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.24557216589977915</v>
+        <v>0.21816040050529906</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.13700000000000001</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.843167062410641</v>
+        <v>9.4902958837964402</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>77.802640211620684</v>
+        <v>58.527348459637231</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>88.645807274031327</v>
+        <v>68.017644343433673</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.22485585600158187</v>
+        <v>0.35999517853083429</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19351,7 +19351,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>96.019211037726251</v>
+        <v>89.232024293322098</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>108.44069756687449</v>
+        <v>101.65351082247034</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>5.1763706881028049E-2</v>
+        <v>4.3502054891001118E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19409,7 +19409,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>89.040398847670232</v>
+        <v>82.746514444288493</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>100.86650294928437</v>
+        <v>94.572618545902628</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.11738532019602332</v>
+        <v>0.11015610386064956</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9A2747-C0FE-47A5-9FCB-F7D5024ECEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC2728B-77A7-4D38-9858-CAB5041DB1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="463">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2466,6 +2466,9 @@
   </si>
   <si>
     <t>CN</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -4216,7 +4219,7 @@
         <v>354</v>
       </c>
       <c r="F1" s="276" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4306,7 +4309,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>68.31</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4327,7 +4330,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>102942.35028</v>
+        <v>102625.88279999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4453,7 +4456,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21816040050529906</v>
+        <v>0.2194806865769845</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4485,7 +4488,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>46.114318019582861</v>
+        <v>52.487323639990407</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4495,7 +4498,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4504,7 +4507,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>68.017644343433673</v>
+        <v>73.53733493377743</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4514,7 +4517,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="342">
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4843,7 +4846,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6856328396378931E-2</v>
+        <v>7.7093330290112269E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4853,7 +4856,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.8028107158541948E-2</v>
+        <v>6.8237885462555076E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -5395,7 +5398,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5430,7 +5433,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5440,7 +5443,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>7.3837172011661796</v>
+        <v>8.0196797144163927</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5450,7 +5453,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>38.730600818416683</v>
+        <v>44.467643925574016</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5459,7 +5462,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>46.114318019582861</v>
+        <v>52.487323639990407</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5485,7 +5488,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.56609220804124138</v>
+        <v>0.50612608654905111</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5499,7 +5502,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5509,7 +5512,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>9.4902958837964402</v>
+        <v>9.9916325637411276</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5519,7 +5522,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>58.527348459637231</v>
+        <v>63.54570237003631</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5528,7 +5531,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>68.017644343433673</v>
+        <v>73.53733493377743</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5554,7 +5557,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35999517853083429</v>
+        <v>0.30805823444907376</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -13390,12 +13393,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.8028107158541948E-2</v>
+        <v>6.8237885462555076E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.8028107158541948E-2</v>
+        <v>6.8237885462555076E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14589,50 +14592,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6856328396378931E-2</v>
+        <v>7.7093330290112269E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.2139927007182356E-2</v>
+        <v>6.2331547927468825E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>8.9066899664368981E-2</v>
+        <v>8.9341555302100528E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.4557304494955854E-2</v>
+        <v>8.4818053892076875E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.7616106029032966E-2</v>
+        <v>6.7824613844981535E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7255168035711809E-2</v>
+        <v>4.7400888818200794E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.0401385435995068E-2</v>
+        <v>6.0587645214872594E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.8320773852907038E-2</v>
+        <v>6.8531454653334503E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.7664898759877042E-2</v>
+        <v>5.7842720033585919E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.1126575735686609E-2</v>
+        <v>5.1284234779805475E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.446724100964445E-2</v>
+        <v>4.4604364660334989E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14646,43 +14649,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4759118107051636E-2</v>
+        <v>6.4958815828086602E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7343498849053092E-2</v>
+        <v>9.7643677039336532E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1210256473270024E-2</v>
+        <v>9.1491521581337387E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2980822533829565E-2</v>
+        <v>7.3205873528427293E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2706775138143859E-2</v>
+        <v>7.293098105266678E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1749779317356377E-2</v>
+        <v>7.1971034143445162E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8833734346714979E-2</v>
+        <v>7.9076833968048474E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.429604653475568E-2</v>
+        <v>6.4494316281779165E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6390096964084972E-2</v>
+        <v>5.6563987130934586E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2118484602370396E-2</v>
+        <v>5.2279202396298421E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18402,7 +18405,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-68.31</v>
+        <v>-68.099999999999994</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18642,7 +18645,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>68.31</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19181,7 +19184,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19190,7 +19193,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>7.3837172011661796</v>
+        <v>8.0196797144163927</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19202,7 +19205,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>38.730600818416683</v>
+        <v>44.467643925574016</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19212,7 +19215,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>46.114318019582861</v>
+        <v>52.487323639990407</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19223,7 +19226,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.56609220804124138</v>
+        <v>0.50612608654905111</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19240,7 +19243,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>68.31</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19253,7 +19256,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21816040050529906</v>
+        <v>0.2194806865769845</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19270,7 +19273,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19279,7 +19282,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>9.4902958837964402</v>
+        <v>9.9916325637411276</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19291,7 +19294,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>58.527348459637231</v>
+        <v>63.54570237003631</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19301,7 +19304,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>68.017644343433673</v>
+        <v>73.53733493377743</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19312,7 +19315,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.35999517853083429</v>
+        <v>0.30805823444907376</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EC0722-3AD7-41C2-B0ED-513F63FBAD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD5531E-2126-4F4C-9692-6DCEA501D435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="462">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2439,9 +2439,6 @@
   </si>
   <si>
     <t>CN</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>洋河股份</t>
@@ -3868,29 +3865,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4218,7 +4215,7 @@
         <v>354</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4249,7 +4246,7 @@
         <v>316</v>
       </c>
       <c r="C5" s="296" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4296,10 +4293,10 @@
         <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
+        <v>454</v>
+      </c>
+      <c r="D11" s="49" t="s">
         <v>455</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>456</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4366,13 +4363,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4393,7 +4390,7 @@
         <v>441</v>
       </c>
       <c r="E21" s="311" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4401,7 +4398,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4414,7 +4411,7 @@
         <v>436</v>
       </c>
       <c r="C23" s="264" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4422,7 +4419,7 @@
         <v>437</v>
       </c>
       <c r="C24" s="264" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -4572,22 +4569,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4599,13 +4596,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4625,13 +4622,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4660,13 +4657,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4682,13 +4679,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4752,13 +4749,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4774,7 +4771,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4796,22 +4793,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4880,22 +4877,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4939,22 +4936,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4991,13 +4988,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5010,13 +5007,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5147,13 +5144,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5192,13 +5189,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5341,13 +5338,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5360,22 +5357,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5708,13 +5705,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5751,13 +5748,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5765,22 +5762,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5804,17 +5801,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5831,6 +5817,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6541,7 +6538,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12380,7 +12377,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12712,7 +12709,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="268" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD5531E-2126-4F4C-9692-6DCEA501D435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE70490-8A1F-40B4-8C29-D40C89D74EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3865,29 +3865,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>68.099999999999994</v>
+        <v>68.13</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>102625.88279999998</v>
+        <v>102671.09243999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,13 +4363,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11076257413104917</v>
+        <v>0.11058922071659794</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4494,7 +4494,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="305">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4569,22 +4569,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4596,13 +4596,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4622,13 +4622,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4657,13 +4657,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4749,13 +4749,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4793,22 +4793,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.314794236784514E-2</v>
+        <v>5.3124539487013844E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.8237885462555076E-2</v>
+        <v>6.8207837956847206E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4877,22 +4877,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4936,22 +4936,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4988,13 +4988,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5007,13 +5007,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5144,13 +5144,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5189,13 +5189,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5338,13 +5338,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5357,22 +5357,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C137" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="C141" s="299">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5705,13 +5705,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5762,22 +5762,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5801,6 +5801,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5817,17 +5828,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.8237885462555076E-2</v>
+        <v>6.8207837956847206E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.8237885462555076E-2</v>
+        <v>6.8207837956847206E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14591,50 +14591,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.314794236784514E-2</v>
+        <v>5.3124539487013844E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.2281858322486935E-2</v>
+        <v>6.2254433461931019E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>8.928035725784933E-2</v>
+        <v>8.9241044022597082E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.4766415975591924E-2</v>
+        <v>8.4729090385113906E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.7789917844528882E-2</v>
+        <v>6.7760067594487258E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7392533509535928E-2</v>
+        <v>4.7371664934674831E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.0581441250092814E-2</v>
+        <v>6.0554765142100703E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.852592681421571E-2</v>
+        <v>6.8495752473918828E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.7842720033585919E-2</v>
+        <v>5.7817249879454004E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.1284234779805475E-2</v>
+        <v>5.1261652554010759E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.4604364660334989E-2</v>
+        <v>4.4584723812840343E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14648,43 +14648,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4958815828086602E-2</v>
+        <v>6.4930212210372776E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7643677039336532E-2</v>
+        <v>9.7600681144559179E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1491521581337387E-2</v>
+        <v>9.145123469380706E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3205873528427293E-2</v>
+        <v>7.3173638445411679E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.293098105266678E-2</v>
+        <v>7.2898867014334456E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1971034143445162E-2</v>
+        <v>7.1939342803003292E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9076833968048474E-2</v>
+        <v>7.9042013697697047E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4494316281779165E-2</v>
+        <v>6.4465917199312509E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6563987130934586E-2</v>
+        <v>5.6539080047213336E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2279202396298421E-2</v>
+        <v>5.2256182051782209E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-68.099999999999994</v>
+        <v>-68.13</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>68.099999999999994</v>
+        <v>68.13</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19242,7 +19242,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>68.099999999999994</v>
+        <v>68.13</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11076257413104917</v>
+        <v>0.11058922071659794</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328D5724-8B48-4E6E-ACFC-54814D2FDEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99BCB97-01F6-4D58-808B-B945FBC3FEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3879,29 +3879,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4319,7 +4319,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>68.13</v>
+        <v>67.75</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>102671.09243999999</v>
+        <v>102098.43700000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4377,13 +4377,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11058922071659794</v>
+        <v>0.11279289592608022</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4508,7 +4508,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4583,22 +4583,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,13 +4610,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4636,13 +4636,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4671,13 +4671,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4693,13 +4693,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4763,13 +4763,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4785,7 +4785,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4807,22 +4807,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.3124539487013844E-2</v>
+        <v>5.3422507383767574E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.8207837956847206E-2</v>
+        <v>6.8590405904059043E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5016,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5068,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,13 +5087,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5215,13 +5215,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5260,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5409,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5428,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5776,13 +5776,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5819,13 +5819,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5833,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5872,6 +5872,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5888,17 +5899,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13463,12 +13463,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.8207837956847206E-2</v>
+        <v>6.8590405904059043E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.8207837956847206E-2</v>
+        <v>6.8590405904059043E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14662,50 +14662,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.3124539487013844E-2</v>
+        <v>5.3422507383767574E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.2254433461931019E-2</v>
+        <v>6.260360962009387E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>8.9241044022597082E-2</v>
+        <v>8.9741584195712751E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.4729090385113906E-2</v>
+        <v>8.5204323659598666E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.7760067594487258E-2</v>
+        <v>6.8140124062175886E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7371664934674831E-2</v>
+        <v>4.7637365785968951E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.0554765142100703E-2</v>
+        <v>6.089440810525934E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.8495752473918828E-2</v>
+        <v>6.8879935292222721E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.7817249879454004E-2</v>
+        <v>5.8141538513464222E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.1261652554010759E-2</v>
+        <v>5.1549171786048009E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.4584723812840343E-2</v>
+        <v>4.4834793112454793E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14719,43 +14719,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4930212210372776E-2</v>
+        <v>6.5294396426460469E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7600681144559179E-2</v>
+        <v>9.8148109319244531E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.145123469380706E-2</v>
+        <v>9.1964171508325837E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3173638445411679E-2</v>
+        <v>7.3584058852928375E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2898867014334456E-2</v>
+        <v>7.3307746268437002E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1939342803003292E-2</v>
+        <v>7.2342840223890995E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9042013697697047E-2</v>
+        <v>7.9485348977477485E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4465917199312509E-2</v>
+        <v>6.4827497251500527E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6539080047213336E-2</v>
+        <v>5.6856199610577779E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2256182051782209E-2</v>
+        <v>5.2549279456648293E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18475,7 +18475,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-68.13</v>
+        <v>-67.75</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>68.13</v>
+        <v>67.75</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19254,7 +19254,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>68.13</v>
+        <v>67.75</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19326,7 +19326,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11058922071659794</v>
+        <v>0.11279289592608022</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99BCB97-01F6-4D58-808B-B945FBC3FEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646FC07-1425-4A98-9F9F-86458285AFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2480,7 +2480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2498,6 +2498,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3146,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3818,36 +3819,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3862,10 +3840,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3877,6 +3851,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4377,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4508,7 +4524,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4583,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,19 +4626,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>7170141860.8562851</v>
       </c>
@@ -4636,19 +4652,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>697421786</v>
       </c>
@@ -4661,7 +4677,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-697421786</v>
       </c>
@@ -4671,19 +4687,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4693,19 +4709,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>118071321.87538444</v>
       </c>
@@ -4720,7 +4736,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-2955080</v>
       </c>
@@ -4735,7 +4751,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>115116241.87538444</v>
       </c>
@@ -4753,7 +4769,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-9589072.5451227482</v>
       </c>
@@ -4763,19 +4779,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-1821314525.6829174</v>
       </c>
@@ -4785,19 +4801,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4807,28 +4823,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>6391730692.7697487</v>
       </c>
@@ -4841,7 +4857,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>5454354504.5036287</v>
       </c>
@@ -4880,10 +4896,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4905,11 +4921,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.29188024664664569</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.3071152608872405</v>
       </c>
@@ -4919,11 +4935,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.37062368553626046</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.42877991347767891</v>
       </c>
@@ -4933,11 +4949,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.3027915865121182</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.3027915865121182</v>
       </c>
@@ -4957,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,19 +5103,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>40134989.460000001</v>
       </c>
@@ -5125,7 +5141,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>7.7640983998987034E-4</v>
       </c>
@@ -5134,7 +5150,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>5.5975167910006915E-3</v>
       </c>
@@ -5148,7 +5164,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>21748297978.369999</v>
       </c>
@@ -5161,7 +5177,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>17616201015.993965</v>
       </c>
@@ -5192,7 +5208,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>3951628136.4709997</v>
       </c>
@@ -5215,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5465,7 +5481,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5500,7 +5516,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5776,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5790,13 +5806,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5819,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6014,399 +6030,399 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>28876296994</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>33126277552</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>30104896187</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>25350178204</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>21101051132</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>23126476885</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>24159801995</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>19917942238</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>17183109620</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>16052444099</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>12577305310</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>13469490847</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>12033845670</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>10403379692</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>9267550366</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>9827842077</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>10123172172</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>7833018393</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>6512546229</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>6344463294</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>7440968847</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>7151376850</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>6114814104</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>5374445029</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>4332884360</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>4548202898</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>4265666731</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>3919595214</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>3451437073</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>3330285076</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>5516238545</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>5386953701</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>4179140808</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>3544364890</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>2603804158</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>2691711171</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>2561401628</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>2387447107</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>1869001822</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>1882406797</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>104796407</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>284753881</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>253574976</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>258458103</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>260094291</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>159965594</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>27565218</v>
       </c>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334">
+      <c r="C11" s="321">
         <v>8812.8943639900008</v>
       </c>
-      <c r="D11" s="334">
+      <c r="D11" s="321">
         <v>12276.83537226</v>
       </c>
-      <c r="E11" s="334">
+      <c r="E11" s="321">
         <v>11766.43425561</v>
       </c>
-      <c r="F11" s="334">
+      <c r="F11" s="321">
         <v>9404.7461288600007</v>
       </c>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>2955080</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>1707108</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>694326</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>603756</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>1964</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>2618</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>3273</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>621439989</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>765369577</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>645806427</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>433923396</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>104495154</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>77589504</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>69133580</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>2476620792</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>3197064563</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>3113885720</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>2433610121</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>2394295578</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>2384713342</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>2723855894</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>2229168424</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>1956036450</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>1800119666</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>6666455820</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>10020768556</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>9389398171</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>7512817397</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>7484606314</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>7386090915</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>8115329895</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>6618786144</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>5804929114</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>5365199298</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>-6932782</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>4838516</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>11565742</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>5134600</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>2377680</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>3268188</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>140100</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>-8383815</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>-22239757</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>13763</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6418,171 +6434,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>697421786</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>730011100</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>752915036</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>759253984</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>782849742</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>776102930</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>757446024</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>4628711237</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>6130220868</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>3647623952</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>15318165481</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>3978790836</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>6797891871</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>9056748816</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>6883169799</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>7405044601</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>5836355329</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-1302245456</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>661034677</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>4016502464</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>1836664314</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>4472834785</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-1293215134</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-3349342124</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-4161022279</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-5964333135</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-3676301732</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-7049805121</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-5608338295</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-4491776979</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-3547817811</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-5504913991</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-4823150583</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-3841359037</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-3417116091</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-3697079125</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-1797917170</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6616,186 +6632,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>1530297140.1800001</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>530005754</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>571147623</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>665097278</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>617721565</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>675347400</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>247961412</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>221297620</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>162441171</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>89745708</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>19732881051.73</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>18954235402</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>17729258967</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>16803093442</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>14852694146</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>14433244696</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>13892118588</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>12861503434</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>12221515305</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>11122379916</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>15652219365.74</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>17742423481</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>20439798531</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>25317393936</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>15396606230</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>16963485271</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>15939249286</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>13763271610</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>12767076382</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>10918840106</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>51693045853.879997</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>52049863975</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>47524448604</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>42481310258</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>38469653077</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>36491552570</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>33624518530</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>29494869092</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>26036985867</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>22941480861</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>104802725.23</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>111348630</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>49501629</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>-4899532</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>-14930907</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>-17282922</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>-20011736</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>-20171194</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>-15785203</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>4384482</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6822,47 +6838,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>28876296994</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>33126277552</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>30104896187</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>25350178204</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>21101051132</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>23126476885</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>24159801995</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>19917942238</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>17183109620</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>16052444099</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6871,47 +6887,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-12577305310</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-13469490847</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-12033845670</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-10403379692</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-9267550366</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-9827842077</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-10123172172</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-7833018393</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-6512546229</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-6344463294</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6920,47 +6936,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>16298991684</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>19656786705</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>18071050517</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>14946798512</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>11833500766</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>13298634808</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>14036629823</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>12084923845</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>10670563391</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>9707980805</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6969,47 +6985,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-7440968847</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-7151376850</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-6114814104</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-5374445029</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-4332884360</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-4548202898</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-4265666731</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-3919595214</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-3451437073</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-3330285076</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7018,47 +7034,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-5516238545</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-5386953701</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-4179140808</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-3544364890</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-2603804158</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-2691711171</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-2561401628</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-2387447107</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-1869001822</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-1882406797</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7067,47 +7083,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-1924730302</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-1764423149</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-1935673296</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-1830080139</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-1729080202</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-1856491727</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-1704265103</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-1532148107</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-1582435251</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-1447878279</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7116,47 +7132,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-104796407</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-284753881</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-253574976</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-258458103</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-260094291</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-159965594</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-27565218</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7165,47 +7181,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>8753226430</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>12220655974</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>11702661437</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>9313895380</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>7240522115</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>8590466316</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>9743397874</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>8165328631</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>7219126318</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>6377695729</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7312,47 +7328,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-2476620792</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-3197064563</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-3113885720</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-2433610121</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-2394295578</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-2384713342</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-2723855894</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-2229168424</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-1956036450</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-1800119666</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7361,47 +7377,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>6666455820</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>10020768556</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>9389398171</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>7512817397</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>7484606314</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>7386090915</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>8115329895</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>6618786144</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>5804929114</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>5365199298</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7410,47 +7426,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-4838516</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>-11565742</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-5134600</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-2377680</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>-3268188</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-140100</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-13763</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7464,47 +7480,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-2955080</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-1707108</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-694326</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-603756</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-1964</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-2618</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-3273</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7513,47 +7529,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>621439989</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>765369577</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>645806427</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>433923396</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>104495154</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>77589504</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>69133580</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7769,47 +7785,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-697421786</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-730011100</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-752915036</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-759253984</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-782849742</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-776102930</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-757446024</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7818,47 +7834,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-697421786</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-730011100</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-752915036</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-759253984</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-782849742</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-776102930</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-757446024</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7867,47 +7883,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7916,47 +7932,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-3723339340</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>1182917250</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>3172349437</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>13607011984</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>2946711630</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>681526154</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>1866047655</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>-694968571</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>-2256367659</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>362136427</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8338,115 +8354,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>1530297140.1800001</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>530005754</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>571147623</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>665097278</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>617721565</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>675347400</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>19732881051.73</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>18954235402</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>17729258967</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>16803093442</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>14852694146</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>14433244696</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>15652219365.74</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>17742423481</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>20439798531</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>25317393936</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>15396606230</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>16963485271</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>15939249286</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>13763271610</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>12767076382</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>10918840106</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8455,47 +8471,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>51693045853.879997</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>52049863975</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>47524448604</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>42481310258</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>38469653077</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>36491552570</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>33624518530</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>29494869092</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>26036985867</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>22941480861</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9579,11 +9595,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-2260503650</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-2066048481.1880178</v>
       </c>
@@ -9611,8 +9627,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>4132096962.3760357</v>
       </c>
@@ -9916,54 +9932,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)*0.85</f>
         <v>24959750399.112499</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>28876296994</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>33126277552</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>30104896187</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>25350178204</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>21101051132</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>23126476885</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>24159801995</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>19917942238</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>17183109620</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>16052444099</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9973,52 +9989,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-15639482394.506214</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-18093543855</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-18856444548</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-16212986478</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-13947744582</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-11871354524</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-12519553248</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-12684573800</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-10220465500</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-8381548051</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-8226870091</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10028,52 +10044,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>9320268004.6062851</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>10782753139</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>14269833004</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>13891909709</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>11402433622</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>9229696608</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>10606923637</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>11475228195</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>9697476738</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>8801561569</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>7825574008</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10083,52 +10099,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-2150126143.75</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-2029526709</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-2049177030</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-2189248272</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-2088538242</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-1989174493</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-2016457321</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-1731830321</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-1532148107</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-1582435251</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-1447878279</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10138,54 +10154,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>7170141860.8562851</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>8753226430</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>12220655974</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>11702661437</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>9313895380</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>7240522115</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>8590466316</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>9743397874</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>8165328631</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>7219126318</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>6377695729</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10195,52 +10211,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>697421786</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>697421786</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>730011100</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>752915036</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>759253984</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>782849742</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>776102930</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>757446024</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10250,52 +10266,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-697421786</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-697421786</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-730011100</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-752915036</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-759253984</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-782849742</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-776102930</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-757446024</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10305,54 +10321,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>8812.8943639900008</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>12276.83537226</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>11766.43425561</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>9404.7461288600007</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10362,52 +10378,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>115116241.87538444</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>115116241.87538444</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>143710308.45080042</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>122006529.85288745</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>81840099.988121659</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>19851732.544706695</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>14739103.587111169</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>13131853.997077813</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10417,52 +10433,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>7285258102.7316694</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>8868351484.7697487</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>12364378559.286173</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>11824679733.287144</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>9395744884.7342491</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>7260373847.5447063</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>8605205419.5871105</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>9756529727.9970779</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>8165328631</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>7219126318</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>6377695729</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10472,52 +10488,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-1821314525.6829174</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-2476620792</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-3197064563</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-3113885720</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-2433610121</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-2394295578</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-2384713342</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-2723855894</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-2229168424</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-1956036450</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-1800119666</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10527,54 +10543,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-9589072.5451227482</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-4838516</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>-11565742</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-5134600</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-2377680</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>-3268188</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-140100</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-13763</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10584,54 +10600,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>5454354504.5036287</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>6391730692.7697487</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>9162475480.2861729</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>8699228271.2871437</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>6957000163.7342491</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>4863700589.5447063</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>6217223889.5871105</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>7032533733.9970779</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>5936160207</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>5263089868</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>4577562300</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10641,7 +10657,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10650,24 +10666,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10675,71 +10691,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>5454354504.5036287</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>6391730692.7697487</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>9162475480.2861729</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>8699228271.2871437</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>6957000163.7342491</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>4863700589.5447063</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>6217223889.5871105</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>7032533733.9970779</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>5936160207</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>5263089868</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>4577562300</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10812,54 +10828,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-10871421681.812622</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-12577305310</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-13469490847</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-12033845670</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-10403379692</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-9267550366</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-9827842077</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-10123172172</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-7833018393</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-6512546229</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-6344463294</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10869,54 +10885,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-4768060712.693593</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-5516238545</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-5386953701</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-4179140808</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-3544364890</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-2603804158</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-2691711171</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-2561401628</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-2387447107</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-1869001822</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-1882406797</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10926,54 +10942,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-15639482394.506214</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-18093543855</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-18856444548</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-16212986478</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-13947744582</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-11871354524</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-12519553248</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-12684573800</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-10220465500</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-8381548051</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-8226870091</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11179,54 +11195,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>G33</f>
         <v>-1924730302</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-1924730302</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-1764423149</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-1935673296</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-1830080139</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-1729080202</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-1856491727</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-1704265103</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-1532148107</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-1582435251</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-1447878279</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11236,7 +11252,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>-225395841.75</v>
       </c>
@@ -11245,47 +11261,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-104796407</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-284753881</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-253574976</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-258458103</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-260094291</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-159965594</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-27565218</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11295,54 +11311,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-2150126143.75</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-2029526709</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-2049177030</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-2189248272</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-2088538242</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-1989174493</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-2016457321</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-1731830321</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-1532148107</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-1582435251</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-1447878279</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11636,52 +11652,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-2955080</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-2955080</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-1707108</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-694326</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-603756</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-1964</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-2618</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-3273</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11691,52 +11707,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>118071321.87538444</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>118071321.87538444</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>145417416.45080042</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>122700855.85288745</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>82443855.988121659</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>19853696.544706695</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>14741721.587111169</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>13135126.997077813</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11746,54 +11762,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>621439989</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>621439989</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>765369577</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>645806427</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>433923396</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>104495154</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>77589504</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>69133580</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11803,52 +11819,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>115116241.87538444</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>115116241.87538444</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>143710308.45080042</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>122006529.85288745</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>81840099.988121659</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>19851732.544706695</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>14739103.587111169</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>13131853.997077813</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11995,52 +12011,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12050,52 +12066,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12105,52 +12121,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>8812.8943639900008</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>12276.83537226</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>11766.43425561</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>9404.7461288600007</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12160,52 +12176,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>8812.8943639900008</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>12276.83537226</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>11766.43425561</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>9404.7461288600007</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12215,53 +12231,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-228643539.894364</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>233502399.16462773</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>155498586.5657444</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>199203093.25387114</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>2533886587</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>1102751055</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>1026657608</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>682625937</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>541839246</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>787623235</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12271,52 +12287,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-228634727</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>233514676</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>155510353</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>199212498</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>2533886587</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>1102751055</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>1026657608</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>682625937</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>541839246</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>787623235</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13691,54 +13707,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>67345265219.619995</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>67345265219.619995</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>69792287456</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>67964247135</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>67798704194</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>53866259307</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>53455037841</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>49563767816</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>43258140702</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>38804062249</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>33860320967</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13748,54 +13764,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>1530297140.1800001</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>530005754</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>571147623</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>665097278</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>617721565</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>675347400</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13805,54 +13821,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>19732881051.73</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>18954235402</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>17729258967</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>16803093442</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>14852694146</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>14433244696</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13862,54 +13878,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>15652219365.74</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>15652219365.74</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>17742423481</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>20439798531</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>25317393936</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>15396606230</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>16963485271</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>15939249286</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>13763271610</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>12767076382</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>10918840106</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13919,54 +13935,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>51693045853.879997</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>51693045853.879997</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>52049863975</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>47524448604</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>42481310258</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>38469653077</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>36491552570</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>33624518530</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>29494869092</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>26036985867</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>22941480861</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15464,7 +15480,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15503,7 +15519,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>5454354504.5036287</v>
       </c>
@@ -15535,7 +15551,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>90905908408.393814</v>
       </c>
@@ -15543,17 +15559,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>40134989.460000001</v>
       </c>
@@ -15561,15 +15577,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>17616201015.993965</v>
       </c>
@@ -15577,15 +15593,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>3951628136.4709997</v>
       </c>
@@ -15593,15 +15609,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>112433602571.39876</v>
       </c>
@@ -15668,7 +15684,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15678,7 +15694,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15692,10 +15708,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15713,7 +15729,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15735,7 +15751,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15757,7 +15773,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15777,9 +15793,19 @@
         <f t="shared" si="1"/>
         <v>4834395137.1687813</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15799,9 +15825,19 @@
         <f t="shared" si="1"/>
         <v>4643816732.6833992</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15821,9 +15857,19 @@
         <f t="shared" si="1"/>
         <v>4460751187.040884</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15845,7 +15891,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15867,7 +15913,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15889,7 +15935,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15911,7 +15957,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15933,7 +15979,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15955,7 +16001,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15977,11 +16023,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15997,13 +16043,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16019,13 +16075,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16041,9 +16107,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16065,7 +16141,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16087,7 +16163,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16109,7 +16185,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16131,7 +16207,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16153,7 +16229,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16175,7 +16251,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16197,7 +16273,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16219,7 +16295,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16241,7 +16317,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16263,7 +16339,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16285,11 +16361,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16305,13 +16381,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16327,13 +16413,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16349,13 +16445,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16371,9 +16477,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16395,7 +16511,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16406,11 +16522,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16420,7 +16536,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>95697646460.255325</v>
@@ -16447,7 +16563,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16469,7 +16585,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16490,14 +16606,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>74034788284.016418</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>90905908408.393738</v>
       </c>
       <c r="D58" s="123">
@@ -16509,16 +16625,26 @@
       <c r="F58" s="123">
         <v>128857518867.44797</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>68768063977.719452</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>90905908408.393738</v>
       </c>
       <c r="D59" s="123">
@@ -16530,16 +16656,26 @@
       <c r="F59" s="123">
         <v>150895861004.93069</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>64183180813.607864</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>90905908408.393738</v>
       </c>
       <c r="D60" s="123">
@@ -16551,16 +16687,26 @@
       <c r="F60" s="123">
         <v>177079273843.49899</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>60381666306.674995</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>90905908408.393738</v>
       </c>
       <c r="D61" s="123">
@@ -16572,26 +16718,56 @@
       <c r="F61" s="123">
         <v>206827111547.89767</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.05</v>
@@ -16963,6 +17139,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17065,7 +17311,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>116716220600</v>
       </c>
@@ -17073,8 +17319,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18531,7 +18777,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>8753226430</v>
       </c>
@@ -18539,11 +18785,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 洋河股份(002304.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18556,7 +18802,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>6391730692.7697487</v>
       </c>
@@ -18564,8 +18810,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18578,7 +18824,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>5454354504.5036287</v>
       </c>
@@ -18586,8 +18832,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18597,8 +18843,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18611,8 +18857,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18630,8 +18876,8 @@
         <v>4.4367851108990219E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18648,8 +18894,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.0482342685147259E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18666,8 +18912,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7852527100317714E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18693,21 +18939,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18721,8 +18967,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18736,8 +18982,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18757,8 +19003,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18768,8 +19014,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18783,8 +19029,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18794,8 +19040,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18815,8 +19061,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18826,8 +19072,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18841,8 +19087,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18852,8 +19098,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18873,8 +19119,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18884,8 +19130,8 @@
         <v>0.04</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18899,8 +19145,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18911,8 +19157,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18974,8 +19220,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18985,8 +19231,8 @@
         <v>-0.05</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19000,8 +19246,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19011,8 +19257,8 @@
         <v>0.1</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19032,8 +19278,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19043,8 +19289,8 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19058,8 +19304,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19069,8 +19315,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19254,7 +19500,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646FC07-1425-4A98-9F9F-86458285AFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C190539-97FE-4717-8BD8-069E97A6D493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,29 +3895,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4335,7 +4335,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>67.75</v>
+        <v>67.33</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>102098.43700000001</v>
+        <v>101465.50204000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4393,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11279289592608022</v>
+        <v>0.11524858955270134</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4524,7 +4524,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4599,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4626,13 +4626,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4652,13 +4652,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4687,13 +4687,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4709,13 +4709,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4779,13 +4779,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4801,7 +4801,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4823,22 +4823,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.3422507383767574E-2</v>
+        <v>5.3755753382596957E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.8590405904059043E-2</v>
+        <v>6.9018268231100549E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5032,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5084,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5103,13 +5103,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5231,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5276,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5425,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5444,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5792,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5835,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5849,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5888,17 +5888,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5915,6 +5904,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.8590405904059043E-2</v>
+        <v>6.9018268231100549E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.8590405904059043E-2</v>
+        <v>6.9018268231100549E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14678,50 +14678,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.3422507383767574E-2</v>
+        <v>5.3755753382596957E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.260360962009387E-2</v>
+        <v>6.2994126715600174E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>8.9741584195712751E-2</v>
+        <v>9.0301386146733081E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.5204323659598666E-2</v>
+        <v>8.5735822485338037E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.8140124062175886E-2</v>
+        <v>6.8565177561449822E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7637365785968951E-2</v>
+        <v>4.7934524461598044E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.089440810525934E-2</v>
+        <v>6.1274263316965998E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.8879935292222721E-2</v>
+        <v>6.9309603684064899E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.8141538513464222E-2</v>
+        <v>5.8504221510280723E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.1549171786048009E-2</v>
+        <v>5.1870732043736115E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.4834793112454793E-2</v>
+        <v>4.5114469528721411E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14735,43 +14735,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5294396426460469E-2</v>
+        <v>6.5701698468627612E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8148109319244531E-2</v>
+        <v>9.8760350607141195E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1964171508325837E-2</v>
+        <v>9.2537837809135229E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3584058852928375E-2</v>
+        <v>7.4043071250347509E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3307746268437002E-2</v>
+        <v>7.3765035046585575E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2342840223890995E-2</v>
+        <v>7.2794109983196409E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9485348977477485E-2</v>
+        <v>7.9981173224774993E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4827497251500527E-2</v>
+        <v>6.5231886808096856E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6856199610577779E-2</v>
+        <v>5.7210864749987295E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2549279456648293E-2</v>
+        <v>5.2877078318549264E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-67.75</v>
+        <v>-67.33</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>67.75</v>
+        <v>67.33</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19500,7 +19500,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>67.75</v>
+        <v>67.33</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11279289592608022</v>
+        <v>0.11524858955270134</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6663194-2B34-46F0-908E-87D60A16DD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A319D9D-5754-D34D-9758-E82615BA4C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2510,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3891,30 +3902,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3929,7 +3940,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4218,16 +4229,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4244,7 +4255,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4258,7 +4269,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4267,7 +4278,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4275,7 +4286,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4284,7 +4295,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4294,7 +4305,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4304,17 +4315,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4326,17 +4337,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>66.7</v>
+        <v>65.98</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4346,13 +4357,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>100516.0996</v>
+        <v>99431.068239999993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4360,7 +4371,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4374,7 +4385,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4384,27 +4395,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4419,7 +4430,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4432,7 +4443,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4440,7 +4451,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4448,7 +4459,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4464,7 +4475,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4478,14 +4489,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11897228741021948</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.1232882180025836</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4504,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4520,10 +4531,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4542,7 +4553,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4561,7 +4572,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4580,11 +4591,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4594,25 +4605,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4621,16 +4632,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4643,20 +4654,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4682,16 +4693,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4704,16 +4715,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4728,7 +4739,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4743,7 +4754,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4756,12 +4767,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4774,16 +4785,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4796,8 +4807,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4805,7 +4816,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4818,25 +4829,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4849,7 +4860,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4862,23 +4873,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.4263491383062266E-2</v>
+        <v>5.4855636181422453E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.967016491754123E-2</v>
+        <v>7.0430433464686262E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4888,7 +4899,7 @@
         <v>1.2839233735573452</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4899,7 +4910,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4912,7 +4923,7 @@
         <v>0.17155792115322036</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4926,7 +4937,7 @@
         <v>0.3071152608872405</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4940,7 +4951,7 @@
         <v>0.42877991347767891</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4954,7 +4965,7 @@
         <v>1.3027915865121182</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4964,34 +4975,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5000,7 +5011,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5018,34 +5029,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5053,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5066,7 +5077,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5076,38 +5087,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5120,7 +5131,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5133,7 +5144,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5142,7 +5153,7 @@
         <v>7.7640983998987034E-4</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5151,12 +5162,12 @@
         <v>5.5975167910006915E-3</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5169,7 +5180,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5182,7 +5193,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5195,12 +5206,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5213,7 +5224,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5226,16 +5237,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5248,7 +5259,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5261,7 +5272,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5271,16 +5282,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5297,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5319,7 +5330,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5341,7 +5352,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5363,7 +5374,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5385,7 +5396,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5407,7 +5418,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5420,16 +5431,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5439,30 +5450,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5471,16 +5482,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5493,7 +5504,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5506,16 +5517,16 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5525,7 +5536,7 @@
         <v>8.0196797144163927</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5535,7 +5546,7 @@
         <v>32.546553796162996</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5548,7 +5559,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5561,7 +5572,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5570,12 +5581,12 @@
         <v>0.47848662078609472</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5584,7 +5595,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5594,7 +5605,7 @@
         <v>9.9916325637411276</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5604,7 +5615,7 @@
         <v>46.510078747659925</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5617,7 +5628,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5639,12 +5650,12 @@
         <v>0.27362252180270386</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5653,7 +5664,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5663,7 +5674,7 @@
         <v>12.421486529148241</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5673,7 +5684,7 @@
         <v>65.310293566799118</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5686,7 +5697,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5699,7 +5710,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5708,12 +5719,12 @@
         <v>6.9195974091051937E-4</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5722,7 +5733,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5732,7 +5743,7 @@
         <v>11.826104101614131</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5742,7 +5753,7 @@
         <v>60.563448972324863</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5755,7 +5766,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5768,7 +5779,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5777,7 +5788,7 @@
         <v>6.9397561757708282E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5787,21 +5798,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5810,80 +5821,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5922,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5941,15 +5952,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5998,7 +6009,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6014,7 +6025,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6022,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6058,7 +6069,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6094,7 +6105,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6130,7 +6141,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6166,7 +6177,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6196,7 +6207,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6212,7 +6223,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6228,7 +6239,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6252,7 +6263,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6282,7 +6293,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6312,7 +6323,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6348,7 +6359,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6384,7 +6395,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6420,13 +6431,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6456,7 +6467,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6472,7 +6483,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6488,7 +6499,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6524,7 +6535,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6560,7 +6571,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6596,7 +6607,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6616,7 +6627,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6624,7 +6635,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6661,7 +6672,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6698,7 +6709,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6735,7 +6746,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6772,7 +6783,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6809,7 +6820,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6825,12 +6836,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6879,7 +6890,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6928,7 +6939,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6977,7 +6988,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7026,7 +7037,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7075,7 +7086,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7124,7 +7135,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7173,7 +7184,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7222,7 +7233,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7271,7 +7282,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7320,7 +7331,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7369,7 +7380,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7418,7 +7429,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7467,12 +7478,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7521,7 +7532,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7570,12 +7581,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7624,7 +7635,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7673,7 +7684,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7722,7 +7733,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7771,13 +7782,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7826,7 +7837,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7875,7 +7886,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7924,7 +7935,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7973,7 +7984,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8022,12 +8033,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8077,7 +8088,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8126,7 +8137,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8176,7 +8187,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8225,7 +8236,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8275,7 +8286,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8291,13 +8302,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8346,7 +8357,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8380,7 +8391,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8414,7 +8425,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8463,7 +8474,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8544,18 +8555,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8571,7 +8582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8582,7 +8593,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8602,7 +8613,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8624,7 +8635,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8645,7 +8656,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8666,7 +8677,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8687,7 +8698,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8708,7 +8719,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8729,7 +8740,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8741,7 +8752,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8753,7 +8764,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8777,12 +8788,12 @@
         <v>23401555442.817001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8802,7 +8813,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8822,7 +8833,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8842,7 +8853,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8862,7 +8873,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8882,7 +8893,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8903,7 +8914,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8923,7 +8934,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8943,7 +8954,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8956,7 +8967,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8969,7 +8980,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8993,7 +9004,7 @@
         <v>123540874.18699999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9010,7 +9021,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9029,7 +9040,7 @@
         <v>23138515188.125008</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9044,7 +9055,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9063,7 +9074,7 @@
         <v>23033712462.895008</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9079,7 +9090,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9096,7 +9107,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9116,7 +9127,7 @@
         <v>38790734553.865005</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9127,7 +9138,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9140,7 +9151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9159,7 +9170,7 @@
         <v>15265638236.861</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9175,7 +9186,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9191,7 +9202,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9207,7 +9218,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9226,7 +9237,7 @@
         <v>755103420.58799994</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9246,7 +9257,7 @@
         <v>23525096317.004002</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9266,7 +9277,7 @@
         <v>19573468180.533001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9285,7 +9296,7 @@
         <v>3951628136.4709997</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9296,7 +9307,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9310,7 +9321,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9324,7 +9335,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9339,10 +9350,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9355,7 +9366,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9369,7 +9380,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9380,10 +9391,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9395,7 +9406,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9409,7 +9420,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9423,10 +9434,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9438,7 +9449,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9449,7 +9460,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9460,10 +9471,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9475,7 +9486,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9491,7 +9502,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9502,7 +9513,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9516,7 +9527,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9532,7 +9543,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9542,7 +9553,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9552,7 +9563,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9562,7 +9573,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9572,10 +9583,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9587,7 +9598,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9603,7 +9614,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9619,7 +9630,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9632,7 +9643,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9645,10 +9656,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9660,7 +9671,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9674,7 +9685,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9688,7 +9699,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9702,7 +9713,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9716,7 +9727,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9727,7 +9738,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9735,7 +9746,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9752,7 +9763,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9769,7 +9780,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9786,7 +9797,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9817,19 +9828,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9886,7 +9897,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9909,7 +9920,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9923,7 +9934,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9980,7 +9991,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10035,7 +10046,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10090,7 +10101,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10145,7 +10156,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10202,7 +10213,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10257,7 +10268,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10312,7 +10323,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10369,7 +10380,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10424,7 +10435,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10479,7 +10490,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10534,7 +10545,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10591,7 +10602,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10648,7 +10659,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10674,7 +10685,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10699,7 +10710,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10756,7 +10767,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10775,7 +10786,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10798,7 +10809,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10819,7 +10830,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10876,7 +10887,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10933,7 +10944,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10990,18 +11001,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11060,7 +11071,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11120,7 +11131,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11175,18 +11186,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11243,7 +11254,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11302,7 +11313,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11359,18 +11370,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11428,7 +11439,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11486,7 +11497,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11541,18 +11552,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11610,10 +11621,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11636,14 +11647,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11698,7 +11709,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11753,7 +11764,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11810,7 +11821,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11865,11 +11876,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11879,7 +11890,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11906,7 +11917,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11933,7 +11944,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11988,11 +11999,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12002,7 +12013,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12057,7 +12068,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12112,7 +12123,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12167,7 +12178,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12222,7 +12233,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12278,7 +12289,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12333,11 +12344,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12347,7 +12358,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12372,7 +12383,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12397,7 +12408,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12422,7 +12433,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12449,10 +12460,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12475,7 +12486,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12496,7 +12507,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12553,7 +12564,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12610,7 +12621,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12667,7 +12678,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12724,7 +12735,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12781,7 +12792,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12840,7 +12851,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12897,7 +12908,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12954,7 +12965,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13011,7 +13022,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13068,7 +13079,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13126,7 +13137,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13183,7 +13194,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13209,7 +13220,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13233,7 +13244,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13290,18 +13301,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13357,7 +13368,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13413,7 +13424,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13468,19 +13479,19 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.967016491754123E-2</v>
+        <v>7.0430433464686262E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.967016491754123E-2</v>
+        <v>7.0430433464686262E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13523,11 +13534,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13548,7 +13559,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13605,7 +13616,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13662,10 +13673,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13688,7 +13699,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13698,7 +13709,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13755,7 +13766,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13812,7 +13823,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13869,7 +13880,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13926,7 +13937,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13983,11 +13994,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14010,7 +14021,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14067,7 +14078,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14124,7 +14135,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14151,18 +14162,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14214,7 +14225,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14266,11 +14277,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14324,7 +14335,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14379,7 +14390,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14433,7 +14444,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14489,7 +14500,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14546,7 +14557,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14565,7 +14576,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14588,7 +14599,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14609,7 +14620,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14667,795 +14678,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.4263491383062266E-2</v>
+        <v>5.4855636181422453E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.3589123714563114E-2</v>
+        <v>6.4283033521693844E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.1154307785000568E-2</v>
+        <v>9.2149019843278848E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.6545621108512882E-2</v>
+        <v>8.7490041344919819E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.9212794680845818E-2</v>
+        <v>6.9968072222073602E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.8387279340320784E-2</v>
+        <v>4.891530057592295E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.1853015729105253E-2</v>
+        <v>6.2527980435454988E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>6.9964252114664005E-2</v>
+        <v>7.0727729858261423E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.9056810109253385E-2</v>
+        <v>5.9701261507838749E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.2360665494823877E-2</v>
+        <v>5.2932045900344837E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.5540588206428971E-2</v>
+        <v>4.6037545216259655E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6322269233773573E-2</v>
+        <v>6.7046004211771704E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9693169510926785E-2</v>
+        <v>0.10078106102423183</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3411883353659297E-2</v>
+        <v>9.4431230974372157E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4742428594990973E-2</v>
+        <v>7.5558047700604689E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4461766262168022E-2</v>
+        <v>7.5274322668787613E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3481670542258085E-2</v>
+        <v>7.4283531754601617E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0736617589566712E-2</v>
+        <v>8.1617647669355864E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5848020071801516E-2</v>
+        <v>6.6566579854337088E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7751237235631851E-2</v>
+        <v>5.8381441703798796E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3376516989324163E-2</v>
+        <v>5.3958982770353471E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15477,16 +15488,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15498,7 +15509,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15511,7 +15522,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15532,7 +15543,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15543,7 +15554,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15561,7 +15572,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15577,7 +15588,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15593,7 +15604,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15609,7 +15620,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15623,7 +15634,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15637,7 +15648,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15651,10 +15662,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15664,13 +15675,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15680,7 +15691,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15690,7 +15701,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15704,10 +15715,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15725,7 +15736,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15747,7 +15758,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15769,7 +15780,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15801,7 +15812,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15833,7 +15844,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15865,7 +15876,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15887,7 +15898,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15909,7 +15920,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15931,7 +15942,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15953,7 +15964,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15975,7 +15986,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15997,7 +16008,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16019,7 +16030,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16051,7 +16062,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16083,7 +16094,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16115,7 +16126,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16137,7 +16148,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16159,7 +16170,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16181,7 +16192,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16203,7 +16214,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16225,7 +16236,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16247,7 +16258,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16269,7 +16280,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16291,7 +16302,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16313,7 +16324,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16335,7 +16346,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16357,7 +16368,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16389,7 +16400,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16421,7 +16432,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16453,7 +16464,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16485,7 +16496,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16507,7 +16518,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16518,11 +16529,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16532,7 +16543,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>95697646460.255325</v>
@@ -16559,7 +16570,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16581,7 +16592,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16602,7 +16613,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16633,7 +16644,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16664,7 +16675,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16695,7 +16706,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16726,7 +16737,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16743,7 +16754,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16763,7 +16774,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.05</v>
@@ -16786,7 +16797,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16812,7 +16823,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16839,7 +16850,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16866,7 +16877,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16893,7 +16904,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16920,7 +16931,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16946,7 +16957,7 @@
         <v>131.7906765060531</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16972,7 +16983,7 @@
         <v>151.53060655486485</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16989,7 +17000,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17011,7 +17022,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17034,7 +17045,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17057,7 +17068,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17080,7 +17091,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17102,14 +17113,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17117,26 +17128,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17150,7 +17161,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17164,7 +17175,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17178,7 +17189,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17192,7 +17203,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17237,16 +17248,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17258,7 +17269,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17271,7 +17282,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17292,7 +17303,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17303,7 +17314,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17319,7 +17330,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17333,10 +17344,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17346,13 +17357,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17362,7 +17373,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17372,7 +17383,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17386,10 +17397,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17407,7 +17418,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17429,7 +17440,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17451,7 +17462,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17473,7 +17484,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17495,7 +17506,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17517,7 +17528,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17539,7 +17550,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17561,7 +17572,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17583,7 +17594,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17605,7 +17616,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17627,7 +17638,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17649,7 +17660,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17671,7 +17682,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17693,7 +17704,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17715,7 +17726,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17737,7 +17748,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17759,7 +17770,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17781,7 +17792,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17803,7 +17814,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17825,7 +17836,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17847,7 +17858,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17869,7 +17880,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17891,7 +17902,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17913,7 +17924,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17935,7 +17946,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17957,7 +17968,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17979,7 +17990,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18001,7 +18012,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18023,7 +18034,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18045,7 +18056,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18067,7 +18078,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18089,7 +18100,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18100,11 +18111,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18114,7 +18125,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>122868445084.74913</v>
@@ -18141,7 +18152,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18163,7 +18174,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18184,7 +18195,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18205,7 +18216,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18226,7 +18237,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18247,7 +18258,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18268,14 +18279,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18285,7 +18296,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>-0.05</v>
@@ -18308,7 +18319,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18334,7 +18345,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18361,7 +18372,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18388,7 +18399,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18415,7 +18426,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18442,7 +18453,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18468,7 +18479,7 @@
         <v>150.86796886254572</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18494,7 +18505,7 @@
         <v>176.2125264446021</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18511,7 +18522,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18533,7 +18544,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18556,7 +18567,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18579,7 +18590,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18602,7 +18613,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18624,14 +18635,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18639,23 +18650,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18685,17 +18696,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18708,7 +18719,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18717,10 +18728,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-66.7</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-65.98</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18740,7 +18751,7 @@
         <v>4.6470000000000002</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18749,7 +18760,7 @@
         <v>4.6470000000000002</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18769,7 +18780,7 @@
         <v>82.43260460275485</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18794,7 +18805,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18816,7 +18827,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18838,7 +18849,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18849,7 +18860,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18863,7 +18874,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18882,7 +18893,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18900,7 +18911,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18911,7 +18922,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18920,7 +18931,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18928,7 +18939,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18940,24 +18951,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>66.7</v>
+        <v>65.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18966,7 +18977,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18981,7 +18992,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18990,7 +19001,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19002,7 +19013,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19013,7 +19024,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19028,7 +19039,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19039,7 +19050,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19048,7 +19059,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19060,7 +19071,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19071,7 +19082,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19086,7 +19097,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19097,7 +19108,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19106,7 +19117,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19118,7 +19129,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19129,7 +19140,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19144,7 +19155,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19156,7 +19167,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19169,7 +19180,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19178,12 +19189,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19193,12 +19204,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19207,7 +19218,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19219,7 +19230,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19230,7 +19241,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19245,7 +19256,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19256,7 +19267,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19265,7 +19276,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19277,7 +19288,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19288,7 +19299,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19303,7 +19314,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19314,7 +19325,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19334,7 +19345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19343,7 +19354,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19351,7 +19362,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19364,7 +19375,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19376,7 +19387,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19392,7 +19403,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19400,7 +19411,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19410,7 +19421,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19422,7 +19433,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19432,7 +19443,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19448,7 +19459,7 @@
         <v>0.18364896670378619</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19457,12 +19468,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19472,7 +19483,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19485,21 +19496,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19511,7 +19522,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19521,7 +19532,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19541,45 +19552,45 @@
         <v>0.47848662078609472</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>66.7</v>
+        <v>65.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11897228741021948</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.1232882180025836</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19588,7 +19599,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19600,7 +19611,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19610,7 +19621,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19630,14 +19641,14 @@
         <v>0.27362252180270386</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19648,7 +19659,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19660,7 +19671,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19672,7 +19683,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19691,15 +19702,15 @@
         <v>6.9195974091051937E-4</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19708,7 +19719,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19718,7 +19729,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19728,7 +19739,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19747,16 +19758,16 @@
         <v>6.9397561757708282E-2</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19764,7 +19775,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19772,7 +19783,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A319D9D-5754-D34D-9758-E82615BA4C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B42F87F-2EFC-4B95-B2DE-CD4C5F231B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2510,7 +2499,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3902,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3940,7 +3929,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4229,7 +4218,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4238,7 +4227,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4255,7 +4244,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4269,7 +4258,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4278,7 +4267,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4286,7 +4275,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4295,7 +4284,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4305,7 +4294,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4315,17 +4304,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4337,17 +4326,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>65.98</v>
+        <v>65.66</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4357,13 +4346,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>99431.068239999993</v>
+        <v>98948.832079999993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4371,7 +4360,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4385,7 +4374,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4395,27 +4384,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4430,7 +4419,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4443,7 +4432,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4451,7 +4440,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4459,7 +4448,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4475,7 +4464,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4489,14 +4478,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1232882180025836</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.12522746818781161</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4515,7 +4504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4534,7 +4523,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4553,7 +4542,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4572,7 +4561,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4591,11 +4580,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4605,25 +4594,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4632,16 +4621,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4654,20 +4643,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4680,7 +4669,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4693,16 +4682,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4715,16 +4704,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4739,7 +4728,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4754,7 +4743,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4767,12 +4756,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4785,16 +4774,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4807,8 +4796,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4816,7 +4805,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4829,25 +4818,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4860,7 +4849,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4873,23 +4862,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.4855636181422453E-2</v>
+        <v>5.5122980128697124E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.0430433464686262E-2</v>
+        <v>7.077368260737131E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4899,7 +4888,7 @@
         <v>1.2839233735573452</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4910,7 +4899,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4923,7 +4912,7 @@
         <v>0.17155792115322036</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4937,7 +4926,7 @@
         <v>0.3071152608872405</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4951,7 +4940,7 @@
         <v>0.42877991347767891</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4965,7 +4954,7 @@
         <v>1.3027915865121182</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4975,34 +4964,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5011,7 +5000,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5020,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5029,34 +5018,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5064,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5077,7 +5066,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5087,38 +5076,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5131,7 +5120,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5144,7 +5133,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5153,7 +5142,7 @@
         <v>7.7640983998987034E-4</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5162,12 +5151,12 @@
         <v>5.5975167910006915E-3</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5180,7 +5169,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5206,12 +5195,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5224,7 +5213,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5237,16 +5226,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5259,7 +5248,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5272,7 +5261,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5282,16 +5271,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5308,7 +5297,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5330,7 +5319,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5352,7 +5341,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5374,7 +5363,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5396,7 +5385,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5418,7 +5407,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5431,16 +5420,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5450,30 +5439,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5482,7 +5471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5491,7 +5480,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5504,7 +5493,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5517,7 +5506,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5526,7 +5515,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5536,7 +5525,7 @@
         <v>8.0196797144163927</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5546,7 +5535,7 @@
         <v>32.546553796162996</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5559,7 +5548,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5572,7 +5561,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5581,12 +5570,12 @@
         <v>0.47848662078609472</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5595,7 +5584,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5605,7 +5594,7 @@
         <v>9.9916325637411276</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5615,7 +5604,7 @@
         <v>46.510078747659925</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5628,7 +5617,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5641,7 +5630,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5650,12 +5639,12 @@
         <v>0.27362252180270386</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5664,7 +5653,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5674,7 +5663,7 @@
         <v>12.421486529148241</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5684,7 +5673,7 @@
         <v>65.310293566799118</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5697,7 +5686,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5710,7 +5699,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5719,12 +5708,12 @@
         <v>6.9195974091051937E-4</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5733,7 +5722,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5743,7 +5732,7 @@
         <v>11.826104101614131</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5753,7 +5742,7 @@
         <v>60.563448972324863</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5766,7 +5755,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5779,7 +5768,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5788,7 +5777,7 @@
         <v>6.9397561757708282E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5798,21 +5787,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5821,91 +5810,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5922,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5952,15 +5941,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6009,7 +5998,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6025,7 +6014,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6033,7 +6022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6069,7 +6058,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6105,7 +6094,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6141,7 +6130,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6177,7 +6166,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6207,7 +6196,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6223,7 +6212,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6239,7 +6228,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6263,7 +6252,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6293,7 +6282,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6323,7 +6312,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6359,7 +6348,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6395,7 +6384,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6431,13 +6420,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6467,7 +6456,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6483,7 +6472,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6499,7 +6488,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6535,7 +6524,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6571,7 +6560,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6607,7 +6596,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6627,7 +6616,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6635,7 +6624,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6672,7 +6661,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6709,7 +6698,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6746,7 +6735,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6783,7 +6772,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6820,7 +6809,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6836,12 +6825,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6890,7 +6879,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6939,7 +6928,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6988,7 +6977,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7037,7 +7026,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7086,7 +7075,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7135,7 +7124,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7184,7 +7173,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7233,7 +7222,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7282,7 +7271,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7331,7 +7320,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7380,7 +7369,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7429,7 +7418,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7478,12 +7467,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7532,7 +7521,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7581,12 +7570,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7635,7 +7624,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7684,7 +7673,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7733,7 +7722,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7782,13 +7771,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7837,7 +7826,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7886,7 +7875,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7935,7 +7924,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7984,7 +7973,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8033,12 +8022,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8088,7 +8077,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8137,7 +8126,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8187,7 +8176,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8236,7 +8225,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8286,7 +8275,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8302,13 +8291,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8357,7 +8346,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8391,7 +8380,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8425,7 +8414,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8474,7 +8463,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8555,7 +8544,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8566,7 +8555,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8582,7 +8571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8593,7 +8582,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8613,7 +8602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8635,7 +8624,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8656,7 +8645,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8677,7 +8666,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8698,7 +8687,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8719,7 +8708,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8740,7 +8729,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8752,7 +8741,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8764,7 +8753,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8788,12 +8777,12 @@
         <v>23401555442.817001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8813,7 +8802,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8833,7 +8822,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8853,7 +8842,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8873,7 +8862,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8893,7 +8882,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8914,7 +8903,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8934,7 +8923,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8954,7 +8943,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8967,7 +8956,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8980,7 +8969,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9004,7 +8993,7 @@
         <v>123540874.18699999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9021,7 +9010,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9040,7 +9029,7 @@
         <v>23138515188.125008</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9055,7 +9044,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9074,7 +9063,7 @@
         <v>23033712462.895008</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9090,7 +9079,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9107,7 +9096,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9127,7 +9116,7 @@
         <v>38790734553.865005</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9138,7 +9127,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9151,7 +9140,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9170,7 +9159,7 @@
         <v>15265638236.861</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9186,7 +9175,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9202,7 +9191,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9218,7 +9207,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9237,7 +9226,7 @@
         <v>755103420.58799994</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9257,7 +9246,7 @@
         <v>23525096317.004002</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9277,7 +9266,7 @@
         <v>19573468180.533001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9296,7 +9285,7 @@
         <v>3951628136.4709997</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9307,7 +9296,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9321,7 +9310,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9335,7 +9324,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9350,10 +9339,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9366,7 +9355,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9380,7 +9369,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9391,10 +9380,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9406,7 +9395,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9420,7 +9409,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9434,10 +9423,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9449,7 +9438,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9460,7 +9449,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9471,10 +9460,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9486,7 +9475,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9502,7 +9491,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9513,7 +9502,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9527,7 +9516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9543,7 +9532,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9553,7 +9542,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9563,7 +9552,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9573,7 +9562,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9583,10 +9572,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9598,7 +9587,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9614,7 +9603,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9630,7 +9619,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9643,7 +9632,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9656,10 +9645,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9671,7 +9660,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9685,7 +9674,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9699,7 +9688,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9713,7 +9702,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9727,7 +9716,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9738,7 +9727,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9746,7 +9735,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9763,7 +9752,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9780,7 +9769,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9797,7 +9786,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9828,19 +9817,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9897,7 +9886,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9920,7 +9909,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9934,7 +9923,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9991,7 +9980,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10046,7 +10035,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10101,7 +10090,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10156,7 +10145,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10213,7 +10202,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10268,7 +10257,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10323,7 +10312,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10380,7 +10369,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10435,7 +10424,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10490,7 +10479,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10545,7 +10534,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10602,7 +10591,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10659,7 +10648,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10685,7 +10674,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10710,7 +10699,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10767,7 +10756,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10786,7 +10775,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10809,7 +10798,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10830,7 +10819,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10887,7 +10876,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10944,7 +10933,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11001,18 +10990,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11071,7 +11060,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11131,7 +11120,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11186,18 +11175,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11254,7 +11243,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11313,7 +11302,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11370,18 +11359,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11439,7 +11428,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11497,7 +11486,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11552,18 +11541,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11621,10 +11610,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11647,14 +11636,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11709,7 +11698,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11764,7 +11753,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11821,7 +11810,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11876,11 +11865,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11890,7 +11879,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11917,7 +11906,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11944,7 +11933,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11999,11 +11988,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12013,7 +12002,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12068,7 +12057,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12123,7 +12112,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12178,7 +12167,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12233,7 +12222,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12289,7 +12278,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12344,11 +12333,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12358,7 +12347,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12383,7 +12372,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12408,7 +12397,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12433,7 +12422,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12460,10 +12449,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12486,7 +12475,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12507,7 +12496,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12564,7 +12553,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12621,7 +12610,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12678,7 +12667,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12735,7 +12724,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12792,7 +12781,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12851,7 +12840,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12908,7 +12897,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12965,7 +12954,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13022,7 +13011,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13079,7 +13068,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13137,7 +13126,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13194,7 +13183,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13220,7 +13209,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13244,7 +13233,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13301,18 +13290,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13368,7 +13357,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13424,7 +13413,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13479,19 +13468,19 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.0430433464686262E-2</v>
+        <v>7.077368260737131E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.0430433464686262E-2</v>
+        <v>7.077368260737131E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13534,11 +13523,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13559,7 +13548,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13616,7 +13605,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13673,10 +13662,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13699,7 +13688,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13709,7 +13698,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13766,7 +13755,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13823,7 +13812,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13880,7 +13869,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13937,7 +13926,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13994,11 +13983,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14021,7 +14010,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14078,7 +14067,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14135,7 +14124,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14162,18 +14151,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14225,7 +14214,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14277,11 +14266,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14335,7 +14324,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14390,7 +14379,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14444,7 +14433,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14500,7 +14489,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14557,7 +14546,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14576,7 +14565,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14599,7 +14588,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14620,7 +14609,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14678,795 +14667,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.4855636181422453E-2</v>
+        <v>5.5122980128697124E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.4283033521693844E-2</v>
+        <v>6.4596322749944562E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.2149019843278848E-2</v>
+        <v>9.2598116498013083E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.7490041344919819E-2</v>
+        <v>8.7916432042915174E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.9968072222073602E-2</v>
+        <v>7.0309068005062703E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.891530057592295E-2</v>
+        <v>4.9153693755702048E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.2527980435454988E-2</v>
+        <v>6.2832716252380766E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.0727729858261423E-2</v>
+        <v>7.1072427902042185E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.9701261507838749E-2</v>
+        <v>5.9992221052196176E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.2932045900344837E-2</v>
+        <v>5.3190015054900286E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.6037545216259655E-2</v>
+        <v>4.6261913392762907E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7046004211771704E-2</v>
+        <v>6.7372759029739521E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10078106102423183</v>
+        <v>0.10127222671914128</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4431230974372157E-2</v>
+        <v>9.4891450193254262E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5558047700604689E-2</v>
+        <v>7.5926286739048082E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5274322668787613E-2</v>
+        <v>7.5641178947404908E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4283531754601617E-2</v>
+        <v>7.4645559323311211E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1617647669355864E-2</v>
+        <v>8.2015418721049352E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6566579854337088E-2</v>
+        <v>6.6890998153962239E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8381441703798796E-2</v>
+        <v>5.8665968985937324E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3958982770353471E-2</v>
+        <v>5.4221956795429821E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15488,16 +15477,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15509,7 +15498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15522,7 +15511,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15543,7 +15532,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15554,7 +15543,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15572,7 +15561,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15588,7 +15577,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15604,7 +15593,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15620,7 +15609,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15634,7 +15623,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15648,7 +15637,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15662,10 +15651,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15675,13 +15664,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15691,7 +15680,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15701,7 +15690,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15715,10 +15704,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15736,7 +15725,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15758,7 +15747,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15780,7 +15769,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15812,7 +15801,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15844,7 +15833,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15876,7 +15865,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15898,7 +15887,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15920,7 +15909,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15942,7 +15931,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15964,7 +15953,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15986,7 +15975,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16008,7 +15997,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16030,7 +16019,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16062,7 +16051,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16094,7 +16083,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16126,7 +16115,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16148,7 +16137,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16170,7 +16159,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16192,7 +16181,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16214,7 +16203,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16236,7 +16225,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16258,7 +16247,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16280,7 +16269,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16302,7 +16291,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16324,7 +16313,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16346,7 +16335,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16368,7 +16357,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16400,7 +16389,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16432,7 +16421,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16464,7 +16453,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16496,7 +16485,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16518,7 +16507,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16529,11 +16518,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16543,7 +16532,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>95697646460.255325</v>
@@ -16570,7 +16559,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16592,7 +16581,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16613,7 +16602,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16644,7 +16633,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16675,7 +16664,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16706,7 +16695,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16737,7 +16726,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16754,7 +16743,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16774,7 +16763,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>-0.05</v>
@@ -16797,7 +16786,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16823,7 +16812,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16850,7 +16839,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16877,7 +16866,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16904,7 +16893,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16931,7 +16920,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16957,7 +16946,7 @@
         <v>131.7906765060531</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16983,7 +16972,7 @@
         <v>151.53060655486485</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17000,7 +16989,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17022,7 +17011,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17045,7 +17034,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17068,7 +17057,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17091,7 +17080,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17113,14 +17102,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17128,26 +17117,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17161,7 +17150,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17175,7 +17164,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17189,7 +17178,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17203,7 +17192,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17248,16 +17237,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17269,7 +17258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17282,7 +17271,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17303,7 +17292,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17314,7 +17303,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17330,7 +17319,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17344,10 +17333,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17357,13 +17346,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17373,7 +17362,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17383,7 +17372,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17397,10 +17386,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17418,7 +17407,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17440,7 +17429,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17462,7 +17451,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17484,7 +17473,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17506,7 +17495,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17528,7 +17517,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17550,7 +17539,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17572,7 +17561,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17594,7 +17583,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17616,7 +17605,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17638,7 +17627,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17660,7 +17649,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17682,7 +17671,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17704,7 +17693,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17726,7 +17715,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17748,7 +17737,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17770,7 +17759,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17792,7 +17781,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17814,7 +17803,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17836,7 +17825,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17858,7 +17847,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17880,7 +17869,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17902,7 +17891,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17924,7 +17913,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17946,7 +17935,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17968,7 +17957,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17990,7 +17979,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18012,7 +18001,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18034,7 +18023,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18056,7 +18045,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18078,7 +18067,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18100,7 +18089,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18111,11 +18100,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18125,7 +18114,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>122868445084.74913</v>
@@ -18152,7 +18141,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18174,7 +18163,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18195,7 +18184,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18216,7 +18205,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18237,7 +18226,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18258,7 +18247,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18279,14 +18268,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18296,7 +18285,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>-0.05</v>
@@ -18319,7 +18308,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18345,7 +18334,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18372,7 +18361,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18399,7 +18388,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18426,7 +18415,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18453,7 +18442,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18479,7 +18468,7 @@
         <v>150.86796886254572</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18505,7 +18494,7 @@
         <v>176.2125264446021</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18522,7 +18511,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18544,7 +18533,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18567,7 +18556,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18590,7 +18579,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18613,7 +18602,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18635,14 +18624,14 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18650,23 +18639,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18696,7 +18685,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18706,7 +18695,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18719,7 +18708,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18728,10 +18717,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-65.98</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-65.66</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18751,7 +18740,7 @@
         <v>4.6470000000000002</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18760,7 +18749,7 @@
         <v>4.6470000000000002</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18780,7 +18769,7 @@
         <v>82.43260460275485</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18805,7 +18794,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18827,7 +18816,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18849,7 +18838,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18860,7 +18849,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18874,7 +18863,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18893,7 +18882,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18911,7 +18900,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18922,7 +18911,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18931,7 +18920,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18939,7 +18928,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18951,24 +18940,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>65.98</v>
+        <v>65.66</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18977,7 +18966,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18992,7 +18981,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19001,7 +18990,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19013,7 +19002,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19024,7 +19013,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19039,7 +19028,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19050,7 +19039,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19059,7 +19048,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19071,7 +19060,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19082,7 +19071,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19097,7 +19086,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19108,7 +19097,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19117,7 +19106,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19129,7 +19118,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19140,7 +19129,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19155,7 +19144,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19167,7 +19156,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19180,7 +19169,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19189,12 +19178,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19204,12 +19193,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19218,7 +19207,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19230,7 +19219,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19241,7 +19230,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19256,7 +19245,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19267,7 +19256,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19276,7 +19265,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19288,7 +19277,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19299,7 +19288,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19314,7 +19303,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19325,7 +19314,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19345,7 +19334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19354,7 +19343,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19362,7 +19351,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19375,7 +19364,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19387,7 +19376,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19403,7 +19392,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19411,7 +19400,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19421,7 +19410,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19433,7 +19422,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19443,7 +19432,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19459,7 +19448,7 @@
         <v>0.18364896670378619</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19468,12 +19457,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19483,7 +19472,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19496,12 +19485,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19510,7 +19499,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19522,7 +19511,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19532,7 +19521,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19552,45 +19541,45 @@
         <v>0.47848662078609472</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>65.98</v>
+        <v>65.66</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1232882180025836</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.12522746818781161</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19599,7 +19588,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19611,7 +19600,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19621,7 +19610,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19641,14 +19630,14 @@
         <v>0.27362252180270386</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19659,7 +19648,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19671,7 +19660,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19683,7 +19672,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19702,15 +19691,15 @@
         <v>6.9195974091051937E-4</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19719,7 +19708,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19729,7 +19718,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19739,7 +19728,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19758,16 +19747,16 @@
         <v>6.9397561757708282E-2</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19775,7 +19764,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19783,7 +19772,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B42F87F-2EFC-4B95-B2DE-CD4C5F231B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5469F5-E7B9-4E4E-ACD9-42E59BFC4335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>65.66</v>
+        <v>66.03</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>98948.832079999993</v>
+        <v>99506.41764</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12522746818781161</v>
+        <v>0.12298639034896053</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.5122980128697124E-2</v>
+        <v>5.4814097762384571E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.077368260737131E-2</v>
+        <v>7.0377101317582916E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13475,12 +13475,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.077368260737131E-2</v>
+        <v>7.0377101317582916E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.077368260737131E-2</v>
+        <v>7.0377101317582916E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14674,50 +14674,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5122980128697124E-2</v>
+        <v>5.4814097762384571E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.4596322749944562E-2</v>
+        <v>6.4234356379847937E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.2598116498013083E-2</v>
+        <v>9.2079241697100384E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.7916432042915174E-2</v>
+        <v>8.7423791124304248E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>7.0309068005062703E-2</v>
+        <v>6.9915090189495932E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.9153693755702048E-2</v>
+        <v>4.8878260366490935E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.2832716252380766E-2</v>
+        <v>6.2480632275197949E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>7.1072427902042185E-2</v>
+        <v>7.0674172588945774E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>5.9992221052196176E-2</v>
+        <v>5.9656053828368936E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>5.3190015054900286E-2</v>
+        <v>5.2891964084579017E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>4.6261913392762907E-2</v>
+        <v>4.6002684134011998E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14731,43 +14731,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7372759029739521E-2</v>
+        <v>6.6995234861316033E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10127222671914128</v>
+        <v>0.10070474642403175</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4891450193254262E-2</v>
+        <v>9.4359724665895428E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5926286739048082E-2</v>
+        <v>7.5500832762167153E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5641178947404908E-2</v>
+        <v>7.5217322575898929E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4645559323311211E-2</v>
+        <v>7.4227281919863913E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2015418721049352E-2</v>
+        <v>8.1555844210572465E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6890998153962239E-2</v>
+        <v>6.6516173539136164E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8665968985937324E-2</v>
+        <v>5.8337233433539977E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4221956795429821E-2</v>
+        <v>5.3918123325578098E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18717,7 +18717,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-65.66</v>
+        <v>-66.03</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>65.66</v>
+        <v>66.03</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>65.66</v>
+        <v>66.03</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19568,7 +19568,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12522746818781161</v>
+        <v>0.12298639034896053</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/002304.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/002304.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5469F5-E7B9-4E4E-ACD9-42E59BFC4335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C71B16-C5E8-40CE-A39E-EC8FA571A005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>66.03</v>
+        <v>65.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>99506.41764</v>
+        <v>99009.111600000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12298639034896053</v>
+        <v>0.12498434453750562</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans=